--- a/Fudbal Bezanija Termini.xlsx
+++ b/Fudbal Bezanija Termini.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beoog\Desktop\Fudbal Bezanija\Sajt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50024061-A6FE-413A-8F5C-2BEBEBD0EB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8970561-6BBC-418F-B2F6-8DDECA40EDDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="75">
   <si>
     <t>No.</t>
   </si>
@@ -253,6 +253,12 @@
   </si>
   <si>
     <t>Body Goals</t>
+  </si>
+  <si>
+    <t>Nenad Vidakovic</t>
+  </si>
+  <si>
+    <t>Bubanja (Golman)</t>
   </si>
 </sst>
 </file>
@@ -1033,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ369"/>
+  <dimension ref="A1:AJ370"/>
   <sheetFormatPr defaultColWidth="7.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
@@ -18085,7 +18091,9 @@
       <c r="AF159" s="31">
         <v>0</v>
       </c>
-      <c r="AG159" s="32"/>
+      <c r="AG159" s="32">
+        <v>3</v>
+      </c>
       <c r="AH159" s="12">
         <v>62</v>
       </c>
@@ -18190,7 +18198,9 @@
       <c r="AF160" s="31">
         <v>0</v>
       </c>
-      <c r="AG160" s="32"/>
+      <c r="AG160" s="32">
+        <v>3</v>
+      </c>
       <c r="AH160" s="12">
         <v>62</v>
       </c>
@@ -18295,7 +18305,9 @@
       <c r="AF161" s="31">
         <v>0</v>
       </c>
-      <c r="AG161" s="32"/>
+      <c r="AG161" s="32">
+        <v>3</v>
+      </c>
       <c r="AH161" s="12">
         <v>62</v>
       </c>
@@ -18400,7 +18412,9 @@
       <c r="AF162" s="31">
         <v>0</v>
       </c>
-      <c r="AG162" s="32"/>
+      <c r="AG162" s="32">
+        <v>3</v>
+      </c>
       <c r="AH162" s="12">
         <v>62</v>
       </c>
@@ -18505,7 +18519,9 @@
       <c r="AF163" s="31">
         <v>0</v>
       </c>
-      <c r="AG163" s="32"/>
+      <c r="AG163" s="32">
+        <v>3</v>
+      </c>
       <c r="AH163" s="12">
         <v>62</v>
       </c>
@@ -18610,7 +18626,9 @@
       <c r="AF164" s="31">
         <v>0</v>
       </c>
-      <c r="AG164" s="32"/>
+      <c r="AG164" s="32">
+        <v>3</v>
+      </c>
       <c r="AH164" s="12">
         <v>62</v>
       </c>
@@ -18715,7 +18733,9 @@
       <c r="AF165" s="31">
         <v>0</v>
       </c>
-      <c r="AG165" s="32"/>
+      <c r="AG165" s="32">
+        <v>0</v>
+      </c>
       <c r="AH165" s="12">
         <v>62</v>
       </c>
@@ -18735,13 +18755,13 @@
       </c>
       <c r="E166" s="3">
         <f t="shared" si="11"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F166" s="3">
         <v>0</v>
       </c>
       <c r="G166" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166" s="3">
         <v>0</v>
@@ -18751,7 +18771,7 @@
       </c>
       <c r="J166" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K166" s="3">
         <v>8</v>
@@ -18760,7 +18780,7 @@
         <v>2</v>
       </c>
       <c r="M166" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N166" s="7">
         <v>0</v>
@@ -18773,7 +18793,7 @@
       </c>
       <c r="Q166" s="36">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R166" s="4">
         <v>3</v>
@@ -18820,7 +18840,9 @@
       <c r="AF166" s="31">
         <v>0</v>
       </c>
-      <c r="AG166" s="32"/>
+      <c r="AG166" s="32">
+        <v>0</v>
+      </c>
       <c r="AH166" s="12">
         <v>62</v>
       </c>
@@ -18925,7 +18947,9 @@
       <c r="AF167" s="31">
         <v>0</v>
       </c>
-      <c r="AG167" s="32"/>
+      <c r="AG167" s="32">
+        <v>0</v>
+      </c>
       <c r="AH167" s="12">
         <v>62</v>
       </c>
@@ -19030,7 +19054,9 @@
       <c r="AF168" s="31">
         <v>0</v>
       </c>
-      <c r="AG168" s="32"/>
+      <c r="AG168" s="32">
+        <v>0</v>
+      </c>
       <c r="AH168" s="12">
         <v>62</v>
       </c>
@@ -19135,7 +19161,9 @@
       <c r="AF169" s="31">
         <v>0</v>
       </c>
-      <c r="AG169" s="32"/>
+      <c r="AG169" s="32">
+        <v>0</v>
+      </c>
       <c r="AH169" s="12">
         <v>62</v>
       </c>
@@ -19240,7 +19268,9 @@
       <c r="AF170" s="31">
         <v>0</v>
       </c>
-      <c r="AG170" s="32"/>
+      <c r="AG170" s="32">
+        <v>0</v>
+      </c>
       <c r="AH170" s="12">
         <v>62</v>
       </c>
@@ -20629,7 +20659,9 @@
       <c r="AF183" s="31">
         <v>0</v>
       </c>
-      <c r="AG183" s="32"/>
+      <c r="AG183" s="32">
+        <v>3</v>
+      </c>
       <c r="AH183" s="6">
         <v>55</v>
       </c>
@@ -20734,7 +20766,9 @@
       <c r="AF184" s="31">
         <v>0</v>
       </c>
-      <c r="AG184" s="32"/>
+      <c r="AG184" s="32">
+        <v>3</v>
+      </c>
       <c r="AH184" s="6">
         <v>55</v>
       </c>
@@ -20839,7 +20873,9 @@
       <c r="AF185" s="31">
         <v>0</v>
       </c>
-      <c r="AG185" s="32"/>
+      <c r="AG185" s="32">
+        <v>3</v>
+      </c>
       <c r="AH185" s="6">
         <v>55</v>
       </c>
@@ -20944,7 +20980,9 @@
       <c r="AF186" s="31">
         <v>0</v>
       </c>
-      <c r="AG186" s="32"/>
+      <c r="AG186" s="32">
+        <v>3</v>
+      </c>
       <c r="AH186" s="6">
         <v>55</v>
       </c>
@@ -21049,7 +21087,9 @@
       <c r="AF187" s="31">
         <v>0</v>
       </c>
-      <c r="AG187" s="32"/>
+      <c r="AG187" s="32">
+        <v>3</v>
+      </c>
       <c r="AH187" s="6">
         <v>55</v>
       </c>
@@ -21154,7 +21194,9 @@
       <c r="AF188" s="31">
         <v>0</v>
       </c>
-      <c r="AG188" s="32"/>
+      <c r="AG188" s="32">
+        <v>0</v>
+      </c>
       <c r="AH188" s="6">
         <v>55</v>
       </c>
@@ -21259,7 +21301,9 @@
       <c r="AF189" s="31">
         <v>0</v>
       </c>
-      <c r="AG189" s="32"/>
+      <c r="AG189" s="32">
+        <v>0</v>
+      </c>
       <c r="AH189" s="6">
         <v>55</v>
       </c>
@@ -21364,7 +21408,9 @@
       <c r="AF190" s="31">
         <v>0</v>
       </c>
-      <c r="AG190" s="32"/>
+      <c r="AG190" s="32">
+        <v>0</v>
+      </c>
       <c r="AH190" s="6">
         <v>55</v>
       </c>
@@ -21469,7 +21515,9 @@
       <c r="AF191" s="31">
         <v>0</v>
       </c>
-      <c r="AG191" s="32"/>
+      <c r="AG191" s="32">
+        <v>0</v>
+      </c>
       <c r="AH191" s="6">
         <v>55</v>
       </c>
@@ -21574,7 +21622,9 @@
       <c r="AF192" s="31">
         <v>0</v>
       </c>
-      <c r="AG192" s="32"/>
+      <c r="AG192" s="32">
+        <v>0</v>
+      </c>
       <c r="AH192" s="6">
         <v>55</v>
       </c>
@@ -23519,7 +23569,7 @@
         <v>44</v>
       </c>
       <c r="E211" s="3">
-        <f t="shared" ref="E211:E274" si="15">SUM(F211:AF211)-SUM(F211:L211,Q211)</f>
+        <f t="shared" ref="E211:E275" si="15">SUM(F211:AF211)-SUM(F211:L211,Q211)</f>
         <v>71</v>
       </c>
       <c r="F211" s="3">
@@ -23856,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="J214" s="3">
-        <f t="shared" ref="J214:J277" si="16">SUM(F214:I214)</f>
+        <f t="shared" ref="J214:J278" si="16">SUM(F214:I214)</f>
         <v>1</v>
       </c>
       <c r="K214" s="3">
@@ -23985,7 +24035,7 @@
         <v>4</v>
       </c>
       <c r="Q215" s="36">
-        <f t="shared" ref="Q215:Q278" si="17">SUM(M215:P215)</f>
+        <f t="shared" ref="Q215:Q279" si="17">SUM(M215:P215)</f>
         <v>9</v>
       </c>
       <c r="R215" s="4">
@@ -25446,10 +25496,14 @@
       </c>
       <c r="E229" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F229" s="3"/>
-      <c r="G229" s="3"/>
+        <v>141</v>
+      </c>
+      <c r="F229" s="3">
+        <v>0</v>
+      </c>
+      <c r="G229" s="3">
+        <v>1</v>
+      </c>
       <c r="H229" s="3">
         <v>0</v>
       </c>
@@ -25458,32 +25512,66 @@
       </c>
       <c r="J229" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K229" s="3"/>
-      <c r="L229" s="3"/>
-      <c r="M229" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K229" s="3">
+        <v>0</v>
+      </c>
+      <c r="L229" s="3">
+        <v>4</v>
+      </c>
+      <c r="M229" s="4">
+        <v>6</v>
+      </c>
       <c r="N229" s="7">
-        <v>0</v>
-      </c>
-      <c r="O229" s="5"/>
-      <c r="P229" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="O229" s="5">
+        <v>1</v>
+      </c>
+      <c r="P229" s="5">
+        <v>0</v>
+      </c>
       <c r="Q229" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R229" s="4"/>
-      <c r="S229" s="4"/>
-      <c r="T229" s="5"/>
-      <c r="U229" s="4"/>
-      <c r="V229" s="5"/>
-      <c r="W229" s="4"/>
-      <c r="X229" s="4"/>
-      <c r="Y229" s="4"/>
-      <c r="Z229" s="5"/>
-      <c r="AA229" s="4"/>
-      <c r="AB229" s="5"/>
-      <c r="AC229" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="R229" s="4">
+        <v>5</v>
+      </c>
+      <c r="S229" s="4">
+        <v>63</v>
+      </c>
+      <c r="T229" s="5">
+        <v>20</v>
+      </c>
+      <c r="U229" s="4">
+        <v>5</v>
+      </c>
+      <c r="V229" s="5">
+        <v>7</v>
+      </c>
+      <c r="W229" s="4">
+        <v>8</v>
+      </c>
+      <c r="X229" s="4">
+        <v>17</v>
+      </c>
+      <c r="Y229" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z229" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA229" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB229" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC229" s="3">
+        <v>5</v>
+      </c>
       <c r="AD229" s="3">
         <v>0</v>
       </c>
@@ -25493,9 +25581,11 @@
       <c r="AF229" s="31">
         <v>0</v>
       </c>
-      <c r="AG229" s="32"/>
+      <c r="AG229" s="32">
+        <v>3</v>
+      </c>
       <c r="AH229" s="6">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="230" spans="1:34" x14ac:dyDescent="0.25">
@@ -25513,10 +25603,14 @@
       </c>
       <c r="E230" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F230" s="3"/>
-      <c r="G230" s="3"/>
+        <v>104</v>
+      </c>
+      <c r="F230" s="3">
+        <v>0</v>
+      </c>
+      <c r="G230" s="3">
+        <v>0</v>
+      </c>
       <c r="H230" s="3">
         <v>0</v>
       </c>
@@ -25527,30 +25621,64 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K230" s="3"/>
-      <c r="L230" s="3"/>
-      <c r="M230" s="4"/>
+      <c r="K230" s="3">
+        <v>1</v>
+      </c>
+      <c r="L230" s="3">
+        <v>3</v>
+      </c>
+      <c r="M230" s="4">
+        <v>1</v>
+      </c>
       <c r="N230" s="7">
         <v>0</v>
       </c>
-      <c r="O230" s="5"/>
-      <c r="P230" s="5"/>
+      <c r="O230" s="5">
+        <v>5</v>
+      </c>
+      <c r="P230" s="5">
+        <v>3</v>
+      </c>
       <c r="Q230" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R230" s="4"/>
-      <c r="S230" s="4"/>
-      <c r="T230" s="5"/>
-      <c r="U230" s="4"/>
-      <c r="V230" s="5"/>
-      <c r="W230" s="4"/>
-      <c r="X230" s="4"/>
-      <c r="Y230" s="4"/>
-      <c r="Z230" s="5"/>
-      <c r="AA230" s="4"/>
-      <c r="AB230" s="5"/>
-      <c r="AC230" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="R230" s="4">
+        <v>5</v>
+      </c>
+      <c r="S230" s="4">
+        <v>42</v>
+      </c>
+      <c r="T230" s="5">
+        <v>13</v>
+      </c>
+      <c r="U230" s="4">
+        <v>5</v>
+      </c>
+      <c r="V230" s="5">
+        <v>6</v>
+      </c>
+      <c r="W230" s="4">
+        <v>4</v>
+      </c>
+      <c r="X230" s="4">
+        <v>12</v>
+      </c>
+      <c r="Y230" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z230" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA230" s="4">
+        <v>4</v>
+      </c>
+      <c r="AB230" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC230" s="3">
+        <v>4</v>
+      </c>
       <c r="AD230" s="3">
         <v>0</v>
       </c>
@@ -25560,9 +25688,11 @@
       <c r="AF230" s="31">
         <v>0</v>
       </c>
-      <c r="AG230" s="32"/>
+      <c r="AG230" s="32">
+        <v>3</v>
+      </c>
       <c r="AH230" s="6">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="231" spans="1:34" x14ac:dyDescent="0.25">
@@ -25580,10 +25710,14 @@
       </c>
       <c r="E231" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F231" s="3"/>
-      <c r="G231" s="3"/>
+        <v>82</v>
+      </c>
+      <c r="F231" s="3">
+        <v>0</v>
+      </c>
+      <c r="G231" s="3">
+        <v>0</v>
+      </c>
       <c r="H231" s="3">
         <v>0</v>
       </c>
@@ -25594,30 +25728,64 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K231" s="3"/>
-      <c r="L231" s="3"/>
-      <c r="M231" s="4"/>
+      <c r="K231" s="3">
+        <v>0</v>
+      </c>
+      <c r="L231" s="3">
+        <v>2</v>
+      </c>
+      <c r="M231" s="4">
+        <v>1</v>
+      </c>
       <c r="N231" s="7">
         <v>0</v>
       </c>
-      <c r="O231" s="5"/>
-      <c r="P231" s="5"/>
+      <c r="O231" s="5">
+        <v>3</v>
+      </c>
+      <c r="P231" s="5">
+        <v>2</v>
+      </c>
       <c r="Q231" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R231" s="4"/>
-      <c r="S231" s="4"/>
-      <c r="T231" s="5"/>
-      <c r="U231" s="4"/>
-      <c r="V231" s="5"/>
-      <c r="W231" s="4"/>
-      <c r="X231" s="4"/>
-      <c r="Y231" s="4"/>
-      <c r="Z231" s="5"/>
-      <c r="AA231" s="4"/>
-      <c r="AB231" s="5"/>
-      <c r="AC231" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="R231" s="4">
+        <v>0</v>
+      </c>
+      <c r="S231" s="4">
+        <v>34</v>
+      </c>
+      <c r="T231" s="5">
+        <v>15</v>
+      </c>
+      <c r="U231" s="4">
+        <v>5</v>
+      </c>
+      <c r="V231" s="5">
+        <v>8</v>
+      </c>
+      <c r="W231" s="4">
+        <v>3</v>
+      </c>
+      <c r="X231" s="4">
+        <v>7</v>
+      </c>
+      <c r="Y231" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z231" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA231" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB231" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC231" s="3">
+        <v>1</v>
+      </c>
       <c r="AD231" s="3">
         <v>0</v>
       </c>
@@ -25627,9 +25795,11 @@
       <c r="AF231" s="31">
         <v>0</v>
       </c>
-      <c r="AG231" s="32"/>
+      <c r="AG231" s="32">
+        <v>3</v>
+      </c>
       <c r="AH231" s="6">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="232" spans="1:34" x14ac:dyDescent="0.25">
@@ -25647,10 +25817,14 @@
       </c>
       <c r="E232" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F232" s="3"/>
-      <c r="G232" s="3"/>
+        <v>118</v>
+      </c>
+      <c r="F232" s="3">
+        <v>0</v>
+      </c>
+      <c r="G232" s="3">
+        <v>1</v>
+      </c>
       <c r="H232" s="3">
         <v>0</v>
       </c>
@@ -25659,32 +25833,66 @@
       </c>
       <c r="J232" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K232" s="3"/>
-      <c r="L232" s="3"/>
-      <c r="M232" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K232" s="3">
+        <v>2</v>
+      </c>
+      <c r="L232" s="3">
+        <v>6</v>
+      </c>
+      <c r="M232" s="4">
+        <v>4</v>
+      </c>
       <c r="N232" s="7">
         <v>0</v>
       </c>
-      <c r="O232" s="5"/>
-      <c r="P232" s="5"/>
+      <c r="O232" s="5">
+        <v>1</v>
+      </c>
+      <c r="P232" s="5">
+        <v>3</v>
+      </c>
       <c r="Q232" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R232" s="4"/>
-      <c r="S232" s="4"/>
-      <c r="T232" s="5"/>
-      <c r="U232" s="4"/>
-      <c r="V232" s="5"/>
-      <c r="W232" s="4"/>
-      <c r="X232" s="4"/>
-      <c r="Y232" s="4"/>
-      <c r="Z232" s="5"/>
-      <c r="AA232" s="4"/>
-      <c r="AB232" s="5"/>
-      <c r="AC232" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="R232" s="4">
+        <v>2</v>
+      </c>
+      <c r="S232" s="4">
+        <v>58</v>
+      </c>
+      <c r="T232" s="5">
+        <v>20</v>
+      </c>
+      <c r="U232" s="4">
+        <v>4</v>
+      </c>
+      <c r="V232" s="5">
+        <v>3</v>
+      </c>
+      <c r="W232" s="4">
+        <v>2</v>
+      </c>
+      <c r="X232" s="4">
+        <v>11</v>
+      </c>
+      <c r="Y232" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z232" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA232" s="4">
+        <v>5</v>
+      </c>
+      <c r="AB232" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC232" s="3">
+        <v>2</v>
+      </c>
       <c r="AD232" s="3">
         <v>0</v>
       </c>
@@ -25694,9 +25902,11 @@
       <c r="AF232" s="31">
         <v>0</v>
       </c>
-      <c r="AG232" s="32"/>
+      <c r="AG232" s="32">
+        <v>3</v>
+      </c>
       <c r="AH232" s="6">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="233" spans="1:34" x14ac:dyDescent="0.25">
@@ -25714,10 +25924,14 @@
       </c>
       <c r="E233" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F233" s="3"/>
-      <c r="G233" s="3"/>
+        <v>86</v>
+      </c>
+      <c r="F233" s="3">
+        <v>0</v>
+      </c>
+      <c r="G233" s="3">
+        <v>2</v>
+      </c>
       <c r="H233" s="3">
         <v>0</v>
       </c>
@@ -25726,32 +25940,66 @@
       </c>
       <c r="J233" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K233" s="3"/>
-      <c r="L233" s="3"/>
-      <c r="M233" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="K233" s="3">
+        <v>0</v>
+      </c>
+      <c r="L233" s="3">
+        <v>3</v>
+      </c>
+      <c r="M233" s="4">
+        <v>5</v>
+      </c>
       <c r="N233" s="7">
         <v>0</v>
       </c>
-      <c r="O233" s="5"/>
-      <c r="P233" s="5"/>
+      <c r="O233" s="5">
+        <v>1</v>
+      </c>
+      <c r="P233" s="5">
+        <v>4</v>
+      </c>
       <c r="Q233" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R233" s="4"/>
-      <c r="S233" s="4"/>
-      <c r="T233" s="5"/>
-      <c r="U233" s="4"/>
-      <c r="V233" s="5"/>
-      <c r="W233" s="4"/>
-      <c r="X233" s="4"/>
-      <c r="Y233" s="4"/>
-      <c r="Z233" s="5"/>
-      <c r="AA233" s="4"/>
-      <c r="AB233" s="5"/>
-      <c r="AC233" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="R233" s="4">
+        <v>0</v>
+      </c>
+      <c r="S233" s="4">
+        <v>32</v>
+      </c>
+      <c r="T233" s="5">
+        <v>13</v>
+      </c>
+      <c r="U233" s="4">
+        <v>5</v>
+      </c>
+      <c r="V233" s="5">
+        <v>6</v>
+      </c>
+      <c r="W233" s="4">
+        <v>1</v>
+      </c>
+      <c r="X233" s="4">
+        <v>17</v>
+      </c>
+      <c r="Y233" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z233" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA233" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB233" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC233" s="3">
+        <v>2</v>
+      </c>
       <c r="AD233" s="3">
         <v>0</v>
       </c>
@@ -25761,9 +26009,11 @@
       <c r="AF233" s="31">
         <v>0</v>
       </c>
-      <c r="AG233" s="32"/>
+      <c r="AG233" s="32">
+        <v>3</v>
+      </c>
       <c r="AH233" s="6">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="234" spans="1:34" x14ac:dyDescent="0.25">
@@ -25777,14 +26027,18 @@
         <v>32</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E234" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F234" s="3"/>
-      <c r="G234" s="3"/>
+        <v>74</v>
+      </c>
+      <c r="F234" s="3">
+        <v>0</v>
+      </c>
+      <c r="G234" s="3">
+        <v>1</v>
+      </c>
       <c r="H234" s="3">
         <v>0</v>
       </c>
@@ -25793,32 +26047,66 @@
       </c>
       <c r="J234" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K234" s="3"/>
-      <c r="L234" s="3"/>
-      <c r="M234" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K234" s="3">
+        <v>1</v>
+      </c>
+      <c r="L234" s="3">
+        <v>1</v>
+      </c>
+      <c r="M234" s="4">
+        <v>3</v>
+      </c>
       <c r="N234" s="7">
         <v>0</v>
       </c>
-      <c r="O234" s="5"/>
-      <c r="P234" s="5"/>
+      <c r="O234" s="5">
+        <v>2</v>
+      </c>
+      <c r="P234" s="5">
+        <v>2</v>
+      </c>
       <c r="Q234" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R234" s="4"/>
-      <c r="S234" s="4"/>
-      <c r="T234" s="5"/>
-      <c r="U234" s="4"/>
-      <c r="V234" s="5"/>
-      <c r="W234" s="4"/>
-      <c r="X234" s="4"/>
-      <c r="Y234" s="4"/>
-      <c r="Z234" s="5"/>
-      <c r="AA234" s="4"/>
-      <c r="AB234" s="5"/>
-      <c r="AC234" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="R234" s="4">
+        <v>1</v>
+      </c>
+      <c r="S234" s="4">
+        <v>29</v>
+      </c>
+      <c r="T234" s="5">
+        <v>14</v>
+      </c>
+      <c r="U234" s="4">
+        <v>1</v>
+      </c>
+      <c r="V234" s="5">
+        <v>3</v>
+      </c>
+      <c r="W234" s="4">
+        <v>3</v>
+      </c>
+      <c r="X234" s="4">
+        <v>8</v>
+      </c>
+      <c r="Y234" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z234" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA234" s="4">
+        <v>3</v>
+      </c>
+      <c r="AB234" s="5">
+        <v>2</v>
+      </c>
+      <c r="AC234" s="3">
+        <v>3</v>
+      </c>
       <c r="AD234" s="3">
         <v>0</v>
       </c>
@@ -25828,9 +26116,11 @@
       <c r="AF234" s="31">
         <v>0</v>
       </c>
-      <c r="AG234" s="32"/>
+      <c r="AG234" s="32">
+        <v>3</v>
+      </c>
       <c r="AH234" s="6">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="235" spans="1:34" x14ac:dyDescent="0.25">
@@ -25840,18 +26130,22 @@
       <c r="B235" s="27">
         <v>20260223</v>
       </c>
-      <c r="C235" s="3" t="s">
-        <v>33</v>
+      <c r="C235" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="E235" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F235" s="3"/>
-      <c r="G235" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="F235" s="3">
+        <v>0</v>
+      </c>
+      <c r="G235" s="3">
+        <v>0</v>
+      </c>
       <c r="H235" s="3">
         <v>0</v>
       </c>
@@ -25862,30 +26156,64 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K235" s="3"/>
-      <c r="L235" s="3"/>
-      <c r="M235" s="4"/>
+      <c r="K235" s="3">
+        <v>0</v>
+      </c>
+      <c r="L235" s="3">
+        <v>0</v>
+      </c>
+      <c r="M235" s="4">
+        <v>0</v>
+      </c>
       <c r="N235" s="7">
         <v>0</v>
       </c>
-      <c r="O235" s="5"/>
-      <c r="P235" s="5"/>
+      <c r="O235" s="5">
+        <v>0</v>
+      </c>
+      <c r="P235" s="5">
+        <v>0</v>
+      </c>
       <c r="Q235" s="36">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="R235" s="4"/>
-      <c r="S235" s="4"/>
-      <c r="T235" s="5"/>
-      <c r="U235" s="4"/>
-      <c r="V235" s="5"/>
-      <c r="W235" s="4"/>
-      <c r="X235" s="4"/>
-      <c r="Y235" s="4"/>
-      <c r="Z235" s="5"/>
-      <c r="AA235" s="4"/>
-      <c r="AB235" s="5"/>
-      <c r="AC235" s="3"/>
+      <c r="R235" s="4">
+        <v>0</v>
+      </c>
+      <c r="S235" s="4">
+        <v>6</v>
+      </c>
+      <c r="T235" s="5">
+        <v>3</v>
+      </c>
+      <c r="U235" s="4">
+        <v>0</v>
+      </c>
+      <c r="V235" s="5">
+        <v>0</v>
+      </c>
+      <c r="W235" s="4">
+        <v>0</v>
+      </c>
+      <c r="X235" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y235" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z235" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA235" s="4">
+        <v>3</v>
+      </c>
+      <c r="AB235" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC235" s="3">
+        <v>0</v>
+      </c>
       <c r="AD235" s="3">
         <v>0</v>
       </c>
@@ -25895,9 +26223,11 @@
       <c r="AF235" s="31">
         <v>0</v>
       </c>
-      <c r="AG235" s="32"/>
+      <c r="AG235" s="32">
+        <v>3</v>
+      </c>
       <c r="AH235" s="6">
-        <v>61</v>
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:34" x14ac:dyDescent="0.25">
@@ -25911,14 +26241,18 @@
         <v>33</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E236" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F236" s="3"/>
-      <c r="G236" s="3"/>
+        <v>88</v>
+      </c>
+      <c r="F236" s="3">
+        <v>0</v>
+      </c>
+      <c r="G236" s="3">
+        <v>0</v>
+      </c>
       <c r="H236" s="3">
         <v>0</v>
       </c>
@@ -25929,30 +26263,64 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K236" s="3"/>
-      <c r="L236" s="3"/>
-      <c r="M236" s="4"/>
+      <c r="K236" s="3">
+        <v>0</v>
+      </c>
+      <c r="L236" s="3">
+        <v>1</v>
+      </c>
+      <c r="M236" s="4">
+        <v>3</v>
+      </c>
       <c r="N236" s="7">
         <v>0</v>
       </c>
-      <c r="O236" s="5"/>
-      <c r="P236" s="5"/>
+      <c r="O236" s="5">
+        <v>4</v>
+      </c>
+      <c r="P236" s="5">
+        <v>0</v>
+      </c>
       <c r="Q236" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R236" s="4"/>
-      <c r="S236" s="4"/>
-      <c r="T236" s="5"/>
-      <c r="U236" s="4"/>
-      <c r="V236" s="5"/>
-      <c r="W236" s="4"/>
-      <c r="X236" s="4"/>
-      <c r="Y236" s="4"/>
-      <c r="Z236" s="5"/>
-      <c r="AA236" s="4"/>
-      <c r="AB236" s="5"/>
-      <c r="AC236" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="R236" s="4">
+        <v>0</v>
+      </c>
+      <c r="S236" s="4">
+        <v>43</v>
+      </c>
+      <c r="T236" s="5">
+        <v>9</v>
+      </c>
+      <c r="U236" s="4">
+        <v>3</v>
+      </c>
+      <c r="V236" s="5">
+        <v>2</v>
+      </c>
+      <c r="W236" s="4">
+        <v>6</v>
+      </c>
+      <c r="X236" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y236" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z236" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA236" s="4">
+        <v>3</v>
+      </c>
+      <c r="AB236" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC236" s="3">
+        <v>1</v>
+      </c>
       <c r="AD236" s="3">
         <v>0</v>
       </c>
@@ -25962,9 +26330,11 @@
       <c r="AF236" s="31">
         <v>0</v>
       </c>
-      <c r="AG236" s="32"/>
+      <c r="AG236" s="32">
+        <v>0</v>
+      </c>
       <c r="AH236" s="6">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="237" spans="1:34" x14ac:dyDescent="0.25">
@@ -25978,14 +26348,18 @@
         <v>33</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E237" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F237" s="3"/>
-      <c r="G237" s="3"/>
+        <v>93</v>
+      </c>
+      <c r="F237" s="3">
+        <v>0</v>
+      </c>
+      <c r="G237" s="3">
+        <v>1</v>
+      </c>
       <c r="H237" s="3">
         <v>0</v>
       </c>
@@ -25994,32 +26368,66 @@
       </c>
       <c r="J237" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K237" s="3"/>
-      <c r="L237" s="3"/>
-      <c r="M237" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K237" s="3">
+        <v>0</v>
+      </c>
+      <c r="L237" s="3">
+        <v>1</v>
+      </c>
+      <c r="M237" s="4">
+        <v>4</v>
+      </c>
       <c r="N237" s="7">
         <v>0</v>
       </c>
-      <c r="O237" s="5"/>
-      <c r="P237" s="5"/>
+      <c r="O237" s="5">
+        <v>4</v>
+      </c>
+      <c r="P237" s="5">
+        <v>5</v>
+      </c>
       <c r="Q237" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R237" s="4"/>
-      <c r="S237" s="4"/>
-      <c r="T237" s="5"/>
-      <c r="U237" s="4"/>
-      <c r="V237" s="5"/>
-      <c r="W237" s="4"/>
-      <c r="X237" s="4"/>
-      <c r="Y237" s="4"/>
-      <c r="Z237" s="5"/>
-      <c r="AA237" s="4"/>
-      <c r="AB237" s="5"/>
-      <c r="AC237" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="R237" s="4">
+        <v>2</v>
+      </c>
+      <c r="S237" s="4">
+        <v>36</v>
+      </c>
+      <c r="T237" s="5">
+        <v>8</v>
+      </c>
+      <c r="U237" s="4">
+        <v>5</v>
+      </c>
+      <c r="V237" s="5">
+        <v>7</v>
+      </c>
+      <c r="W237" s="4">
+        <v>5</v>
+      </c>
+      <c r="X237" s="4">
+        <v>13</v>
+      </c>
+      <c r="Y237" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z237" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA237" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB237" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC237" s="3">
+        <v>2</v>
+      </c>
       <c r="AD237" s="3">
         <v>0</v>
       </c>
@@ -26029,9 +26437,11 @@
       <c r="AF237" s="31">
         <v>0</v>
       </c>
-      <c r="AG237" s="32"/>
+      <c r="AG237" s="32">
+        <v>0</v>
+      </c>
       <c r="AH237" s="6">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="238" spans="1:34" x14ac:dyDescent="0.25">
@@ -26045,14 +26455,18 @@
         <v>33</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E238" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F238" s="3"/>
-      <c r="G238" s="3"/>
+        <v>124</v>
+      </c>
+      <c r="F238" s="3">
+        <v>0</v>
+      </c>
+      <c r="G238" s="3">
+        <v>1</v>
+      </c>
       <c r="H238" s="3">
         <v>0</v>
       </c>
@@ -26061,32 +26475,66 @@
       </c>
       <c r="J238" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K238" s="3"/>
-      <c r="L238" s="3"/>
-      <c r="M238" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K238" s="3">
+        <v>1</v>
+      </c>
+      <c r="L238" s="3">
+        <v>4</v>
+      </c>
+      <c r="M238" s="4">
+        <v>3</v>
+      </c>
       <c r="N238" s="7">
         <v>0</v>
       </c>
-      <c r="O238" s="5"/>
-      <c r="P238" s="5"/>
+      <c r="O238" s="5">
+        <v>1</v>
+      </c>
+      <c r="P238" s="5">
+        <v>1</v>
+      </c>
       <c r="Q238" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R238" s="4"/>
-      <c r="S238" s="4"/>
-      <c r="T238" s="5"/>
-      <c r="U238" s="4"/>
-      <c r="V238" s="5"/>
-      <c r="W238" s="4"/>
-      <c r="X238" s="4"/>
-      <c r="Y238" s="4"/>
-      <c r="Z238" s="5"/>
-      <c r="AA238" s="4"/>
-      <c r="AB238" s="5"/>
-      <c r="AC238" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="R238" s="4">
+        <v>4</v>
+      </c>
+      <c r="S238" s="4">
+        <v>47</v>
+      </c>
+      <c r="T238" s="5">
+        <v>19</v>
+      </c>
+      <c r="U238" s="4">
+        <v>6</v>
+      </c>
+      <c r="V238" s="5">
+        <v>3</v>
+      </c>
+      <c r="W238" s="4">
+        <v>7</v>
+      </c>
+      <c r="X238" s="4">
+        <v>29</v>
+      </c>
+      <c r="Y238" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z238" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA238" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB238" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC238" s="3">
+        <v>4</v>
+      </c>
       <c r="AD238" s="3">
         <v>0</v>
       </c>
@@ -26096,9 +26544,11 @@
       <c r="AF238" s="31">
         <v>0</v>
       </c>
-      <c r="AG238" s="32"/>
+      <c r="AG238" s="32">
+        <v>0</v>
+      </c>
       <c r="AH238" s="6">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="239" spans="1:34" x14ac:dyDescent="0.25">
@@ -26112,14 +26562,18 @@
         <v>33</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E239" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F239" s="3"/>
-      <c r="G239" s="3"/>
+        <v>104</v>
+      </c>
+      <c r="F239" s="3">
+        <v>0</v>
+      </c>
+      <c r="G239" s="3">
+        <v>0</v>
+      </c>
       <c r="H239" s="3">
         <v>0</v>
       </c>
@@ -26130,30 +26584,64 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K239" s="3"/>
-      <c r="L239" s="3"/>
-      <c r="M239" s="4"/>
+      <c r="K239" s="3">
+        <v>0</v>
+      </c>
+      <c r="L239" s="3">
+        <v>0</v>
+      </c>
+      <c r="M239" s="4">
+        <v>6</v>
+      </c>
       <c r="N239" s="7">
         <v>0</v>
       </c>
-      <c r="O239" s="5"/>
-      <c r="P239" s="5"/>
+      <c r="O239" s="5">
+        <v>2</v>
+      </c>
+      <c r="P239" s="5">
+        <v>1</v>
+      </c>
       <c r="Q239" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R239" s="4"/>
-      <c r="S239" s="4"/>
-      <c r="T239" s="5"/>
-      <c r="U239" s="4"/>
-      <c r="V239" s="5"/>
-      <c r="W239" s="4"/>
-      <c r="X239" s="4"/>
-      <c r="Y239" s="4"/>
-      <c r="Z239" s="5"/>
-      <c r="AA239" s="4"/>
-      <c r="AB239" s="5"/>
-      <c r="AC239" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="R239" s="4">
+        <v>5</v>
+      </c>
+      <c r="S239" s="4">
+        <v>48</v>
+      </c>
+      <c r="T239" s="5">
+        <v>14</v>
+      </c>
+      <c r="U239" s="4">
+        <v>3</v>
+      </c>
+      <c r="V239" s="5">
+        <v>4</v>
+      </c>
+      <c r="W239" s="4">
+        <v>7</v>
+      </c>
+      <c r="X239" s="4">
+        <v>11</v>
+      </c>
+      <c r="Y239" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z239" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA239" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB239" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC239" s="3">
+        <v>1</v>
+      </c>
       <c r="AD239" s="3">
         <v>0</v>
       </c>
@@ -26163,9 +26651,11 @@
       <c r="AF239" s="31">
         <v>0</v>
       </c>
-      <c r="AG239" s="32"/>
+      <c r="AG239" s="32">
+        <v>0</v>
+      </c>
       <c r="AH239" s="6">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="240" spans="1:34" x14ac:dyDescent="0.25">
@@ -26179,14 +26669,18 @@
         <v>33</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E240" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F240" s="3"/>
-      <c r="G240" s="3"/>
+        <v>107</v>
+      </c>
+      <c r="F240" s="3">
+        <v>0</v>
+      </c>
+      <c r="G240" s="3">
+        <v>2</v>
+      </c>
       <c r="H240" s="3">
         <v>0</v>
       </c>
@@ -26195,32 +26689,66 @@
       </c>
       <c r="J240" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K240" s="3"/>
-      <c r="L240" s="3"/>
-      <c r="M240" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="K240" s="3">
+        <v>1</v>
+      </c>
+      <c r="L240" s="3">
+        <v>5</v>
+      </c>
+      <c r="M240" s="4">
+        <v>5</v>
+      </c>
       <c r="N240" s="7">
         <v>0</v>
       </c>
-      <c r="O240" s="5"/>
-      <c r="P240" s="5"/>
+      <c r="O240" s="5">
+        <v>5</v>
+      </c>
+      <c r="P240" s="5">
+        <v>4</v>
+      </c>
       <c r="Q240" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R240" s="4"/>
-      <c r="S240" s="4"/>
-      <c r="T240" s="5"/>
-      <c r="U240" s="4"/>
-      <c r="V240" s="5"/>
-      <c r="W240" s="4"/>
-      <c r="X240" s="4"/>
-      <c r="Y240" s="4"/>
-      <c r="Z240" s="5"/>
-      <c r="AA240" s="4"/>
-      <c r="AB240" s="5"/>
-      <c r="AC240" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="R240" s="4">
+        <v>1</v>
+      </c>
+      <c r="S240" s="4">
+        <v>51</v>
+      </c>
+      <c r="T240" s="5">
+        <v>15</v>
+      </c>
+      <c r="U240" s="4">
+        <v>2</v>
+      </c>
+      <c r="V240" s="5">
+        <v>1</v>
+      </c>
+      <c r="W240" s="4">
+        <v>4</v>
+      </c>
+      <c r="X240" s="4">
+        <v>5</v>
+      </c>
+      <c r="Y240" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z240" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA240" s="4">
+        <v>10</v>
+      </c>
+      <c r="AB240" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC240" s="3">
+        <v>4</v>
+      </c>
       <c r="AD240" s="3">
         <v>0</v>
       </c>
@@ -26230,30 +26758,36 @@
       <c r="AF240" s="31">
         <v>0</v>
       </c>
-      <c r="AG240" s="32"/>
+      <c r="AG240" s="32">
+        <v>0</v>
+      </c>
       <c r="AH240" s="6">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="241" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A241" s="18">
-        <v>23</v>
-      </c>
-      <c r="B241" s="28">
-        <v>20260302</v>
-      </c>
-      <c r="C241" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
+      </c>
+      <c r="B241" s="27">
+        <v>20260223</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E241" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F241" s="3"/>
-      <c r="G241" s="3"/>
+        <v>104</v>
+      </c>
+      <c r="F241" s="3">
+        <v>0</v>
+      </c>
+      <c r="G241" s="3">
+        <v>0</v>
+      </c>
       <c r="H241" s="3">
         <v>0</v>
       </c>
@@ -26264,30 +26798,64 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K241" s="3"/>
-      <c r="L241" s="3"/>
-      <c r="M241" s="4"/>
+      <c r="K241" s="3">
+        <v>0</v>
+      </c>
+      <c r="L241" s="3">
+        <v>2</v>
+      </c>
+      <c r="M241" s="4">
+        <v>1</v>
+      </c>
       <c r="N241" s="7">
-        <v>0</v>
-      </c>
-      <c r="O241" s="5"/>
-      <c r="P241" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="O241" s="5">
+        <v>5</v>
+      </c>
+      <c r="P241" s="5">
+        <v>2</v>
+      </c>
       <c r="Q241" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R241" s="4"/>
-      <c r="S241" s="4"/>
-      <c r="T241" s="5"/>
-      <c r="U241" s="4"/>
-      <c r="V241" s="5"/>
-      <c r="W241" s="4"/>
-      <c r="X241" s="4"/>
-      <c r="Y241" s="4"/>
-      <c r="Z241" s="5"/>
-      <c r="AA241" s="4"/>
-      <c r="AB241" s="5"/>
-      <c r="AC241" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="R241" s="4">
+        <v>2</v>
+      </c>
+      <c r="S241" s="4">
+        <v>46</v>
+      </c>
+      <c r="T241" s="5">
+        <v>19</v>
+      </c>
+      <c r="U241" s="4">
+        <v>3</v>
+      </c>
+      <c r="V241" s="5">
+        <v>4</v>
+      </c>
+      <c r="W241" s="4">
+        <v>4</v>
+      </c>
+      <c r="X241" s="4">
+        <v>10</v>
+      </c>
+      <c r="Y241" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z241" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA241" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB241" s="5">
+        <v>3</v>
+      </c>
+      <c r="AC241" s="3">
+        <v>2</v>
+      </c>
       <c r="AD241" s="3">
         <v>0</v>
       </c>
@@ -26297,9 +26865,11 @@
       <c r="AF241" s="31">
         <v>0</v>
       </c>
-      <c r="AG241" s="32"/>
+      <c r="AG241" s="32">
+        <v>0</v>
+      </c>
       <c r="AH241" s="6">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="242" spans="1:34" x14ac:dyDescent="0.25">
@@ -26313,14 +26883,18 @@
         <v>32</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E242" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F242" s="3"/>
-      <c r="G242" s="3"/>
+        <v>131</v>
+      </c>
+      <c r="F242" s="3">
+        <v>0</v>
+      </c>
+      <c r="G242" s="3">
+        <v>1</v>
+      </c>
       <c r="H242" s="3">
         <v>0</v>
       </c>
@@ -26329,32 +26903,66 @@
       </c>
       <c r="J242" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K242" s="3"/>
-      <c r="L242" s="3"/>
-      <c r="M242" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K242" s="3">
+        <v>3</v>
+      </c>
+      <c r="L242" s="3">
+        <v>6</v>
+      </c>
+      <c r="M242" s="4">
+        <v>1</v>
+      </c>
       <c r="N242" s="7">
         <v>0</v>
       </c>
-      <c r="O242" s="5"/>
-      <c r="P242" s="5"/>
+      <c r="O242" s="5">
+        <v>3</v>
+      </c>
+      <c r="P242" s="5">
+        <v>0</v>
+      </c>
       <c r="Q242" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R242" s="4"/>
-      <c r="S242" s="4"/>
-      <c r="T242" s="5"/>
-      <c r="U242" s="4"/>
-      <c r="V242" s="5"/>
-      <c r="W242" s="4"/>
-      <c r="X242" s="4"/>
-      <c r="Y242" s="4"/>
-      <c r="Z242" s="5"/>
-      <c r="AA242" s="4"/>
-      <c r="AB242" s="5"/>
-      <c r="AC242" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="R242" s="4">
+        <v>0</v>
+      </c>
+      <c r="S242" s="4">
+        <v>65</v>
+      </c>
+      <c r="T242" s="5">
+        <v>14</v>
+      </c>
+      <c r="U242" s="4">
+        <v>5</v>
+      </c>
+      <c r="V242" s="5">
+        <v>11</v>
+      </c>
+      <c r="W242" s="4">
+        <v>9</v>
+      </c>
+      <c r="X242" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y242" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z242" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA242" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB242" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC242" s="3">
+        <v>6</v>
+      </c>
       <c r="AD242" s="3">
         <v>0</v>
       </c>
@@ -26364,7 +26972,9 @@
       <c r="AF242" s="31">
         <v>0</v>
       </c>
-      <c r="AG242" s="32"/>
+      <c r="AG242" s="32">
+        <v>0</v>
+      </c>
       <c r="AH242" s="6">
         <v>58</v>
       </c>
@@ -26380,14 +26990,18 @@
         <v>32</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E243" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F243" s="3"/>
-      <c r="G243" s="3"/>
+        <v>90</v>
+      </c>
+      <c r="F243" s="3">
+        <v>0</v>
+      </c>
+      <c r="G243" s="3">
+        <v>0</v>
+      </c>
       <c r="H243" s="3">
         <v>0</v>
       </c>
@@ -26398,30 +27012,64 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K243" s="3"/>
-      <c r="L243" s="3"/>
-      <c r="M243" s="4"/>
+      <c r="K243" s="3">
+        <v>1</v>
+      </c>
+      <c r="L243" s="3">
+        <v>3</v>
+      </c>
+      <c r="M243" s="4">
+        <v>2</v>
+      </c>
       <c r="N243" s="7">
         <v>0</v>
       </c>
-      <c r="O243" s="5"/>
-      <c r="P243" s="5"/>
+      <c r="O243" s="5">
+        <v>8</v>
+      </c>
+      <c r="P243" s="5">
+        <v>1</v>
+      </c>
       <c r="Q243" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R243" s="4"/>
-      <c r="S243" s="4"/>
-      <c r="T243" s="5"/>
-      <c r="U243" s="4"/>
-      <c r="V243" s="5"/>
-      <c r="W243" s="4"/>
-      <c r="X243" s="4"/>
-      <c r="Y243" s="4"/>
-      <c r="Z243" s="5"/>
-      <c r="AA243" s="4"/>
-      <c r="AB243" s="5"/>
-      <c r="AC243" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="R243" s="4">
+        <v>1</v>
+      </c>
+      <c r="S243" s="4">
+        <v>49</v>
+      </c>
+      <c r="T243" s="5">
+        <v>8</v>
+      </c>
+      <c r="U243" s="4">
+        <v>0</v>
+      </c>
+      <c r="V243" s="5">
+        <v>5</v>
+      </c>
+      <c r="W243" s="4">
+        <v>1</v>
+      </c>
+      <c r="X243" s="4">
+        <v>7</v>
+      </c>
+      <c r="Y243" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z243" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA243" s="4">
+        <v>6</v>
+      </c>
+      <c r="AB243" s="5">
+        <v>2</v>
+      </c>
+      <c r="AC243" s="3">
+        <v>0</v>
+      </c>
       <c r="AD243" s="3">
         <v>0</v>
       </c>
@@ -26431,7 +27079,9 @@
       <c r="AF243" s="31">
         <v>0</v>
       </c>
-      <c r="AG243" s="32"/>
+      <c r="AG243" s="32">
+        <v>0</v>
+      </c>
       <c r="AH243" s="6">
         <v>58</v>
       </c>
@@ -26447,14 +27097,18 @@
         <v>32</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E244" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F244" s="3"/>
-      <c r="G244" s="3"/>
+        <v>56</v>
+      </c>
+      <c r="F244" s="3">
+        <v>0</v>
+      </c>
+      <c r="G244" s="3">
+        <v>0</v>
+      </c>
       <c r="H244" s="3">
         <v>0</v>
       </c>
@@ -26465,30 +27119,64 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K244" s="3"/>
-      <c r="L244" s="3"/>
-      <c r="M244" s="4"/>
+      <c r="K244" s="3">
+        <v>0</v>
+      </c>
+      <c r="L244" s="3">
+        <v>2</v>
+      </c>
+      <c r="M244" s="4">
+        <v>0</v>
+      </c>
       <c r="N244" s="7">
         <v>0</v>
       </c>
-      <c r="O244" s="5"/>
-      <c r="P244" s="5"/>
+      <c r="O244" s="5">
+        <v>0</v>
+      </c>
+      <c r="P244" s="5">
+        <v>0</v>
+      </c>
       <c r="Q244" s="36">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="R244" s="4"/>
-      <c r="S244" s="4"/>
-      <c r="T244" s="5"/>
-      <c r="U244" s="4"/>
-      <c r="V244" s="5"/>
-      <c r="W244" s="4"/>
-      <c r="X244" s="4"/>
-      <c r="Y244" s="4"/>
-      <c r="Z244" s="5"/>
-      <c r="AA244" s="4"/>
-      <c r="AB244" s="5"/>
-      <c r="AC244" s="3"/>
+      <c r="R244" s="4">
+        <v>0</v>
+      </c>
+      <c r="S244" s="4">
+        <v>34</v>
+      </c>
+      <c r="T244" s="5">
+        <v>7</v>
+      </c>
+      <c r="U244" s="4">
+        <v>0</v>
+      </c>
+      <c r="V244" s="5">
+        <v>2</v>
+      </c>
+      <c r="W244" s="4">
+        <v>0</v>
+      </c>
+      <c r="X244" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y244" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z244" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA244" s="4">
+        <v>6</v>
+      </c>
+      <c r="AB244" s="5">
+        <v>3</v>
+      </c>
+      <c r="AC244" s="3">
+        <v>1</v>
+      </c>
       <c r="AD244" s="3">
         <v>0</v>
       </c>
@@ -26498,7 +27186,9 @@
       <c r="AF244" s="31">
         <v>0</v>
       </c>
-      <c r="AG244" s="32"/>
+      <c r="AG244" s="32">
+        <v>0</v>
+      </c>
       <c r="AH244" s="6">
         <v>58</v>
       </c>
@@ -26514,14 +27204,18 @@
         <v>32</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E245" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F245" s="3"/>
-      <c r="G245" s="3"/>
+        <v>97</v>
+      </c>
+      <c r="F245" s="3">
+        <v>0</v>
+      </c>
+      <c r="G245" s="3">
+        <v>3</v>
+      </c>
       <c r="H245" s="3">
         <v>0</v>
       </c>
@@ -26530,32 +27224,66 @@
       </c>
       <c r="J245" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K245" s="3"/>
-      <c r="L245" s="3"/>
-      <c r="M245" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="K245" s="3">
+        <v>2</v>
+      </c>
+      <c r="L245" s="3">
+        <v>3</v>
+      </c>
+      <c r="M245" s="4">
+        <v>6</v>
+      </c>
       <c r="N245" s="7">
         <v>0</v>
       </c>
-      <c r="O245" s="5"/>
-      <c r="P245" s="5"/>
+      <c r="O245" s="5">
+        <v>5</v>
+      </c>
+      <c r="P245" s="5">
+        <v>4</v>
+      </c>
       <c r="Q245" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R245" s="4"/>
-      <c r="S245" s="4"/>
-      <c r="T245" s="5"/>
-      <c r="U245" s="4"/>
-      <c r="V245" s="5"/>
-      <c r="W245" s="4"/>
-      <c r="X245" s="4"/>
-      <c r="Y245" s="4"/>
-      <c r="Z245" s="5"/>
-      <c r="AA245" s="4"/>
-      <c r="AB245" s="5"/>
-      <c r="AC245" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="R245" s="4">
+        <v>1</v>
+      </c>
+      <c r="S245" s="4">
+        <v>38</v>
+      </c>
+      <c r="T245" s="5">
+        <v>12</v>
+      </c>
+      <c r="U245" s="4">
+        <v>1</v>
+      </c>
+      <c r="V245" s="5">
+        <v>3</v>
+      </c>
+      <c r="W245" s="4">
+        <v>3</v>
+      </c>
+      <c r="X245" s="4">
+        <v>8</v>
+      </c>
+      <c r="Y245" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z245" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA245" s="4">
+        <v>11</v>
+      </c>
+      <c r="AB245" s="5">
+        <v>3</v>
+      </c>
+      <c r="AC245" s="3">
+        <v>1</v>
+      </c>
       <c r="AD245" s="3">
         <v>0</v>
       </c>
@@ -26565,7 +27293,9 @@
       <c r="AF245" s="31">
         <v>0</v>
       </c>
-      <c r="AG245" s="32"/>
+      <c r="AG245" s="32">
+        <v>0</v>
+      </c>
       <c r="AH245" s="6">
         <v>58</v>
       </c>
@@ -26577,18 +27307,22 @@
       <c r="B246" s="28">
         <v>20260302</v>
       </c>
-      <c r="C246" s="3" t="s">
-        <v>33</v>
+      <c r="C246" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E246" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F246" s="3"/>
-      <c r="G246" s="3"/>
+        <v>114</v>
+      </c>
+      <c r="F246" s="3">
+        <v>0</v>
+      </c>
+      <c r="G246" s="3">
+        <v>4</v>
+      </c>
       <c r="H246" s="3">
         <v>0</v>
       </c>
@@ -26597,32 +27331,66 @@
       </c>
       <c r="J246" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K246" s="3"/>
-      <c r="L246" s="3"/>
-      <c r="M246" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="K246" s="3">
+        <v>1</v>
+      </c>
+      <c r="L246" s="3">
+        <v>4</v>
+      </c>
+      <c r="M246" s="4">
+        <v>5</v>
+      </c>
       <c r="N246" s="7">
-        <v>0</v>
-      </c>
-      <c r="O246" s="5"/>
-      <c r="P246" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="O246" s="5">
+        <v>1</v>
+      </c>
+      <c r="P246" s="5">
+        <v>3</v>
+      </c>
       <c r="Q246" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R246" s="4"/>
-      <c r="S246" s="4"/>
-      <c r="T246" s="5"/>
-      <c r="U246" s="4"/>
-      <c r="V246" s="5"/>
-      <c r="W246" s="4"/>
-      <c r="X246" s="4"/>
-      <c r="Y246" s="4"/>
-      <c r="Z246" s="5"/>
-      <c r="AA246" s="4"/>
-      <c r="AB246" s="5"/>
-      <c r="AC246" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="R246" s="4">
+        <v>1</v>
+      </c>
+      <c r="S246" s="4">
+        <v>48</v>
+      </c>
+      <c r="T246" s="5">
+        <v>10</v>
+      </c>
+      <c r="U246" s="4">
+        <v>8</v>
+      </c>
+      <c r="V246" s="5">
+        <v>10</v>
+      </c>
+      <c r="W246" s="4">
+        <v>5</v>
+      </c>
+      <c r="X246" s="4">
+        <v>16</v>
+      </c>
+      <c r="Y246" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z246" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA246" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB246" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC246" s="3">
+        <v>2</v>
+      </c>
       <c r="AD246" s="3">
         <v>0</v>
       </c>
@@ -26632,7 +27400,9 @@
       <c r="AF246" s="31">
         <v>0</v>
       </c>
-      <c r="AG246" s="32"/>
+      <c r="AG246" s="32">
+        <v>0</v>
+      </c>
       <c r="AH246" s="6">
         <v>58</v>
       </c>
@@ -26648,14 +27418,18 @@
         <v>33</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E247" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F247" s="3"/>
-      <c r="G247" s="3"/>
+        <v>158</v>
+      </c>
+      <c r="F247" s="3">
+        <v>0</v>
+      </c>
+      <c r="G247" s="3">
+        <v>0</v>
+      </c>
       <c r="H247" s="3">
         <v>0</v>
       </c>
@@ -26666,30 +27440,64 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K247" s="3"/>
-      <c r="L247" s="3"/>
-      <c r="M247" s="4"/>
+      <c r="K247" s="3">
+        <v>3</v>
+      </c>
+      <c r="L247" s="3">
+        <v>7</v>
+      </c>
+      <c r="M247" s="4">
+        <v>8</v>
+      </c>
       <c r="N247" s="7">
-        <v>0</v>
-      </c>
-      <c r="O247" s="5"/>
-      <c r="P247" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="O247" s="5">
+        <v>5</v>
+      </c>
+      <c r="P247" s="5">
+        <v>0</v>
+      </c>
       <c r="Q247" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R247" s="4"/>
-      <c r="S247" s="4"/>
-      <c r="T247" s="5"/>
-      <c r="U247" s="4"/>
-      <c r="V247" s="5"/>
-      <c r="W247" s="4"/>
-      <c r="X247" s="4"/>
-      <c r="Y247" s="4"/>
-      <c r="Z247" s="5"/>
-      <c r="AA247" s="4"/>
-      <c r="AB247" s="5"/>
-      <c r="AC247" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="R247" s="4">
+        <v>2</v>
+      </c>
+      <c r="S247" s="4">
+        <v>79</v>
+      </c>
+      <c r="T247" s="5">
+        <v>21</v>
+      </c>
+      <c r="U247" s="4">
+        <v>4</v>
+      </c>
+      <c r="V247" s="5">
+        <v>7</v>
+      </c>
+      <c r="W247" s="4">
+        <v>10</v>
+      </c>
+      <c r="X247" s="4">
+        <v>12</v>
+      </c>
+      <c r="Y247" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z247" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA247" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB247" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC247" s="3">
+        <v>4</v>
+      </c>
       <c r="AD247" s="3">
         <v>0</v>
       </c>
@@ -26699,7 +27507,9 @@
       <c r="AF247" s="31">
         <v>0</v>
       </c>
-      <c r="AG247" s="32"/>
+      <c r="AG247" s="32">
+        <v>3</v>
+      </c>
       <c r="AH247" s="6">
         <v>58</v>
       </c>
@@ -26715,14 +27525,18 @@
         <v>33</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E248" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F248" s="3"/>
-      <c r="G248" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="F248" s="3">
+        <v>0</v>
+      </c>
+      <c r="G248" s="3">
+        <v>2</v>
+      </c>
       <c r="H248" s="3">
         <v>0</v>
       </c>
@@ -26731,32 +27545,66 @@
       </c>
       <c r="J248" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K248" s="3"/>
-      <c r="L248" s="3"/>
-      <c r="M248" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="K248" s="3">
+        <v>1</v>
+      </c>
+      <c r="L248" s="3">
+        <v>2</v>
+      </c>
+      <c r="M248" s="4">
+        <v>5</v>
+      </c>
       <c r="N248" s="7">
         <v>0</v>
       </c>
-      <c r="O248" s="5"/>
-      <c r="P248" s="5"/>
+      <c r="O248" s="5">
+        <v>2</v>
+      </c>
+      <c r="P248" s="5">
+        <v>1</v>
+      </c>
       <c r="Q248" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R248" s="4"/>
-      <c r="S248" s="4"/>
-      <c r="T248" s="5"/>
-      <c r="U248" s="4"/>
-      <c r="V248" s="5"/>
-      <c r="W248" s="4"/>
-      <c r="X248" s="4"/>
-      <c r="Y248" s="4"/>
-      <c r="Z248" s="5"/>
-      <c r="AA248" s="4"/>
-      <c r="AB248" s="5"/>
-      <c r="AC248" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="R248" s="4">
+        <v>1</v>
+      </c>
+      <c r="S248" s="4">
+        <v>41</v>
+      </c>
+      <c r="T248" s="5">
+        <v>10</v>
+      </c>
+      <c r="U248" s="4">
+        <v>1</v>
+      </c>
+      <c r="V248" s="5">
+        <v>4</v>
+      </c>
+      <c r="W248" s="4">
+        <v>4</v>
+      </c>
+      <c r="X248" s="4">
+        <v>7</v>
+      </c>
+      <c r="Y248" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z248" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA248" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB248" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC248" s="3">
+        <v>3</v>
+      </c>
       <c r="AD248" s="3">
         <v>0</v>
       </c>
@@ -26766,7 +27614,9 @@
       <c r="AF248" s="31">
         <v>0</v>
       </c>
-      <c r="AG248" s="32"/>
+      <c r="AG248" s="32">
+        <v>3</v>
+      </c>
       <c r="AH248" s="6">
         <v>58</v>
       </c>
@@ -26782,14 +27632,18 @@
         <v>33</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E249" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F249" s="3"/>
-      <c r="G249" s="3"/>
+        <v>104</v>
+      </c>
+      <c r="F249" s="3">
+        <v>2</v>
+      </c>
+      <c r="G249" s="3">
+        <v>0</v>
+      </c>
       <c r="H249" s="3">
         <v>0</v>
       </c>
@@ -26798,32 +27652,66 @@
       </c>
       <c r="J249" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K249" s="3"/>
-      <c r="L249" s="3"/>
-      <c r="M249" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="K249" s="3">
+        <v>1</v>
+      </c>
+      <c r="L249" s="3">
+        <v>4</v>
+      </c>
+      <c r="M249" s="4">
+        <v>7</v>
+      </c>
       <c r="N249" s="7">
-        <v>0</v>
-      </c>
-      <c r="O249" s="5"/>
-      <c r="P249" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="O249" s="5">
+        <v>3</v>
+      </c>
+      <c r="P249" s="5">
+        <v>0</v>
+      </c>
       <c r="Q249" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R249" s="4"/>
-      <c r="S249" s="4"/>
-      <c r="T249" s="5"/>
-      <c r="U249" s="4"/>
-      <c r="V249" s="5"/>
-      <c r="W249" s="4"/>
-      <c r="X249" s="4"/>
-      <c r="Y249" s="4"/>
-      <c r="Z249" s="5"/>
-      <c r="AA249" s="4"/>
-      <c r="AB249" s="5"/>
-      <c r="AC249" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="R249" s="4">
+        <v>0</v>
+      </c>
+      <c r="S249" s="4">
+        <v>56</v>
+      </c>
+      <c r="T249" s="5">
+        <v>8</v>
+      </c>
+      <c r="U249" s="4">
+        <v>0</v>
+      </c>
+      <c r="V249" s="5">
+        <v>6</v>
+      </c>
+      <c r="W249" s="4">
+        <v>6</v>
+      </c>
+      <c r="X249" s="4">
+        <v>10</v>
+      </c>
+      <c r="Y249" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z249" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA249" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB249" s="5">
+        <v>3</v>
+      </c>
+      <c r="AC249" s="3">
+        <v>2</v>
+      </c>
       <c r="AD249" s="3">
         <v>0</v>
       </c>
@@ -26833,7 +27721,9 @@
       <c r="AF249" s="31">
         <v>0</v>
       </c>
-      <c r="AG249" s="32"/>
+      <c r="AG249" s="32">
+        <v>3</v>
+      </c>
       <c r="AH249" s="6">
         <v>58</v>
       </c>
@@ -26849,14 +27739,18 @@
         <v>33</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E250" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F250" s="3"/>
-      <c r="G250" s="3"/>
+        <v>79</v>
+      </c>
+      <c r="F250" s="3">
+        <v>0</v>
+      </c>
+      <c r="G250" s="3">
+        <v>2</v>
+      </c>
       <c r="H250" s="3">
         <v>0</v>
       </c>
@@ -26865,32 +27759,66 @@
       </c>
       <c r="J250" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K250" s="3"/>
-      <c r="L250" s="3"/>
-      <c r="M250" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="K250" s="3">
+        <v>1</v>
+      </c>
+      <c r="L250" s="3">
+        <v>5</v>
+      </c>
+      <c r="M250" s="4">
+        <v>7</v>
+      </c>
       <c r="N250" s="7">
         <v>0</v>
       </c>
-      <c r="O250" s="5"/>
-      <c r="P250" s="5"/>
+      <c r="O250" s="5">
+        <v>2</v>
+      </c>
+      <c r="P250" s="5">
+        <v>2</v>
+      </c>
       <c r="Q250" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R250" s="4"/>
-      <c r="S250" s="4"/>
-      <c r="T250" s="5"/>
-      <c r="U250" s="4"/>
-      <c r="V250" s="5"/>
-      <c r="W250" s="4"/>
-      <c r="X250" s="4"/>
-      <c r="Y250" s="4"/>
-      <c r="Z250" s="5"/>
-      <c r="AA250" s="4"/>
-      <c r="AB250" s="5"/>
-      <c r="AC250" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="R250" s="4">
+        <v>3</v>
+      </c>
+      <c r="S250" s="4">
+        <v>38</v>
+      </c>
+      <c r="T250" s="5">
+        <v>7</v>
+      </c>
+      <c r="U250" s="4">
+        <v>0</v>
+      </c>
+      <c r="V250" s="5">
+        <v>2</v>
+      </c>
+      <c r="W250" s="4">
+        <v>5</v>
+      </c>
+      <c r="X250" s="4">
+        <v>5</v>
+      </c>
+      <c r="Y250" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z250" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA250" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB250" s="5">
+        <v>2</v>
+      </c>
+      <c r="AC250" s="3">
+        <v>2</v>
+      </c>
       <c r="AD250" s="3">
         <v>0</v>
       </c>
@@ -26900,30 +27828,36 @@
       <c r="AF250" s="31">
         <v>0</v>
       </c>
-      <c r="AG250" s="32"/>
+      <c r="AG250" s="32">
+        <v>3</v>
+      </c>
       <c r="AH250" s="6">
         <v>58</v>
       </c>
     </row>
     <row r="251" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A251" s="18">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B251" s="28">
-        <v>20260309</v>
+        <v>20260302</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E251" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F251" s="3"/>
-      <c r="G251" s="3"/>
+        <v>142</v>
+      </c>
+      <c r="F251" s="3">
+        <v>0</v>
+      </c>
+      <c r="G251" s="3">
+        <v>3</v>
+      </c>
       <c r="H251" s="3">
         <v>0</v>
       </c>
@@ -26932,32 +27866,66 @@
       </c>
       <c r="J251" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K251" s="3"/>
-      <c r="L251" s="3"/>
-      <c r="M251" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="K251" s="3">
+        <v>3</v>
+      </c>
+      <c r="L251" s="3">
+        <v>8</v>
+      </c>
+      <c r="M251" s="4">
+        <v>7</v>
+      </c>
       <c r="N251" s="7">
         <v>0</v>
       </c>
-      <c r="O251" s="5"/>
-      <c r="P251" s="5"/>
+      <c r="O251" s="5">
+        <v>3</v>
+      </c>
+      <c r="P251" s="5">
+        <v>0</v>
+      </c>
       <c r="Q251" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R251" s="4"/>
-      <c r="S251" s="4"/>
-      <c r="T251" s="5"/>
-      <c r="U251" s="4"/>
-      <c r="V251" s="5"/>
-      <c r="W251" s="4"/>
-      <c r="X251" s="4"/>
-      <c r="Y251" s="4"/>
-      <c r="Z251" s="5"/>
-      <c r="AA251" s="4"/>
-      <c r="AB251" s="5"/>
-      <c r="AC251" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="R251" s="4">
+        <v>2</v>
+      </c>
+      <c r="S251" s="4">
+        <v>85</v>
+      </c>
+      <c r="T251" s="5">
+        <v>18</v>
+      </c>
+      <c r="U251" s="4">
+        <v>5</v>
+      </c>
+      <c r="V251" s="5">
+        <v>4</v>
+      </c>
+      <c r="W251" s="4">
+        <v>4</v>
+      </c>
+      <c r="X251" s="4">
+        <v>10</v>
+      </c>
+      <c r="Y251" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z251" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA251" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB251" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC251" s="3">
+        <v>1</v>
+      </c>
       <c r="AD251" s="3">
         <v>0</v>
       </c>
@@ -26967,9 +27935,11 @@
       <c r="AF251" s="31">
         <v>0</v>
       </c>
-      <c r="AG251" s="32"/>
+      <c r="AG251" s="32">
+        <v>3</v>
+      </c>
       <c r="AH251" s="6">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="252" spans="1:34" x14ac:dyDescent="0.25">
@@ -26983,14 +27953,18 @@
         <v>32</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E252" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F252" s="3"/>
-      <c r="G252" s="3"/>
+        <v>90</v>
+      </c>
+      <c r="F252" s="3">
+        <v>0</v>
+      </c>
+      <c r="G252" s="3">
+        <v>2</v>
+      </c>
       <c r="H252" s="3">
         <v>0</v>
       </c>
@@ -26999,32 +27973,66 @@
       </c>
       <c r="J252" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K252" s="3"/>
-      <c r="L252" s="3"/>
-      <c r="M252" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="K252" s="3">
+        <v>0</v>
+      </c>
+      <c r="L252" s="3">
+        <v>1</v>
+      </c>
+      <c r="M252" s="4">
+        <v>4</v>
+      </c>
       <c r="N252" s="7">
         <v>0</v>
       </c>
-      <c r="O252" s="5"/>
-      <c r="P252" s="5"/>
+      <c r="O252" s="5">
+        <v>4</v>
+      </c>
+      <c r="P252" s="5">
+        <v>6</v>
+      </c>
       <c r="Q252" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R252" s="4"/>
-      <c r="S252" s="4"/>
-      <c r="T252" s="5"/>
-      <c r="U252" s="4"/>
-      <c r="V252" s="5"/>
-      <c r="W252" s="4"/>
-      <c r="X252" s="4"/>
-      <c r="Y252" s="4"/>
-      <c r="Z252" s="5"/>
-      <c r="AA252" s="4"/>
-      <c r="AB252" s="5"/>
-      <c r="AC252" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="R252" s="4">
+        <v>0</v>
+      </c>
+      <c r="S252" s="4">
+        <v>43</v>
+      </c>
+      <c r="T252" s="5">
+        <v>6</v>
+      </c>
+      <c r="U252" s="4">
+        <v>3</v>
+      </c>
+      <c r="V252" s="5">
+        <v>2</v>
+      </c>
+      <c r="W252" s="4">
+        <v>2</v>
+      </c>
+      <c r="X252" s="4">
+        <v>13</v>
+      </c>
+      <c r="Y252" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z252" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA252" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB252" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC252" s="3">
+        <v>1</v>
+      </c>
       <c r="AD252" s="3">
         <v>0</v>
       </c>
@@ -27050,14 +28058,18 @@
         <v>32</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="E253" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F253" s="3"/>
-      <c r="G253" s="3"/>
+        <v>117</v>
+      </c>
+      <c r="F253" s="3">
+        <v>0</v>
+      </c>
+      <c r="G253" s="3">
+        <v>0</v>
+      </c>
       <c r="H253" s="3">
         <v>0</v>
       </c>
@@ -27068,30 +28080,64 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K253" s="3"/>
-      <c r="L253" s="3"/>
-      <c r="M253" s="4"/>
+      <c r="K253" s="3">
+        <v>1</v>
+      </c>
+      <c r="L253" s="3">
+        <v>2</v>
+      </c>
+      <c r="M253" s="4">
+        <v>3</v>
+      </c>
       <c r="N253" s="7">
-        <v>0</v>
-      </c>
-      <c r="O253" s="5"/>
-      <c r="P253" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="O253" s="5">
+        <v>3</v>
+      </c>
+      <c r="P253" s="5">
+        <v>1</v>
+      </c>
       <c r="Q253" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R253" s="4"/>
-      <c r="S253" s="4"/>
-      <c r="T253" s="5"/>
-      <c r="U253" s="4"/>
-      <c r="V253" s="5"/>
-      <c r="W253" s="4"/>
-      <c r="X253" s="4"/>
-      <c r="Y253" s="4"/>
-      <c r="Z253" s="5"/>
-      <c r="AA253" s="4"/>
-      <c r="AB253" s="5"/>
-      <c r="AC253" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="R253" s="4">
+        <v>1</v>
+      </c>
+      <c r="S253" s="4">
+        <v>59</v>
+      </c>
+      <c r="T253" s="5">
+        <v>10</v>
+      </c>
+      <c r="U253" s="4">
+        <v>9</v>
+      </c>
+      <c r="V253" s="5">
+        <v>7</v>
+      </c>
+      <c r="W253" s="4">
+        <v>5</v>
+      </c>
+      <c r="X253" s="4">
+        <v>11</v>
+      </c>
+      <c r="Y253" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z253" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA253" s="4">
+        <v>3</v>
+      </c>
+      <c r="AB253" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC253" s="3">
+        <v>3</v>
+      </c>
       <c r="AD253" s="3">
         <v>0</v>
       </c>
@@ -27117,14 +28163,18 @@
         <v>32</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="E254" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F254" s="3"/>
-      <c r="G254" s="3"/>
+        <v>62</v>
+      </c>
+      <c r="F254" s="3">
+        <v>0</v>
+      </c>
+      <c r="G254" s="3">
+        <v>0</v>
+      </c>
       <c r="H254" s="3">
         <v>0</v>
       </c>
@@ -27135,30 +28185,64 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K254" s="3"/>
-      <c r="L254" s="3"/>
-      <c r="M254" s="4"/>
+      <c r="K254" s="3">
+        <v>0</v>
+      </c>
+      <c r="L254" s="3">
+        <v>0</v>
+      </c>
+      <c r="M254" s="4">
+        <v>1</v>
+      </c>
       <c r="N254" s="7">
         <v>0</v>
       </c>
-      <c r="O254" s="5"/>
-      <c r="P254" s="5"/>
+      <c r="O254" s="5">
+        <v>3</v>
+      </c>
+      <c r="P254" s="5">
+        <v>0</v>
+      </c>
       <c r="Q254" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R254" s="4"/>
-      <c r="S254" s="4"/>
-      <c r="T254" s="5"/>
-      <c r="U254" s="4"/>
-      <c r="V254" s="5"/>
-      <c r="W254" s="4"/>
-      <c r="X254" s="4"/>
-      <c r="Y254" s="4"/>
-      <c r="Z254" s="5"/>
-      <c r="AA254" s="4"/>
-      <c r="AB254" s="5"/>
-      <c r="AC254" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="R254" s="4">
+        <v>0</v>
+      </c>
+      <c r="S254" s="4">
+        <v>24</v>
+      </c>
+      <c r="T254" s="5">
+        <v>12</v>
+      </c>
+      <c r="U254" s="4">
+        <v>0</v>
+      </c>
+      <c r="V254" s="5">
+        <v>4</v>
+      </c>
+      <c r="W254" s="4">
+        <v>1</v>
+      </c>
+      <c r="X254" s="4">
+        <v>9</v>
+      </c>
+      <c r="Y254" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z254" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA254" s="4">
+        <v>4</v>
+      </c>
+      <c r="AB254" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC254" s="3">
+        <v>4</v>
+      </c>
       <c r="AD254" s="3">
         <v>0</v>
       </c>
@@ -27184,14 +28268,18 @@
         <v>32</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E255" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F255" s="3"/>
-      <c r="G255" s="3"/>
+        <v>118</v>
+      </c>
+      <c r="F255" s="3">
+        <v>0</v>
+      </c>
+      <c r="G255" s="3">
+        <v>1</v>
+      </c>
       <c r="H255" s="3">
         <v>0</v>
       </c>
@@ -27200,32 +28288,66 @@
       </c>
       <c r="J255" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K255" s="3"/>
-      <c r="L255" s="3"/>
-      <c r="M255" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K255" s="3">
+        <v>2</v>
+      </c>
+      <c r="L255" s="3">
+        <v>4</v>
+      </c>
+      <c r="M255" s="4">
+        <v>7</v>
+      </c>
       <c r="N255" s="7">
         <v>0</v>
       </c>
-      <c r="O255" s="5"/>
-      <c r="P255" s="5"/>
+      <c r="O255" s="5">
+        <v>2</v>
+      </c>
+      <c r="P255" s="5">
+        <v>1</v>
+      </c>
       <c r="Q255" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R255" s="4"/>
-      <c r="S255" s="4"/>
-      <c r="T255" s="5"/>
-      <c r="U255" s="4"/>
-      <c r="V255" s="5"/>
-      <c r="W255" s="4"/>
-      <c r="X255" s="4"/>
-      <c r="Y255" s="4"/>
-      <c r="Z255" s="5"/>
-      <c r="AA255" s="4"/>
-      <c r="AB255" s="5"/>
-      <c r="AC255" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="R255" s="4">
+        <v>0</v>
+      </c>
+      <c r="S255" s="4">
+        <v>65</v>
+      </c>
+      <c r="T255" s="5">
+        <v>17</v>
+      </c>
+      <c r="U255" s="4">
+        <v>5</v>
+      </c>
+      <c r="V255" s="5">
+        <v>3</v>
+      </c>
+      <c r="W255" s="4">
+        <v>5</v>
+      </c>
+      <c r="X255" s="4">
+        <v>5</v>
+      </c>
+      <c r="Y255" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z255" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA255" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB255" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC255" s="3">
+        <v>7</v>
+      </c>
       <c r="AD255" s="3">
         <v>0</v>
       </c>
@@ -27251,14 +28373,18 @@
         <v>32</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E256" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F256" s="3"/>
-      <c r="G256" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="F256" s="3">
+        <v>0</v>
+      </c>
+      <c r="G256" s="3">
+        <v>1</v>
+      </c>
       <c r="H256" s="3">
         <v>0</v>
       </c>
@@ -27267,32 +28393,66 @@
       </c>
       <c r="J256" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K256" s="3"/>
-      <c r="L256" s="3"/>
-      <c r="M256" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K256" s="3">
+        <v>0</v>
+      </c>
+      <c r="L256" s="3">
+        <v>0</v>
+      </c>
+      <c r="M256" s="4">
+        <v>3</v>
+      </c>
       <c r="N256" s="7">
         <v>0</v>
       </c>
-      <c r="O256" s="5"/>
-      <c r="P256" s="5"/>
+      <c r="O256" s="5">
+        <v>5</v>
+      </c>
+      <c r="P256" s="5">
+        <v>3</v>
+      </c>
       <c r="Q256" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R256" s="4"/>
-      <c r="S256" s="4"/>
-      <c r="T256" s="5"/>
-      <c r="U256" s="4"/>
-      <c r="V256" s="5"/>
-      <c r="W256" s="4"/>
-      <c r="X256" s="4"/>
-      <c r="Y256" s="4"/>
-      <c r="Z256" s="5"/>
-      <c r="AA256" s="4"/>
-      <c r="AB256" s="5"/>
-      <c r="AC256" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="R256" s="4">
+        <v>1</v>
+      </c>
+      <c r="S256" s="4">
+        <v>32</v>
+      </c>
+      <c r="T256" s="5">
+        <v>8</v>
+      </c>
+      <c r="U256" s="4">
+        <v>1</v>
+      </c>
+      <c r="V256" s="5">
+        <v>6</v>
+      </c>
+      <c r="W256" s="4">
+        <v>0</v>
+      </c>
+      <c r="X256" s="4">
+        <v>16</v>
+      </c>
+      <c r="Y256" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z256" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA256" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB256" s="5">
+        <v>2</v>
+      </c>
+      <c r="AC256" s="3">
+        <v>1</v>
+      </c>
       <c r="AD256" s="3">
         <v>0</v>
       </c>
@@ -27315,17 +28475,21 @@
         <v>20260309</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E257" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F257" s="3"/>
-      <c r="G257" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="F257" s="3">
+        <v>0</v>
+      </c>
+      <c r="G257" s="3">
+        <v>1</v>
+      </c>
       <c r="H257" s="3">
         <v>0</v>
       </c>
@@ -27334,32 +28498,66 @@
       </c>
       <c r="J257" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K257" s="3"/>
-      <c r="L257" s="3"/>
-      <c r="M257" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K257" s="3">
+        <v>1</v>
+      </c>
+      <c r="L257" s="3">
+        <v>4</v>
+      </c>
+      <c r="M257" s="4">
+        <v>3</v>
+      </c>
       <c r="N257" s="7">
         <v>0</v>
       </c>
-      <c r="O257" s="5"/>
-      <c r="P257" s="5"/>
+      <c r="O257" s="5">
+        <v>3</v>
+      </c>
+      <c r="P257" s="5">
+        <v>0</v>
+      </c>
       <c r="Q257" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R257" s="4"/>
-      <c r="S257" s="4"/>
-      <c r="T257" s="5"/>
-      <c r="U257" s="4"/>
-      <c r="V257" s="5"/>
-      <c r="W257" s="4"/>
-      <c r="X257" s="4"/>
-      <c r="Y257" s="4"/>
-      <c r="Z257" s="5"/>
-      <c r="AA257" s="4"/>
-      <c r="AB257" s="5"/>
-      <c r="AC257" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="R257" s="4">
+        <v>1</v>
+      </c>
+      <c r="S257" s="4">
+        <v>33</v>
+      </c>
+      <c r="T257" s="5">
+        <v>14</v>
+      </c>
+      <c r="U257" s="4">
+        <v>2</v>
+      </c>
+      <c r="V257" s="5">
+        <v>1</v>
+      </c>
+      <c r="W257" s="4">
+        <v>1</v>
+      </c>
+      <c r="X257" s="4">
+        <v>5</v>
+      </c>
+      <c r="Y257" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z257" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA257" s="4">
+        <v>3</v>
+      </c>
+      <c r="AB257" s="5">
+        <v>2</v>
+      </c>
+      <c r="AC257" s="3">
+        <v>4</v>
+      </c>
       <c r="AD257" s="3">
         <v>0</v>
       </c>
@@ -27385,14 +28583,18 @@
         <v>33</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E258" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F258" s="3"/>
-      <c r="G258" s="3"/>
+        <v>108</v>
+      </c>
+      <c r="F258" s="3">
+        <v>0</v>
+      </c>
+      <c r="G258" s="3">
+        <v>1</v>
+      </c>
       <c r="H258" s="3">
         <v>0</v>
       </c>
@@ -27401,32 +28603,66 @@
       </c>
       <c r="J258" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K258" s="3"/>
-      <c r="L258" s="3"/>
-      <c r="M258" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K258" s="3">
+        <v>1</v>
+      </c>
+      <c r="L258" s="3">
+        <v>1</v>
+      </c>
+      <c r="M258" s="4">
+        <v>5</v>
+      </c>
       <c r="N258" s="7">
         <v>0</v>
       </c>
-      <c r="O258" s="5"/>
-      <c r="P258" s="5"/>
+      <c r="O258" s="5">
+        <v>3</v>
+      </c>
+      <c r="P258" s="5">
+        <v>0</v>
+      </c>
       <c r="Q258" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R258" s="4"/>
-      <c r="S258" s="4"/>
-      <c r="T258" s="5"/>
-      <c r="U258" s="4"/>
-      <c r="V258" s="5"/>
-      <c r="W258" s="4"/>
-      <c r="X258" s="4"/>
-      <c r="Y258" s="4"/>
-      <c r="Z258" s="5"/>
-      <c r="AA258" s="4"/>
-      <c r="AB258" s="5"/>
-      <c r="AC258" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="R258" s="4">
+        <v>3</v>
+      </c>
+      <c r="S258" s="4">
+        <v>48</v>
+      </c>
+      <c r="T258" s="5">
+        <v>14</v>
+      </c>
+      <c r="U258" s="4">
+        <v>4</v>
+      </c>
+      <c r="V258" s="5">
+        <v>2</v>
+      </c>
+      <c r="W258" s="4">
+        <v>6</v>
+      </c>
+      <c r="X258" s="4">
+        <v>18</v>
+      </c>
+      <c r="Y258" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z258" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA258" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB258" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC258" s="3">
+        <v>1</v>
+      </c>
       <c r="AD258" s="3">
         <v>0</v>
       </c>
@@ -27452,14 +28688,18 @@
         <v>33</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E259" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F259" s="3"/>
-      <c r="G259" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="F259" s="3">
+        <v>1</v>
+      </c>
+      <c r="G259" s="3">
+        <v>0</v>
+      </c>
       <c r="H259" s="3">
         <v>0</v>
       </c>
@@ -27468,32 +28708,66 @@
       </c>
       <c r="J259" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K259" s="3"/>
-      <c r="L259" s="3"/>
-      <c r="M259" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K259" s="3">
+        <v>1</v>
+      </c>
+      <c r="L259" s="3">
+        <v>0</v>
+      </c>
+      <c r="M259" s="4">
+        <v>3</v>
+      </c>
       <c r="N259" s="7">
         <v>0</v>
       </c>
-      <c r="O259" s="5"/>
-      <c r="P259" s="5"/>
+      <c r="O259" s="5">
+        <v>0</v>
+      </c>
+      <c r="P259" s="5">
+        <v>0</v>
+      </c>
       <c r="Q259" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R259" s="4"/>
-      <c r="S259" s="4"/>
-      <c r="T259" s="5"/>
-      <c r="U259" s="4"/>
-      <c r="V259" s="5"/>
-      <c r="W259" s="4"/>
-      <c r="X259" s="4"/>
-      <c r="Y259" s="4"/>
-      <c r="Z259" s="5"/>
-      <c r="AA259" s="4"/>
-      <c r="AB259" s="5"/>
-      <c r="AC259" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="R259" s="4">
+        <v>1</v>
+      </c>
+      <c r="S259" s="4">
+        <v>29</v>
+      </c>
+      <c r="T259" s="5">
+        <v>8</v>
+      </c>
+      <c r="U259" s="4">
+        <v>2</v>
+      </c>
+      <c r="V259" s="5">
+        <v>2</v>
+      </c>
+      <c r="W259" s="4">
+        <v>7</v>
+      </c>
+      <c r="X259" s="4">
+        <v>13</v>
+      </c>
+      <c r="Y259" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z259" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA259" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB259" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC259" s="3">
+        <v>1</v>
+      </c>
       <c r="AD259" s="3">
         <v>0</v>
       </c>
@@ -27519,14 +28793,18 @@
         <v>33</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="E260" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F260" s="3"/>
-      <c r="G260" s="3"/>
+        <v>111</v>
+      </c>
+      <c r="F260" s="3">
+        <v>0</v>
+      </c>
+      <c r="G260" s="3">
+        <v>0</v>
+      </c>
       <c r="H260" s="3">
         <v>0</v>
       </c>
@@ -27537,30 +28815,64 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K260" s="3"/>
-      <c r="L260" s="3"/>
-      <c r="M260" s="4"/>
+      <c r="K260" s="3">
+        <v>1</v>
+      </c>
+      <c r="L260" s="3">
+        <v>4</v>
+      </c>
+      <c r="M260" s="4">
+        <v>1</v>
+      </c>
       <c r="N260" s="7">
         <v>0</v>
       </c>
-      <c r="O260" s="5"/>
-      <c r="P260" s="5"/>
+      <c r="O260" s="5">
+        <v>4</v>
+      </c>
+      <c r="P260" s="5">
+        <v>1</v>
+      </c>
       <c r="Q260" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R260" s="4"/>
-      <c r="S260" s="4"/>
-      <c r="T260" s="5"/>
-      <c r="U260" s="4"/>
-      <c r="V260" s="5"/>
-      <c r="W260" s="4"/>
-      <c r="X260" s="4"/>
-      <c r="Y260" s="4"/>
-      <c r="Z260" s="5"/>
-      <c r="AA260" s="4"/>
-      <c r="AB260" s="5"/>
-      <c r="AC260" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="R260" s="4">
+        <v>1</v>
+      </c>
+      <c r="S260" s="4">
+        <v>58</v>
+      </c>
+      <c r="T260" s="5">
+        <v>19</v>
+      </c>
+      <c r="U260" s="4">
+        <v>1</v>
+      </c>
+      <c r="V260" s="5">
+        <v>3</v>
+      </c>
+      <c r="W260" s="4">
+        <v>3</v>
+      </c>
+      <c r="X260" s="4">
+        <v>12</v>
+      </c>
+      <c r="Y260" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z260" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA260" s="4">
+        <v>5</v>
+      </c>
+      <c r="AB260" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC260" s="3">
+        <v>1</v>
+      </c>
       <c r="AD260" s="3">
         <v>0</v>
       </c>
@@ -27586,14 +28898,18 @@
         <v>33</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E261" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F261" s="3"/>
-      <c r="G261" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="F261" s="3">
+        <v>0</v>
+      </c>
+      <c r="G261" s="3">
+        <v>1</v>
+      </c>
       <c r="H261" s="3">
         <v>0</v>
       </c>
@@ -27602,32 +28918,66 @@
       </c>
       <c r="J261" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K261" s="3"/>
-      <c r="L261" s="3"/>
-      <c r="M261" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K261" s="3">
+        <v>0</v>
+      </c>
+      <c r="L261" s="3">
+        <v>2</v>
+      </c>
+      <c r="M261" s="4">
+        <v>3</v>
+      </c>
       <c r="N261" s="7">
         <v>0</v>
       </c>
-      <c r="O261" s="5"/>
-      <c r="P261" s="5"/>
+      <c r="O261" s="5">
+        <v>1</v>
+      </c>
+      <c r="P261" s="5">
+        <v>1</v>
+      </c>
       <c r="Q261" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R261" s="4"/>
-      <c r="S261" s="4"/>
-      <c r="T261" s="5"/>
-      <c r="U261" s="4"/>
-      <c r="V261" s="5"/>
-      <c r="W261" s="4"/>
-      <c r="X261" s="4"/>
-      <c r="Y261" s="4"/>
-      <c r="Z261" s="5"/>
-      <c r="AA261" s="4"/>
-      <c r="AB261" s="5"/>
-      <c r="AC261" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="R261" s="4">
+        <v>0</v>
+      </c>
+      <c r="S261" s="4">
+        <v>36</v>
+      </c>
+      <c r="T261" s="5">
+        <v>13</v>
+      </c>
+      <c r="U261" s="4">
+        <v>3</v>
+      </c>
+      <c r="V261" s="5">
+        <v>5</v>
+      </c>
+      <c r="W261" s="4">
+        <v>2</v>
+      </c>
+      <c r="X261" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y261" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z261" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA261" s="4">
+        <v>4</v>
+      </c>
+      <c r="AB261" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC261" s="3">
+        <v>0</v>
+      </c>
       <c r="AD261" s="3">
         <v>0</v>
       </c>
@@ -27653,14 +29003,18 @@
         <v>33</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E262" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F262" s="3"/>
-      <c r="G262" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="F262" s="3">
+        <v>0</v>
+      </c>
+      <c r="G262" s="3">
+        <v>0</v>
+      </c>
       <c r="H262" s="3">
         <v>0</v>
       </c>
@@ -27671,30 +29025,64 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K262" s="3"/>
-      <c r="L262" s="3"/>
-      <c r="M262" s="4"/>
+      <c r="K262" s="3">
+        <v>1</v>
+      </c>
+      <c r="L262" s="3">
+        <v>5</v>
+      </c>
+      <c r="M262" s="4">
+        <v>0</v>
+      </c>
       <c r="N262" s="7">
         <v>0</v>
       </c>
-      <c r="O262" s="5"/>
-      <c r="P262" s="5"/>
+      <c r="O262" s="5">
+        <v>2</v>
+      </c>
+      <c r="P262" s="5">
+        <v>0</v>
+      </c>
       <c r="Q262" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R262" s="4"/>
-      <c r="S262" s="4"/>
-      <c r="T262" s="5"/>
-      <c r="U262" s="4"/>
-      <c r="V262" s="5"/>
-      <c r="W262" s="4"/>
-      <c r="X262" s="4"/>
-      <c r="Y262" s="4"/>
-      <c r="Z262" s="5"/>
-      <c r="AA262" s="4"/>
-      <c r="AB262" s="5"/>
-      <c r="AC262" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="R262" s="4">
+        <v>5</v>
+      </c>
+      <c r="S262" s="4">
+        <v>24</v>
+      </c>
+      <c r="T262" s="5">
+        <v>11</v>
+      </c>
+      <c r="U262" s="4">
+        <v>0</v>
+      </c>
+      <c r="V262" s="5">
+        <v>1</v>
+      </c>
+      <c r="W262" s="4">
+        <v>3</v>
+      </c>
+      <c r="X262" s="4">
+        <v>6</v>
+      </c>
+      <c r="Y262" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z262" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA262" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB262" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC262" s="3">
+        <v>1</v>
+      </c>
       <c r="AD262" s="3">
         <v>0</v>
       </c>
@@ -27711,23 +29099,27 @@
     </row>
     <row r="263" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A263" s="18">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B263" s="28">
-        <v>20260316</v>
+        <v>20260309</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E263" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F263" s="3"/>
-      <c r="G263" s="3"/>
+        <v>87</v>
+      </c>
+      <c r="F263" s="3">
+        <v>0</v>
+      </c>
+      <c r="G263" s="3">
+        <v>0</v>
+      </c>
       <c r="H263" s="3">
         <v>0</v>
       </c>
@@ -27738,30 +29130,64 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K263" s="3"/>
-      <c r="L263" s="3"/>
-      <c r="M263" s="4"/>
+      <c r="K263" s="3">
+        <v>1</v>
+      </c>
+      <c r="L263" s="3">
+        <v>2</v>
+      </c>
+      <c r="M263" s="4">
+        <v>7</v>
+      </c>
       <c r="N263" s="7">
         <v>0</v>
       </c>
-      <c r="O263" s="5"/>
-      <c r="P263" s="5"/>
+      <c r="O263" s="5">
+        <v>4</v>
+      </c>
+      <c r="P263" s="5">
+        <v>1</v>
+      </c>
       <c r="Q263" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R263" s="4"/>
-      <c r="S263" s="4"/>
-      <c r="T263" s="5"/>
-      <c r="U263" s="4"/>
-      <c r="V263" s="5"/>
-      <c r="W263" s="4"/>
-      <c r="X263" s="4"/>
-      <c r="Y263" s="4"/>
-      <c r="Z263" s="5"/>
-      <c r="AA263" s="4"/>
-      <c r="AB263" s="5"/>
-      <c r="AC263" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="R263" s="4">
+        <v>1</v>
+      </c>
+      <c r="S263" s="4">
+        <v>45</v>
+      </c>
+      <c r="T263" s="5">
+        <v>9</v>
+      </c>
+      <c r="U263" s="4">
+        <v>1</v>
+      </c>
+      <c r="V263" s="5">
+        <v>2</v>
+      </c>
+      <c r="W263" s="4">
+        <v>2</v>
+      </c>
+      <c r="X263" s="4">
+        <v>8</v>
+      </c>
+      <c r="Y263" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z263" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA263" s="4">
+        <v>4</v>
+      </c>
+      <c r="AB263" s="5">
+        <v>2</v>
+      </c>
+      <c r="AC263" s="3">
+        <v>0</v>
+      </c>
       <c r="AD263" s="3">
         <v>0</v>
       </c>
@@ -27773,7 +29199,7 @@
       </c>
       <c r="AG263" s="32"/>
       <c r="AH263" s="6">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="264" spans="1:34" x14ac:dyDescent="0.25">
@@ -27787,7 +29213,7 @@
         <v>32</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E264" s="3">
         <f t="shared" si="15"/>
@@ -27854,7 +29280,7 @@
         <v>32</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E265" s="3">
         <f t="shared" si="15"/>
@@ -27921,7 +29347,7 @@
         <v>32</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E266" s="3">
         <f t="shared" si="15"/>
@@ -27988,7 +29414,7 @@
         <v>32</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E267" s="3">
         <f t="shared" si="15"/>
@@ -28055,7 +29481,7 @@
         <v>32</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E268" s="3">
         <f t="shared" si="15"/>
@@ -28119,10 +29545,10 @@
         <v>20260316</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E269" s="3">
         <f t="shared" si="15"/>
@@ -28189,7 +29615,7 @@
         <v>33</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E270" s="3">
         <f t="shared" si="15"/>
@@ -28256,7 +29682,7 @@
         <v>33</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E271" s="3">
         <f t="shared" si="15"/>
@@ -28323,7 +29749,7 @@
         <v>33</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E272" s="3">
         <f t="shared" si="15"/>
@@ -28390,7 +29816,7 @@
         <v>33</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E273" s="3">
         <f t="shared" si="15"/>
@@ -28457,7 +29883,7 @@
         <v>33</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E274" s="3">
         <f t="shared" si="15"/>
@@ -28515,19 +29941,19 @@
     </row>
     <row r="275" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A275" s="18">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B275" s="28">
-        <v>20260323</v>
+        <v>20260316</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E275" s="3">
-        <f t="shared" ref="E275:E338" si="18">SUM(F275:AF275)-SUM(F275:L275,Q275)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F275" s="3"/>
@@ -28591,10 +30017,10 @@
         <v>32</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E276" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="E276:E339" si="18">SUM(F276:AF276)-SUM(F276:L276,Q276)</f>
         <v>0</v>
       </c>
       <c r="F276" s="3"/>
@@ -28658,7 +30084,7 @@
         <v>32</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E277" s="3">
         <f t="shared" si="18"/>
@@ -28725,7 +30151,7 @@
         <v>32</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E278" s="3">
         <f t="shared" si="18"/>
@@ -28740,7 +30166,7 @@
         <v>0</v>
       </c>
       <c r="J278" s="3">
-        <f t="shared" ref="J278:J367" si="19">SUM(F278:I278)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K278" s="3"/>
@@ -28792,7 +30218,7 @@
         <v>32</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E279" s="3">
         <f t="shared" si="18"/>
@@ -28807,7 +30233,7 @@
         <v>0</v>
       </c>
       <c r="J279" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="J279:J368" si="19">SUM(F279:I279)</f>
         <v>0</v>
       </c>
       <c r="K279" s="3"/>
@@ -28819,7 +30245,7 @@
       <c r="O279" s="5"/>
       <c r="P279" s="5"/>
       <c r="Q279" s="36">
-        <f t="shared" ref="Q279:Q368" si="20">SUM(M279:P279)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="R279" s="4"/>
@@ -28859,7 +30285,7 @@
         <v>32</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E280" s="3">
         <f t="shared" si="18"/>
@@ -28886,7 +30312,7 @@
       <c r="O280" s="5"/>
       <c r="P280" s="5"/>
       <c r="Q280" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="Q280:Q369" si="20">SUM(M280:P280)</f>
         <v>0</v>
       </c>
       <c r="R280" s="4"/>
@@ -28923,10 +30349,10 @@
         <v>20260323</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E281" s="3">
         <f t="shared" si="18"/>
@@ -28945,6 +30371,7 @@
         <v>0</v>
       </c>
       <c r="K281" s="3"/>
+      <c r="L281" s="3"/>
       <c r="M281" s="4"/>
       <c r="N281" s="7">
         <v>0</v>
@@ -28992,7 +30419,7 @@
         <v>33</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E282" s="3">
         <f t="shared" si="18"/>
@@ -29011,7 +30438,6 @@
         <v>0</v>
       </c>
       <c r="K282" s="3"/>
-      <c r="L282" s="3"/>
       <c r="M282" s="4"/>
       <c r="N282" s="7">
         <v>0</v>
@@ -29059,7 +30485,7 @@
         <v>33</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E283" s="3">
         <f t="shared" si="18"/>
@@ -29126,7 +30552,7 @@
         <v>33</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E284" s="3">
         <f t="shared" si="18"/>
@@ -29193,7 +30619,7 @@
         <v>33</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="E285" s="3">
         <f t="shared" si="18"/>
@@ -29260,7 +30686,7 @@
         <v>33</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E286" s="3">
         <f t="shared" si="18"/>
@@ -29318,16 +30744,16 @@
     </row>
     <row r="287" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A287" s="18">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B287" s="28">
-        <v>20260330</v>
+        <v>20260323</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E287" s="3">
         <f t="shared" si="18"/>
@@ -29380,7 +30806,7 @@
       </c>
       <c r="AG287" s="32"/>
       <c r="AH287" s="6">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="288" spans="1:34" x14ac:dyDescent="0.25">
@@ -29393,8 +30819,8 @@
       <c r="C288" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D288" s="1" t="s">
-        <v>39</v>
+      <c r="D288" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="E288" s="3">
         <f t="shared" si="18"/>
@@ -29460,8 +30886,8 @@
       <c r="C289" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D289" s="3" t="s">
-        <v>36</v>
+      <c r="D289" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="E289" s="3">
         <f t="shared" si="18"/>
@@ -29528,7 +30954,7 @@
         <v>32</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E290" s="3">
         <f t="shared" si="18"/>
@@ -29595,7 +31021,7 @@
         <v>32</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E291" s="3">
         <f t="shared" si="18"/>
@@ -29662,7 +31088,7 @@
         <v>32</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E292" s="3">
         <f t="shared" si="18"/>
@@ -29726,10 +31152,10 @@
         <v>20260330</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E293" s="3">
         <f t="shared" si="18"/>
@@ -29796,7 +31222,7 @@
         <v>33</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E294" s="3">
         <f t="shared" si="18"/>
@@ -29862,8 +31288,8 @@
       <c r="C295" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D295" s="1" t="s">
-        <v>50</v>
+      <c r="D295" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="E295" s="3">
         <f t="shared" si="18"/>
@@ -29929,8 +31355,8 @@
       <c r="C296" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D296" s="3" t="s">
-        <v>57</v>
+      <c r="D296" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="E296" s="3">
         <f t="shared" si="18"/>
@@ -29997,7 +31423,7 @@
         <v>33</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E297" s="3">
         <f t="shared" si="18"/>
@@ -30064,7 +31490,7 @@
         <v>33</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E298" s="3">
         <f t="shared" si="18"/>
@@ -30122,16 +31548,16 @@
     </row>
     <row r="299" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A299" s="18">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B299" s="28">
-        <v>20260406</v>
+        <v>20260330</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E299" s="3">
         <f t="shared" si="18"/>
@@ -30184,7 +31610,7 @@
       </c>
       <c r="AG299" s="32"/>
       <c r="AH299" s="6">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="300" spans="1:34" x14ac:dyDescent="0.25">
@@ -30198,7 +31624,7 @@
         <v>32</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E300" s="3">
         <f t="shared" si="18"/>
@@ -30265,7 +31691,7 @@
         <v>32</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E301" s="3">
         <f t="shared" si="18"/>
@@ -30331,8 +31757,8 @@
       <c r="C302" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D302" s="1" t="s">
-        <v>43</v>
+      <c r="D302" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="E302" s="3">
         <f t="shared" si="18"/>
@@ -30398,8 +31824,8 @@
       <c r="C303" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D303" s="3" t="s">
-        <v>36</v>
+      <c r="D303" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E303" s="3">
         <f t="shared" si="18"/>
@@ -30466,7 +31892,7 @@
         <v>32</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E304" s="3">
         <f t="shared" si="18"/>
@@ -30530,10 +31956,10 @@
         <v>20260406</v>
       </c>
       <c r="C305" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E305" s="3">
         <f t="shared" si="18"/>
@@ -30600,7 +32026,7 @@
         <v>33</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E306" s="3">
         <f t="shared" si="18"/>
@@ -30667,7 +32093,7 @@
         <v>33</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E307" s="3">
         <f t="shared" si="18"/>
@@ -30734,7 +32160,7 @@
         <v>33</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E308" s="3">
         <f t="shared" si="18"/>
@@ -30800,8 +32226,8 @@
       <c r="C309" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D309" s="1" t="s">
-        <v>39</v>
+      <c r="D309" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="E309" s="3">
         <f t="shared" si="18"/>
@@ -30867,8 +32293,8 @@
       <c r="C310" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D310" s="3" t="s">
-        <v>41</v>
+      <c r="D310" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="E310" s="3">
         <f t="shared" si="18"/>
@@ -30926,16 +32352,16 @@
     </row>
     <row r="311" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A311" s="18">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B311" s="28">
-        <v>20260420</v>
+        <v>20260406</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E311" s="3">
         <f t="shared" si="18"/>
@@ -30988,7 +32414,7 @@
       </c>
       <c r="AG311" s="32"/>
       <c r="AH311" s="6">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="312" spans="1:34" x14ac:dyDescent="0.25">
@@ -31002,7 +32428,7 @@
         <v>32</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E312" s="3">
         <f t="shared" si="18"/>
@@ -31069,7 +32495,7 @@
         <v>32</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E313" s="3">
         <f t="shared" si="18"/>
@@ -31136,7 +32562,7 @@
         <v>32</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E314" s="3">
         <f t="shared" si="18"/>
@@ -31203,7 +32629,7 @@
         <v>32</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E315" s="3">
         <f t="shared" si="18"/>
@@ -31269,8 +32695,8 @@
       <c r="C316" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D316" s="1" t="s">
-        <v>50</v>
+      <c r="D316" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="E316" s="3">
         <f t="shared" si="18"/>
@@ -31334,10 +32760,10 @@
         <v>20260420</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D317" s="3" t="s">
-        <v>41</v>
+        <v>32</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="E317" s="3">
         <f t="shared" si="18"/>
@@ -31404,7 +32830,7 @@
         <v>33</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="E318" s="3">
         <f t="shared" si="18"/>
@@ -31471,7 +32897,7 @@
         <v>33</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="E319" s="3">
         <f t="shared" si="18"/>
@@ -31538,7 +32964,7 @@
         <v>33</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="E320" s="3">
         <f t="shared" si="18"/>
@@ -31605,7 +33031,7 @@
         <v>33</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E321" s="3">
         <f t="shared" si="18"/>
@@ -31672,7 +33098,7 @@
         <v>33</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E322" s="3">
         <f t="shared" si="18"/>
@@ -31730,16 +33156,16 @@
     </row>
     <row r="323" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A323" s="18">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B323" s="28">
-        <v>20260427</v>
+        <v>20260420</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D323" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
+      </c>
+      <c r="D323" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E323" s="3">
         <f t="shared" si="18"/>
@@ -31792,7 +33218,7 @@
       </c>
       <c r="AG323" s="32"/>
       <c r="AH323" s="6">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="324" spans="1:34" x14ac:dyDescent="0.25">
@@ -31805,8 +33231,8 @@
       <c r="C324" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D324" s="3" t="s">
-        <v>50</v>
+      <c r="D324" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="E324" s="3">
         <f t="shared" si="18"/>
@@ -31873,7 +33299,7 @@
         <v>32</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E325" s="3">
         <f t="shared" si="18"/>
@@ -31940,7 +33366,7 @@
         <v>32</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E326" s="3">
         <f t="shared" si="18"/>
@@ -32007,7 +33433,7 @@
         <v>32</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E327" s="3">
         <f t="shared" si="18"/>
@@ -32074,7 +33500,7 @@
         <v>32</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E328" s="3">
         <f t="shared" si="18"/>
@@ -32138,10 +33564,10 @@
         <v>20260427</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="E329" s="3">
         <f t="shared" si="18"/>
@@ -32207,8 +33633,8 @@
       <c r="C330" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D330" s="1" t="s">
-        <v>37</v>
+      <c r="D330" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="E330" s="3">
         <f t="shared" si="18"/>
@@ -32274,8 +33700,8 @@
       <c r="C331" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D331" s="3" t="s">
-        <v>41</v>
+      <c r="D331" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E331" s="3">
         <f t="shared" si="18"/>
@@ -32342,7 +33768,7 @@
         <v>33</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E332" s="3">
         <f t="shared" si="18"/>
@@ -32409,7 +33835,7 @@
         <v>33</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E333" s="3">
         <f t="shared" si="18"/>
@@ -32476,7 +33902,7 @@
         <v>33</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="E334" s="3">
         <f t="shared" si="18"/>
@@ -32533,17 +33959,17 @@
       </c>
     </row>
     <row r="335" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A335" s="39">
-        <v>31</v>
-      </c>
-      <c r="B335" s="40">
-        <v>20260504</v>
-      </c>
-      <c r="C335" s="41" t="s">
-        <v>32</v>
+      <c r="A335" s="18">
+        <v>30</v>
+      </c>
+      <c r="B335" s="28">
+        <v>20260427</v>
+      </c>
+      <c r="C335" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="E335" s="3">
         <f t="shared" si="18"/>
@@ -32596,7 +34022,7 @@
       </c>
       <c r="AG335" s="32"/>
       <c r="AH335" s="6">
-        <v>51</v>
+        <v>64</v>
       </c>
     </row>
     <row r="336" spans="1:34" x14ac:dyDescent="0.25">
@@ -32610,7 +34036,7 @@
         <v>32</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E336" s="3">
         <f t="shared" si="18"/>
@@ -32676,8 +34102,8 @@
       <c r="C337" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="D337" s="1" t="s">
-        <v>47</v>
+      <c r="D337" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="E337" s="3">
         <f t="shared" si="18"/>
@@ -32743,16 +34169,14 @@
       <c r="C338" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="D338" s="3" t="s">
-        <v>44</v>
+      <c r="D338" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="E338" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="F338" s="3" t="s">
-        <v>69</v>
-      </c>
+      <c r="F338" s="3"/>
       <c r="G338" s="3"/>
       <c r="H338" s="3">
         <v>0</v>
@@ -32813,14 +34237,14 @@
         <v>32</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E339" s="3">
-        <f t="shared" ref="E339:E367" si="21">SUM(F339:AF339)-SUM(F339:L339,Q339)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F339" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G339" s="3"/>
       <c r="H339" s="3">
@@ -32882,14 +34306,14 @@
         <v>32</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E340" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="E340:E368" si="21">SUM(F340:AF340)-SUM(F340:L340,Q340)</f>
         <v>0</v>
       </c>
       <c r="F340" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G340" s="3"/>
       <c r="H340" s="3">
@@ -32948,16 +34372,18 @@
         <v>20260504</v>
       </c>
       <c r="C341" s="41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="E341" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="F341" s="3"/>
+      <c r="F341" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="G341" s="3"/>
       <c r="H341" s="3">
         <v>0</v>
@@ -33018,7 +34444,7 @@
         <v>33</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E342" s="3">
         <f t="shared" si="21"/>
@@ -33084,8 +34510,8 @@
       <c r="C343" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="D343" s="1" t="s">
-        <v>40</v>
+      <c r="D343" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="E343" s="3">
         <f t="shared" si="21"/>
@@ -33151,8 +34577,8 @@
       <c r="C344" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="D344" s="3" t="s">
-        <v>41</v>
+      <c r="D344" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="E344" s="3">
         <f t="shared" si="21"/>
@@ -33219,7 +34645,7 @@
         <v>33</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E345" s="3">
         <f t="shared" si="21"/>
@@ -33286,7 +34712,7 @@
         <v>33</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E346" s="3">
         <f t="shared" si="21"/>
@@ -33343,17 +34769,17 @@
       </c>
     </row>
     <row r="347" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A347" s="18">
-        <v>32</v>
-      </c>
-      <c r="B347" s="28">
-        <v>20260511</v>
-      </c>
-      <c r="C347" s="3" t="s">
-        <v>32</v>
+      <c r="A347" s="39">
+        <v>31</v>
+      </c>
+      <c r="B347" s="40">
+        <v>20260504</v>
+      </c>
+      <c r="C347" s="41" t="s">
+        <v>33</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E347" s="3">
         <f t="shared" si="21"/>
@@ -33420,7 +34846,7 @@
         <v>32</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E348" s="3">
         <f t="shared" si="21"/>
@@ -33487,7 +34913,7 @@
         <v>32</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E349" s="3">
         <f t="shared" si="21"/>
@@ -33553,8 +34979,8 @@
       <c r="C350" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D350" s="1" t="s">
-        <v>40</v>
+      <c r="D350" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="E350" s="3">
         <f t="shared" si="21"/>
@@ -33620,8 +35046,8 @@
       <c r="C351" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D351" s="3" t="s">
-        <v>57</v>
+      <c r="D351" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="E351" s="3">
         <f t="shared" si="21"/>
@@ -33685,10 +35111,10 @@
         <v>20260511</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E352" s="3">
         <f t="shared" si="21"/>
@@ -33755,7 +35181,7 @@
         <v>33</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E353" s="3">
         <f t="shared" si="21"/>
@@ -33822,7 +35248,7 @@
         <v>33</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E354" s="3">
         <f t="shared" si="21"/>
@@ -33889,7 +35315,7 @@
         <v>33</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E355" s="3">
         <f t="shared" si="21"/>
@@ -33956,7 +35382,7 @@
         <v>33</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E356" s="3">
         <f t="shared" si="21"/>
@@ -34014,16 +35440,16 @@
     </row>
     <row r="357" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A357" s="18">
+        <v>32</v>
+      </c>
+      <c r="B357" s="28">
+        <v>20260511</v>
+      </c>
+      <c r="C357" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B357" s="28">
-        <v>20260525</v>
-      </c>
-      <c r="C357" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D357" s="1" t="s">
-        <v>43</v>
+      <c r="D357" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="E357" s="3">
         <f t="shared" si="21"/>
@@ -34076,7 +35502,7 @@
       </c>
       <c r="AG357" s="32"/>
       <c r="AH357" s="6">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="358" spans="1:34" x14ac:dyDescent="0.25">
@@ -34089,8 +35515,8 @@
       <c r="C358" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D358" s="3" t="s">
-        <v>36</v>
+      <c r="D358" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E358" s="3">
         <f t="shared" si="21"/>
@@ -34157,7 +35583,7 @@
         <v>32</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E359" s="3">
         <f t="shared" si="21"/>
@@ -34224,7 +35650,7 @@
         <v>32</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E360" s="3">
         <f t="shared" si="21"/>
@@ -34291,7 +35717,7 @@
         <v>32</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E361" s="3">
         <f t="shared" si="21"/>
@@ -34358,7 +35784,7 @@
         <v>32</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E362" s="3">
         <f t="shared" si="21"/>
@@ -34422,10 +35848,10 @@
         <v>20260525</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D363" s="1" t="s">
-        <v>68</v>
+        <v>32</v>
+      </c>
+      <c r="D363" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="E363" s="3">
         <f t="shared" si="21"/>
@@ -34491,8 +35917,8 @@
       <c r="C364" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D364" s="3" t="s">
-        <v>40</v>
+      <c r="D364" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="E364" s="3">
         <f t="shared" si="21"/>
@@ -34559,7 +35985,7 @@
         <v>33</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E365" s="3">
         <f t="shared" si="21"/>
@@ -34626,7 +36052,7 @@
         <v>33</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E366" s="3">
         <f t="shared" si="21"/>
@@ -34693,7 +36119,7 @@
         <v>33</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E367" s="3">
         <f t="shared" si="21"/>
@@ -34749,74 +36175,141 @@
         <v>57</v>
       </c>
     </row>
-    <row r="368" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A368" s="19">
+    <row r="368" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A368" s="18">
         <v>33</v>
       </c>
-      <c r="B368" s="29">
+      <c r="B368" s="28">
         <v>20260525</v>
       </c>
-      <c r="C368" s="20" t="s">
+      <c r="C368" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D368" s="20" t="s">
+      <c r="D368" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E368" s="3">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="F368" s="3"/>
+      <c r="G368" s="3"/>
+      <c r="H368" s="3">
+        <v>0</v>
+      </c>
+      <c r="I368" s="3">
+        <v>0</v>
+      </c>
+      <c r="J368" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="K368" s="3"/>
+      <c r="L368" s="3"/>
+      <c r="M368" s="4"/>
+      <c r="N368" s="7">
+        <v>0</v>
+      </c>
+      <c r="O368" s="5"/>
+      <c r="P368" s="5"/>
+      <c r="Q368" s="36">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="R368" s="4"/>
+      <c r="S368" s="4"/>
+      <c r="T368" s="5"/>
+      <c r="U368" s="4"/>
+      <c r="V368" s="5"/>
+      <c r="W368" s="4"/>
+      <c r="X368" s="4"/>
+      <c r="Y368" s="4"/>
+      <c r="Z368" s="5"/>
+      <c r="AA368" s="4"/>
+      <c r="AB368" s="5"/>
+      <c r="AC368" s="3"/>
+      <c r="AD368" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE368" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF368" s="31">
+        <v>0</v>
+      </c>
+      <c r="AG368" s="32"/>
+      <c r="AH368" s="6">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="369" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A369" s="19">
+        <v>33</v>
+      </c>
+      <c r="B369" s="29">
+        <v>20260525</v>
+      </c>
+      <c r="C369" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D369" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="E368" s="20">
-        <f>SUM(F368:AF368)-SUM(F368:L368,Q368)</f>
-        <v>0</v>
-      </c>
-      <c r="F368" s="20"/>
-      <c r="G368" s="20"/>
-      <c r="H368" s="20">
-        <v>0</v>
-      </c>
-      <c r="I368" s="20">
-        <v>0</v>
-      </c>
-      <c r="J368" s="20">
-        <f t="shared" ref="J368" si="22">SUM(F368:I368)</f>
-        <v>0</v>
-      </c>
-      <c r="K368" s="20"/>
-      <c r="L368" s="20"/>
-      <c r="M368" s="21"/>
-      <c r="N368" s="22">
-        <v>0</v>
-      </c>
-      <c r="O368" s="23"/>
-      <c r="P368" s="23"/>
-      <c r="Q368" s="37">
+      <c r="E369" s="20">
+        <f>SUM(F369:AF369)-SUM(F369:L369,Q369)</f>
+        <v>0</v>
+      </c>
+      <c r="F369" s="20"/>
+      <c r="G369" s="20"/>
+      <c r="H369" s="20">
+        <v>0</v>
+      </c>
+      <c r="I369" s="20">
+        <v>0</v>
+      </c>
+      <c r="J369" s="20">
+        <f t="shared" ref="J369" si="22">SUM(F369:I369)</f>
+        <v>0</v>
+      </c>
+      <c r="K369" s="20"/>
+      <c r="L369" s="20"/>
+      <c r="M369" s="21"/>
+      <c r="N369" s="22">
+        <v>0</v>
+      </c>
+      <c r="O369" s="23"/>
+      <c r="P369" s="23"/>
+      <c r="Q369" s="37">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="R368" s="21"/>
-      <c r="S368" s="21"/>
-      <c r="T368" s="23"/>
-      <c r="U368" s="21"/>
-      <c r="V368" s="23"/>
-      <c r="W368" s="21"/>
-      <c r="X368" s="21"/>
-      <c r="Y368" s="21"/>
-      <c r="Z368" s="23"/>
-      <c r="AA368" s="21"/>
-      <c r="AB368" s="23"/>
-      <c r="AC368" s="20"/>
-      <c r="AD368" s="20">
-        <v>0</v>
-      </c>
-      <c r="AE368" s="20">
-        <v>0</v>
-      </c>
-      <c r="AF368" s="33">
-        <v>0</v>
-      </c>
-      <c r="AG368" s="33"/>
-      <c r="AH368" s="24">
+      <c r="R369" s="21"/>
+      <c r="S369" s="21"/>
+      <c r="T369" s="23"/>
+      <c r="U369" s="21"/>
+      <c r="V369" s="23"/>
+      <c r="W369" s="21"/>
+      <c r="X369" s="21"/>
+      <c r="Y369" s="21"/>
+      <c r="Z369" s="23"/>
+      <c r="AA369" s="21"/>
+      <c r="AB369" s="23"/>
+      <c r="AC369" s="20"/>
+      <c r="AD369" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE369" s="20">
+        <v>0</v>
+      </c>
+      <c r="AF369" s="33">
+        <v>0</v>
+      </c>
+      <c r="AG369" s="33"/>
+      <c r="AH369" s="24">
         <v>57</v>
       </c>
     </row>
-    <row r="369" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="370" spans="1:34" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Fudbal Bezanija Termini.xlsx
+++ b/Fudbal Bezanija Termini.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beoog\Desktop\Fudbal Bezanija\Sajt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8970561-6BBC-418F-B2F6-8DDECA40EDDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA851FA9-A608-43F1-B4E1-608E8857A3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -210,9 +210,6 @@
     <t>Ivan Apostolski</t>
   </si>
   <si>
-    <t>Ognjen Bubanja (golman)</t>
-  </si>
-  <si>
     <t>GRESKA</t>
   </si>
   <si>
@@ -259,6 +256,9 @@
   </si>
   <si>
     <t>Bubanja (Golman)</t>
+  </si>
+  <si>
+    <t>Bubanja (golman)</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1105,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J1" s="14" t="s">
         <v>8</v>
@@ -1129,7 +1129,7 @@
         <v>12</v>
       </c>
       <c r="Q1" s="34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R1" s="14" t="s">
         <v>17</v>
@@ -14665,7 +14665,7 @@
         <v>60</v>
       </c>
       <c r="AJ127" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="128" spans="1:36" x14ac:dyDescent="0.25">
@@ -14775,7 +14775,7 @@
         <v>60</v>
       </c>
       <c r="AJ128" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="129" spans="1:36" x14ac:dyDescent="0.25">
@@ -14885,7 +14885,7 @@
         <v>60</v>
       </c>
       <c r="AJ129" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="130" spans="1:36" x14ac:dyDescent="0.25">
@@ -16825,7 +16825,7 @@
         <v>33</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="E148" s="3">
         <f t="shared" si="8"/>
@@ -17360,7 +17360,7 @@
         <v>32</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E153" s="3">
         <f t="shared" si="11"/>
@@ -17467,7 +17467,7 @@
         <v>33</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E154" s="3">
         <f t="shared" si="11"/>
@@ -18323,7 +18323,7 @@
         <v>32</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E162" s="3">
         <f t="shared" si="11"/>
@@ -21319,7 +21319,7 @@
         <v>33</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E190" s="3">
         <f t="shared" si="14"/>
@@ -24636,7 +24636,7 @@
         <v>32</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E221" s="3">
         <f t="shared" si="15"/>
@@ -26027,7 +26027,7 @@
         <v>32</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E234" s="3">
         <f t="shared" si="15"/>
@@ -26134,7 +26134,7 @@
         <v>32</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E235" s="3">
         <f t="shared" si="15"/>
@@ -28163,7 +28163,7 @@
         <v>32</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E254" s="3">
         <f t="shared" si="15"/>
@@ -28478,7 +28478,7 @@
         <v>32</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E257" s="3">
         <f t="shared" si="15"/>
@@ -32897,7 +32897,7 @@
         <v>33</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E319" s="3">
         <f t="shared" si="18"/>
@@ -33634,7 +33634,7 @@
         <v>33</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E330" s="3">
         <f t="shared" si="18"/>
@@ -33969,7 +33969,7 @@
         <v>33</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E335" s="3">
         <f t="shared" si="18"/>
@@ -34244,7 +34244,7 @@
         <v>0</v>
       </c>
       <c r="F339" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G339" s="3"/>
       <c r="H339" s="3">
@@ -34313,7 +34313,7 @@
         <v>0</v>
       </c>
       <c r="F340" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G340" s="3"/>
       <c r="H340" s="3">
@@ -34382,7 +34382,7 @@
         <v>0</v>
       </c>
       <c r="F341" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G341" s="3"/>
       <c r="H341" s="3">
@@ -34511,7 +34511,7 @@
         <v>33</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E343" s="3">
         <f t="shared" si="21"/>
@@ -35918,7 +35918,7 @@
         <v>33</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E364" s="3">
         <f t="shared" si="21"/>

--- a/Fudbal Bezanija Termini.xlsx
+++ b/Fudbal Bezanija Termini.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beoog\Desktop\Fudbal Bezanija\Sajt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA851FA9-A608-43F1-B4E1-608E8857A3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD249CC-0FBF-43A5-980B-854E200A7CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="74">
   <si>
     <t>No.</t>
   </si>
@@ -253,9 +253,6 @@
   </si>
   <si>
     <t>Nenad Vidakovic</t>
-  </si>
-  <si>
-    <t>Bubanja (Golman)</t>
   </si>
   <si>
     <t>Bubanja (golman)</t>
@@ -16825,7 +16822,7 @@
         <v>33</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E148" s="3">
         <f t="shared" si="8"/>

--- a/Fudbal Bezanija Termini.xlsx
+++ b/Fudbal Bezanija Termini.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beoog\Desktop\Fudbal Bezanija\Sajt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD249CC-0FBF-43A5-980B-854E200A7CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB399964-3FD8-4EE6-A60B-92875A74501F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fudbal Bezanija Termini" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="73">
   <si>
     <t>No.</t>
   </si>
@@ -183,9 +183,6 @@
     <t>Strahinja Milovanovic</t>
   </si>
   <si>
-    <t>Drug Tegijev Marko</t>
-  </si>
-  <si>
     <t>Ivan Filipovic</t>
   </si>
   <si>
@@ -231,9 +228,6 @@
     <t>Vanijev Burazer</t>
   </si>
   <si>
-    <t>Nenad</t>
-  </si>
-  <si>
     <t>Drug Tegijev</t>
   </si>
   <si>
@@ -252,10 +246,13 @@
     <t>Body Goals</t>
   </si>
   <si>
-    <t>Nenad Vidakovic</t>
+    <t>Bubanja (golman)</t>
   </si>
   <si>
-    <t>Bubanja (golman)</t>
+    <t>Nenad Tegijev</t>
+  </si>
+  <si>
+    <t>Nenad Tegijev Vidakovic</t>
   </si>
 </sst>
 </file>
@@ -1037,46 +1034,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AJ370"/>
-  <sheetFormatPr defaultColWidth="7.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="7.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="5.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8" style="38" customWidth="1"/>
-    <col min="18" max="18" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="9.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="7.42578125" style="1"/>
+    <col min="28" max="28" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="5.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.33203125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="7.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="2" customFormat="1" ht="31.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" s="2" customFormat="1" ht="31.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1102,7 +1099,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J1" s="14" t="s">
         <v>8</v>
@@ -1126,7 +1123,7 @@
         <v>12</v>
       </c>
       <c r="Q1" s="34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R1" s="14" t="s">
         <v>17</v>
@@ -1180,7 +1177,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" s="25">
         <v>1</v>
       </c>
@@ -1287,7 +1284,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="18">
         <v>1</v>
       </c>
@@ -1394,7 +1391,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="25">
         <v>1</v>
       </c>
@@ -1501,7 +1498,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>1</v>
       </c>
@@ -1608,7 +1605,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
         <v>1</v>
       </c>
@@ -1715,7 +1712,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A7" s="18">
         <v>1</v>
       </c>
@@ -1822,7 +1819,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
         <v>1</v>
       </c>
@@ -1929,7 +1926,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A9" s="18">
         <v>1</v>
       </c>
@@ -2036,7 +2033,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
         <v>1</v>
       </c>
@@ -2143,7 +2140,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A11" s="18">
         <v>1</v>
       </c>
@@ -2250,7 +2247,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="18">
         <v>2</v>
       </c>
@@ -2357,7 +2354,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13" s="18">
         <v>2</v>
       </c>
@@ -2464,7 +2461,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" s="18">
         <v>2</v>
       </c>
@@ -2571,7 +2568,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A15" s="18">
         <v>2</v>
       </c>
@@ -2678,7 +2675,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A16" s="18">
         <v>2</v>
       </c>
@@ -2785,7 +2782,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A17" s="18">
         <v>2</v>
       </c>
@@ -2892,7 +2889,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A18" s="18">
         <v>2</v>
       </c>
@@ -2999,7 +2996,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A19" s="18">
         <v>2</v>
       </c>
@@ -3106,7 +3103,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A20" s="18">
         <v>2</v>
       </c>
@@ -3213,7 +3210,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A21" s="18">
         <v>2</v>
       </c>
@@ -3320,7 +3317,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A22" s="18">
         <v>3</v>
       </c>
@@ -3427,7 +3424,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A23" s="18">
         <v>3</v>
       </c>
@@ -3534,7 +3531,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A24" s="18">
         <v>3</v>
       </c>
@@ -3641,7 +3638,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
         <v>3</v>
       </c>
@@ -3652,7 +3649,7 @@
         <v>34</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
@@ -3748,7 +3745,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A26" s="18">
         <v>3</v>
       </c>
@@ -3855,7 +3852,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A27" s="18">
         <v>3</v>
       </c>
@@ -3962,7 +3959,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A28" s="18">
         <v>3</v>
       </c>
@@ -3973,7 +3970,7 @@
         <v>35</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
@@ -4069,7 +4066,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A29" s="18">
         <v>3</v>
       </c>
@@ -4176,7 +4173,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A30" s="18">
         <v>3</v>
       </c>
@@ -4283,7 +4280,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A31" s="18">
         <v>3</v>
       </c>
@@ -4294,7 +4291,7 @@
         <v>35</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
@@ -4390,7 +4387,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A32" s="18">
         <v>4</v>
       </c>
@@ -4497,7 +4494,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A33" s="18">
         <v>4</v>
       </c>
@@ -4604,7 +4601,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A34" s="18">
         <v>4</v>
       </c>
@@ -4711,7 +4708,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A35" s="18">
         <v>4</v>
       </c>
@@ -4818,7 +4815,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A36" s="18">
         <v>4</v>
       </c>
@@ -4829,7 +4826,7 @@
         <v>32</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E36" s="3">
         <f t="shared" si="3"/>
@@ -4925,7 +4922,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A37" s="18">
         <v>4</v>
       </c>
@@ -5032,7 +5029,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A38" s="18">
         <v>4</v>
       </c>
@@ -5139,7 +5136,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A39" s="18">
         <v>4</v>
       </c>
@@ -5150,7 +5147,7 @@
         <v>33</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E39" s="3">
         <f t="shared" si="3"/>
@@ -5246,7 +5243,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A40" s="18">
         <v>4</v>
       </c>
@@ -5353,7 +5350,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A41" s="18">
         <v>4</v>
       </c>
@@ -5364,7 +5361,7 @@
         <v>33</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="E41" s="3">
         <f t="shared" si="3"/>
@@ -5460,7 +5457,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A42" s="18">
         <v>5</v>
       </c>
@@ -5567,7 +5564,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A43" s="18">
         <v>5</v>
       </c>
@@ -5674,7 +5671,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A44" s="18">
         <v>5</v>
       </c>
@@ -5781,7 +5778,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A45" s="18">
         <v>5</v>
       </c>
@@ -5888,7 +5885,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A46" s="18">
         <v>5</v>
       </c>
@@ -5995,7 +5992,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A47" s="18">
         <v>5</v>
       </c>
@@ -6102,7 +6099,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A48" s="18">
         <v>5</v>
       </c>
@@ -6209,7 +6206,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A49" s="18">
         <v>5</v>
       </c>
@@ -6316,7 +6313,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A50" s="18">
         <v>5</v>
       </c>
@@ -6327,7 +6324,7 @@
         <v>35</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="E50" s="3">
         <f t="shared" si="3"/>
@@ -6423,7 +6420,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A51" s="18">
         <v>5</v>
       </c>
@@ -6434,7 +6431,7 @@
         <v>35</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E51" s="3">
         <f t="shared" si="3"/>
@@ -6530,7 +6527,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A52" s="18">
         <v>6</v>
       </c>
@@ -6637,7 +6634,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A53" s="18">
         <v>6</v>
       </c>
@@ -6744,7 +6741,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A54" s="18">
         <v>6</v>
       </c>
@@ -6851,7 +6848,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A55" s="18">
         <v>6</v>
       </c>
@@ -6958,7 +6955,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="56" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A56" s="18">
         <v>6</v>
       </c>
@@ -6969,7 +6966,7 @@
         <v>32</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E56" s="3">
         <f t="shared" si="3"/>
@@ -7065,7 +7062,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A57" s="18">
         <v>6</v>
       </c>
@@ -7172,7 +7169,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A58" s="18">
         <v>6</v>
       </c>
@@ -7183,7 +7180,7 @@
         <v>33</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E58" s="3">
         <f t="shared" si="3"/>
@@ -7279,7 +7276,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A59" s="18">
         <v>6</v>
       </c>
@@ -7386,7 +7383,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A60" s="18">
         <v>6</v>
       </c>
@@ -7493,7 +7490,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A61" s="18">
         <v>6</v>
       </c>
@@ -7600,7 +7597,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="62" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A62" s="18">
         <v>7</v>
       </c>
@@ -7707,7 +7704,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="63" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A63" s="18">
         <v>7</v>
       </c>
@@ -7814,7 +7811,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="64" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A64" s="18">
         <v>7</v>
       </c>
@@ -7921,7 +7918,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="65" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A65" s="18">
         <v>7</v>
       </c>
@@ -8028,7 +8025,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="66" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A66" s="18">
         <v>7</v>
       </c>
@@ -8039,7 +8036,7 @@
         <v>32</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E66" s="3">
         <f t="shared" ref="E66:E97" si="4">SUM(F66:AC66)</f>
@@ -8135,7 +8132,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="67" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A67" s="18">
         <v>7</v>
       </c>
@@ -8242,7 +8239,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="68" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A68" s="18">
         <v>7</v>
       </c>
@@ -8349,7 +8346,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A69" s="18">
         <v>7</v>
       </c>
@@ -8360,7 +8357,7 @@
         <v>33</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E69" s="3">
         <f t="shared" si="4"/>
@@ -8456,7 +8453,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="70" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A70" s="18">
         <v>7</v>
       </c>
@@ -8467,7 +8464,7 @@
         <v>33</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E70" s="3">
         <f t="shared" si="4"/>
@@ -8563,7 +8560,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="71" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A71" s="18">
         <v>7</v>
       </c>
@@ -8670,7 +8667,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="72" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A72" s="18">
         <v>8</v>
       </c>
@@ -8777,7 +8774,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="73" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A73" s="18">
         <v>8</v>
       </c>
@@ -8884,7 +8881,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="74" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A74" s="18">
         <v>8</v>
       </c>
@@ -8991,7 +8988,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="75" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A75" s="18">
         <v>8</v>
       </c>
@@ -9002,7 +8999,7 @@
         <v>32</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E75" s="3">
         <f t="shared" si="4"/>
@@ -9098,7 +9095,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="76" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A76" s="18">
         <v>8</v>
       </c>
@@ -9109,7 +9106,7 @@
         <v>32</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E76" s="3">
         <f t="shared" si="4"/>
@@ -9205,7 +9202,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="77" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A77" s="18">
         <v>8</v>
       </c>
@@ -9312,7 +9309,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="78" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A78" s="18">
         <v>8</v>
       </c>
@@ -9419,7 +9416,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="79" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A79" s="18">
         <v>8</v>
       </c>
@@ -9430,7 +9427,7 @@
         <v>33</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E79" s="3">
         <f t="shared" si="4"/>
@@ -9526,7 +9523,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="80" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A80" s="18">
         <v>8</v>
       </c>
@@ -9633,7 +9630,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="81" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A81" s="18">
         <v>8</v>
       </c>
@@ -9740,7 +9737,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="82" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A82" s="18">
         <v>9</v>
       </c>
@@ -9751,7 +9748,7 @@
         <v>32</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E82" s="3">
         <f t="shared" si="4"/>
@@ -9847,7 +9844,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="83" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A83" s="18">
         <v>9</v>
       </c>
@@ -9954,7 +9951,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="84" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A84" s="18">
         <v>9</v>
       </c>
@@ -9965,7 +9962,7 @@
         <v>32</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E84" s="3">
         <f t="shared" si="4"/>
@@ -10061,7 +10058,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="85" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A85" s="18">
         <v>9</v>
       </c>
@@ -10168,7 +10165,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="86" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A86" s="18">
         <v>9</v>
       </c>
@@ -10275,7 +10272,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="87" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A87" s="18">
         <v>9</v>
       </c>
@@ -10382,7 +10379,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="88" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A88" s="18">
         <v>9</v>
       </c>
@@ -10489,7 +10486,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="89" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A89" s="18">
         <v>9</v>
       </c>
@@ -10596,7 +10593,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="90" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A90" s="18">
         <v>9</v>
       </c>
@@ -10703,7 +10700,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="91" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A91" s="18">
         <v>9</v>
       </c>
@@ -10810,7 +10807,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="92" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A92" s="18">
         <v>10</v>
       </c>
@@ -10917,7 +10914,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="93" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A93" s="18">
         <v>10</v>
       </c>
@@ -11024,7 +11021,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="94" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A94" s="18">
         <v>10</v>
       </c>
@@ -11131,7 +11128,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="95" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A95" s="18">
         <v>10</v>
       </c>
@@ -11238,7 +11235,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="96" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A96" s="18">
         <v>10</v>
       </c>
@@ -11345,7 +11342,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="97" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A97" s="18">
         <v>10</v>
       </c>
@@ -11452,7 +11449,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="98" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A98" s="18">
         <v>10</v>
       </c>
@@ -11559,7 +11556,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="99" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A99" s="18">
         <v>10</v>
       </c>
@@ -11666,7 +11663,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="100" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A100" s="18">
         <v>10</v>
       </c>
@@ -11677,7 +11674,7 @@
         <v>33</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E100" s="3">
         <f t="shared" si="7"/>
@@ -11773,7 +11770,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="101" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A101" s="18">
         <v>10</v>
       </c>
@@ -11880,7 +11877,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="102" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A102" s="18">
         <v>11</v>
       </c>
@@ -11891,7 +11888,7 @@
         <v>32</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E102" s="3">
         <f t="shared" si="7"/>
@@ -11987,7 +11984,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="103" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A103" s="18">
         <v>11</v>
       </c>
@@ -12094,7 +12091,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="104" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A104" s="18">
         <v>11</v>
       </c>
@@ -12201,7 +12198,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="105" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A105" s="18">
         <v>11</v>
       </c>
@@ -12308,7 +12305,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="106" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A106" s="18">
         <v>11</v>
       </c>
@@ -12319,7 +12316,7 @@
         <v>32</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E106" s="3">
         <f t="shared" si="7"/>
@@ -12415,7 +12412,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="107" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A107" s="18">
         <v>11</v>
       </c>
@@ -12522,7 +12519,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="108" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A108" s="18">
         <v>11</v>
       </c>
@@ -12533,7 +12530,7 @@
         <v>33</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E108" s="3">
         <f t="shared" si="7"/>
@@ -12629,7 +12626,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="109" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A109" s="18">
         <v>11</v>
       </c>
@@ -12736,7 +12733,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="110" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A110" s="18">
         <v>11</v>
       </c>
@@ -12843,7 +12840,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="111" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A111" s="18">
         <v>11</v>
       </c>
@@ -12950,7 +12947,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="112" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A112" s="18">
         <v>11</v>
       </c>
@@ -13057,7 +13054,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="113" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A113" s="18">
         <v>11</v>
       </c>
@@ -13164,7 +13161,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="114" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A114" s="18">
         <v>12</v>
       </c>
@@ -13175,7 +13172,7 @@
         <v>32</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="E114" s="3">
         <f t="shared" si="7"/>
@@ -13271,7 +13268,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="115" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A115" s="18">
         <v>12</v>
       </c>
@@ -13378,7 +13375,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="116" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A116" s="18">
         <v>12</v>
       </c>
@@ -13485,7 +13482,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="117" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A117" s="18">
         <v>12</v>
       </c>
@@ -13592,7 +13589,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="118" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A118" s="18">
         <v>12</v>
       </c>
@@ -13699,7 +13696,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A119" s="18">
         <v>12</v>
       </c>
@@ -13806,7 +13803,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="120" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A120" s="18">
         <v>12</v>
       </c>
@@ -13913,7 +13910,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="121" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A121" s="18">
         <v>12</v>
       </c>
@@ -13924,7 +13921,7 @@
         <v>33</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E121" s="3">
         <f t="shared" si="7"/>
@@ -14020,7 +14017,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="122" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A122" s="18">
         <v>12</v>
       </c>
@@ -14031,7 +14028,7 @@
         <v>33</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E122" s="3">
         <f t="shared" si="7"/>
@@ -14127,7 +14124,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="123" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A123" s="18">
         <v>12</v>
       </c>
@@ -14234,7 +14231,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="124" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A124" s="18">
         <v>13</v>
       </c>
@@ -14245,7 +14242,7 @@
         <v>32</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E124" s="3">
         <f t="shared" si="7"/>
@@ -14341,7 +14338,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="125" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A125" s="18">
         <v>13</v>
       </c>
@@ -14448,7 +14445,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="126" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A126" s="18">
         <v>13</v>
       </c>
@@ -14555,7 +14552,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="127" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A127" s="18">
         <v>13</v>
       </c>
@@ -14566,7 +14563,7 @@
         <v>32</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E127" s="3">
         <f t="shared" si="7"/>
@@ -14662,10 +14659,10 @@
         <v>60</v>
       </c>
       <c r="AJ127" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="128" spans="1:36" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="128" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A128" s="18">
         <v>13</v>
       </c>
@@ -14772,10 +14769,10 @@
         <v>60</v>
       </c>
       <c r="AJ128" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="129" spans="1:36" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="129" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A129" s="18">
         <v>13</v>
       </c>
@@ -14882,10 +14879,10 @@
         <v>60</v>
       </c>
       <c r="AJ129" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="130" spans="1:36" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="130" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A130" s="18">
         <v>13</v>
       </c>
@@ -14992,7 +14989,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="131" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A131" s="18">
         <v>13</v>
       </c>
@@ -15099,7 +15096,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="132" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A132" s="18">
         <v>13</v>
       </c>
@@ -15206,7 +15203,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="133" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A133" s="18">
         <v>13</v>
       </c>
@@ -15217,7 +15214,7 @@
         <v>33</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E133" s="3">
         <f t="shared" si="8"/>
@@ -15313,7 +15310,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="134" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A134" s="18">
         <v>13</v>
       </c>
@@ -15324,7 +15321,7 @@
         <v>33</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E134" s="3">
         <f t="shared" si="8"/>
@@ -15420,7 +15417,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="135" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A135" s="18">
         <v>13</v>
       </c>
@@ -15527,7 +15524,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="136" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A136" s="18">
         <v>14</v>
       </c>
@@ -15538,7 +15535,7 @@
         <v>32</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E136" s="3">
         <f t="shared" si="8"/>
@@ -15634,7 +15631,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="137" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A137" s="18">
         <v>14</v>
       </c>
@@ -15741,7 +15738,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="138" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A138" s="18">
         <v>14</v>
       </c>
@@ -15752,7 +15749,7 @@
         <v>32</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E138" s="3">
         <f t="shared" si="8"/>
@@ -15848,7 +15845,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="139" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A139" s="18">
         <v>14</v>
       </c>
@@ -15859,7 +15856,7 @@
         <v>32</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E139" s="3">
         <f t="shared" si="8"/>
@@ -15955,7 +15952,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="140" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A140" s="18">
         <v>14</v>
       </c>
@@ -16062,7 +16059,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="141" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A141" s="18">
         <v>14</v>
       </c>
@@ -16169,7 +16166,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="142" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A142" s="18">
         <v>14</v>
       </c>
@@ -16276,7 +16273,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="143" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A143" s="18">
         <v>14</v>
       </c>
@@ -16383,7 +16380,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="144" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A144" s="18">
         <v>14</v>
       </c>
@@ -16490,7 +16487,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="145" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A145" s="18">
         <v>14</v>
       </c>
@@ -16597,7 +16594,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="146" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A146" s="18">
         <v>14</v>
       </c>
@@ -16704,7 +16701,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="147" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A147" s="18">
         <v>14</v>
       </c>
@@ -16811,7 +16808,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="148" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A148" s="18">
         <v>14</v>
       </c>
@@ -16822,7 +16819,7 @@
         <v>33</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E148" s="3">
         <f t="shared" si="8"/>
@@ -16918,7 +16915,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="149" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A149" s="25">
         <v>15</v>
       </c>
@@ -17025,7 +17022,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="150" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A150" s="25">
         <v>15</v>
       </c>
@@ -17132,7 +17129,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="151" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A151" s="25">
         <v>15</v>
       </c>
@@ -17239,7 +17236,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="152" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A152" s="25">
         <v>15</v>
       </c>
@@ -17346,7 +17343,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="153" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A153" s="25">
         <v>15</v>
       </c>
@@ -17357,7 +17354,7 @@
         <v>32</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E153" s="3">
         <f t="shared" si="11"/>
@@ -17453,7 +17450,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="154" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A154" s="25">
         <v>15</v>
       </c>
@@ -17464,7 +17461,7 @@
         <v>33</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E154" s="3">
         <f t="shared" si="11"/>
@@ -17560,7 +17557,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="155" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A155" s="25">
         <v>15</v>
       </c>
@@ -17667,7 +17664,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="156" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A156" s="25">
         <v>15</v>
       </c>
@@ -17678,7 +17675,7 @@
         <v>33</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E156" s="3">
         <f t="shared" si="11"/>
@@ -17774,7 +17771,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="157" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A157" s="25">
         <v>15</v>
       </c>
@@ -17881,7 +17878,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="158" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A158" s="25">
         <v>15</v>
       </c>
@@ -17988,7 +17985,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="159" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A159" s="18">
         <v>16</v>
       </c>
@@ -18095,7 +18092,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="160" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A160" s="18">
         <v>16</v>
       </c>
@@ -18202,7 +18199,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="161" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A161" s="18">
         <v>16</v>
       </c>
@@ -18309,7 +18306,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="162" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A162" s="18">
         <v>16</v>
       </c>
@@ -18320,7 +18317,7 @@
         <v>32</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E162" s="3">
         <f t="shared" si="11"/>
@@ -18416,7 +18413,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="163" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A163" s="18">
         <v>16</v>
       </c>
@@ -18523,7 +18520,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="164" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A164" s="18">
         <v>16</v>
       </c>
@@ -18630,7 +18627,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="165" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A165" s="18">
         <v>16</v>
       </c>
@@ -18737,7 +18734,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="166" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A166" s="18">
         <v>16</v>
       </c>
@@ -18844,7 +18841,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="167" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A167" s="18">
         <v>16</v>
       </c>
@@ -18951,7 +18948,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="168" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A168" s="18">
         <v>16</v>
       </c>
@@ -18962,7 +18959,7 @@
         <v>33</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E168" s="3">
         <f t="shared" si="11"/>
@@ -19058,7 +19055,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="169" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A169" s="18">
         <v>16</v>
       </c>
@@ -19069,7 +19066,7 @@
         <v>33</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E169" s="3">
         <f t="shared" si="11"/>
@@ -19165,7 +19162,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="170" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A170" s="18">
         <v>16</v>
       </c>
@@ -19272,7 +19269,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="171" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A171" s="18">
         <v>17</v>
       </c>
@@ -19379,7 +19376,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="172" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A172" s="18">
         <v>17</v>
       </c>
@@ -19486,7 +19483,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="173" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A173" s="18">
         <v>17</v>
       </c>
@@ -19593,7 +19590,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="174" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A174" s="18">
         <v>17</v>
       </c>
@@ -19700,7 +19697,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="175" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A175" s="18">
         <v>17</v>
       </c>
@@ -19807,7 +19804,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="176" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A176" s="18">
         <v>17</v>
       </c>
@@ -19914,7 +19911,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="177" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A177" s="18">
         <v>17</v>
       </c>
@@ -20021,7 +20018,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="178" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A178" s="18">
         <v>17</v>
       </c>
@@ -20032,7 +20029,7 @@
         <v>33</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E178" s="3">
         <f t="shared" si="11"/>
@@ -20128,7 +20125,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="179" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A179" s="18">
         <v>17</v>
       </c>
@@ -20235,7 +20232,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="180" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A180" s="18">
         <v>17</v>
       </c>
@@ -20246,7 +20243,7 @@
         <v>33</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E180" s="3">
         <f t="shared" si="11"/>
@@ -20342,7 +20339,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="181" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A181" s="18">
         <v>17</v>
       </c>
@@ -20449,7 +20446,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="182" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A182" s="18">
         <v>17</v>
       </c>
@@ -20556,7 +20553,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="183" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A183" s="18">
         <v>18</v>
       </c>
@@ -20663,7 +20660,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="184" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A184" s="18">
         <v>18</v>
       </c>
@@ -20770,7 +20767,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="185" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A185" s="18">
         <v>18</v>
       </c>
@@ -20877,7 +20874,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="186" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A186" s="18">
         <v>18</v>
       </c>
@@ -20984,7 +20981,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="187" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A187" s="18">
         <v>18</v>
       </c>
@@ -21091,7 +21088,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="188" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A188" s="18">
         <v>18</v>
       </c>
@@ -21198,7 +21195,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="189" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A189" s="18">
         <v>18</v>
       </c>
@@ -21305,7 +21302,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="190" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A190" s="18">
         <v>18</v>
       </c>
@@ -21316,7 +21313,7 @@
         <v>33</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E190" s="3">
         <f t="shared" si="14"/>
@@ -21412,7 +21409,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="191" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A191" s="18">
         <v>18</v>
       </c>
@@ -21423,7 +21420,7 @@
         <v>33</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E191" s="3">
         <f t="shared" si="14"/>
@@ -21519,7 +21516,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="192" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A192" s="18">
         <v>18</v>
       </c>
@@ -21626,7 +21623,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="193" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A193" s="18">
         <v>19</v>
       </c>
@@ -21733,7 +21730,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="194" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A194" s="18">
         <v>19</v>
       </c>
@@ -21840,7 +21837,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="195" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A195" s="18">
         <v>19</v>
       </c>
@@ -21947,7 +21944,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="196" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A196" s="18">
         <v>19</v>
       </c>
@@ -21958,7 +21955,7 @@
         <v>32</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E196" s="3">
         <f t="shared" si="14"/>
@@ -22054,7 +22051,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="197" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A197" s="18">
         <v>19</v>
       </c>
@@ -22161,7 +22158,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="198" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A198" s="18">
         <v>19</v>
       </c>
@@ -22268,7 +22265,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="199" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A199" s="18">
         <v>19</v>
       </c>
@@ -22375,7 +22372,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="200" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A200" s="18">
         <v>19</v>
       </c>
@@ -22386,7 +22383,7 @@
         <v>33</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E200" s="3">
         <f t="shared" si="14"/>
@@ -22482,7 +22479,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="201" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A201" s="18">
         <v>19</v>
       </c>
@@ -22493,7 +22490,7 @@
         <v>33</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E201" s="3">
         <f t="shared" si="14"/>
@@ -22589,7 +22586,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="202" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A202" s="18">
         <v>19</v>
       </c>
@@ -22696,7 +22693,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="203" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A203" s="18">
         <v>19</v>
       </c>
@@ -22803,7 +22800,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="204" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A204" s="18">
         <v>19</v>
       </c>
@@ -22910,7 +22907,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="205" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A205" s="18">
         <v>20</v>
       </c>
@@ -23017,7 +23014,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="206" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A206" s="18">
         <v>20</v>
       </c>
@@ -23124,7 +23121,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="207" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A207" s="18">
         <v>20</v>
       </c>
@@ -23135,7 +23132,7 @@
         <v>32</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E207" s="3">
         <f t="shared" si="14"/>
@@ -23231,7 +23228,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="208" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A208" s="18">
         <v>20</v>
       </c>
@@ -23338,7 +23335,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="209" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A209" s="18">
         <v>20</v>
       </c>
@@ -23445,7 +23442,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="210" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A210" s="18">
         <v>20</v>
       </c>
@@ -23552,7 +23549,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="211" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A211" s="18">
         <v>20</v>
       </c>
@@ -23659,7 +23656,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="212" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A212" s="18">
         <v>20</v>
       </c>
@@ -23766,7 +23763,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="213" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A213" s="18">
         <v>20</v>
       </c>
@@ -23873,7 +23870,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="214" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A214" s="18">
         <v>20</v>
       </c>
@@ -23884,7 +23881,7 @@
         <v>33</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E214" s="3">
         <f t="shared" si="15"/>
@@ -23980,7 +23977,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="215" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A215" s="18">
         <v>20</v>
       </c>
@@ -23991,7 +23988,7 @@
         <v>33</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E215" s="3">
         <f t="shared" si="15"/>
@@ -24087,7 +24084,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="216" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A216" s="18">
         <v>20</v>
       </c>
@@ -24194,7 +24191,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="217" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A217" s="18">
         <v>21</v>
       </c>
@@ -24301,7 +24298,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="218" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A218" s="18">
         <v>21</v>
       </c>
@@ -24408,7 +24405,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="219" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A219" s="18">
         <v>21</v>
       </c>
@@ -24515,7 +24512,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="220" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A220" s="18">
         <v>21</v>
       </c>
@@ -24526,7 +24523,7 @@
         <v>32</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E220" s="3">
         <f t="shared" si="15"/>
@@ -24622,7 +24619,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="221" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A221" s="18">
         <v>21</v>
       </c>
@@ -24633,7 +24630,7 @@
         <v>32</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E221" s="3">
         <f t="shared" si="15"/>
@@ -24729,7 +24726,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="222" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A222" s="18">
         <v>21</v>
       </c>
@@ -24836,7 +24833,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="223" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A223" s="18">
         <v>21</v>
       </c>
@@ -24847,7 +24844,7 @@
         <v>33</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E223" s="3">
         <f t="shared" si="15"/>
@@ -24943,7 +24940,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="224" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A224" s="18">
         <v>21</v>
       </c>
@@ -24954,7 +24951,7 @@
         <v>33</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E224" s="3">
         <f t="shared" si="15"/>
@@ -25050,7 +25047,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="225" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A225" s="18">
         <v>21</v>
       </c>
@@ -25157,7 +25154,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="226" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A226" s="18">
         <v>21</v>
       </c>
@@ -25264,7 +25261,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="227" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A227" s="18">
         <v>21</v>
       </c>
@@ -25371,7 +25368,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="228" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A228" s="18">
         <v>21</v>
       </c>
@@ -25478,7 +25475,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="229" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A229" s="18">
         <v>22</v>
       </c>
@@ -25585,7 +25582,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="230" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A230" s="18">
         <v>22</v>
       </c>
@@ -25692,7 +25689,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="231" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A231" s="18">
         <v>22</v>
       </c>
@@ -25703,7 +25700,7 @@
         <v>32</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E231" s="3">
         <f t="shared" si="15"/>
@@ -25799,7 +25796,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="232" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A232" s="18">
         <v>22</v>
       </c>
@@ -25906,7 +25903,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="233" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A233" s="18">
         <v>22</v>
       </c>
@@ -26013,7 +26010,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="234" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A234" s="18">
         <v>22</v>
       </c>
@@ -26120,7 +26117,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="235" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A235" s="18">
         <v>22</v>
       </c>
@@ -26131,7 +26128,7 @@
         <v>32</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E235" s="3">
         <f t="shared" si="15"/>
@@ -26227,7 +26224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A236" s="18">
         <v>22</v>
       </c>
@@ -26238,7 +26235,7 @@
         <v>33</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E236" s="3">
         <f t="shared" si="15"/>
@@ -26334,7 +26331,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="237" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A237" s="18">
         <v>22</v>
       </c>
@@ -26441,7 +26438,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="238" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A238" s="18">
         <v>22</v>
       </c>
@@ -26548,7 +26545,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="239" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A239" s="18">
         <v>22</v>
       </c>
@@ -26655,7 +26652,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="240" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A240" s="18">
         <v>22</v>
       </c>
@@ -26762,7 +26759,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="241" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A241" s="18">
         <v>22</v>
       </c>
@@ -26869,7 +26866,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="242" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A242" s="18">
         <v>23</v>
       </c>
@@ -26976,7 +26973,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="243" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A243" s="18">
         <v>23</v>
       </c>
@@ -27083,7 +27080,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="244" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A244" s="18">
         <v>23</v>
       </c>
@@ -27190,7 +27187,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="245" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A245" s="18">
         <v>23</v>
       </c>
@@ -27297,7 +27294,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="246" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A246" s="18">
         <v>23</v>
       </c>
@@ -27404,7 +27401,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="247" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A247" s="18">
         <v>23</v>
       </c>
@@ -27511,7 +27508,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="248" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A248" s="18">
         <v>23</v>
       </c>
@@ -27522,7 +27519,7 @@
         <v>33</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E248" s="3">
         <f t="shared" si="15"/>
@@ -27618,7 +27615,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="249" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A249" s="18">
         <v>23</v>
       </c>
@@ -27629,7 +27626,7 @@
         <v>33</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E249" s="3">
         <f t="shared" si="15"/>
@@ -27725,7 +27722,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="250" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A250" s="18">
         <v>23</v>
       </c>
@@ -27832,7 +27829,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="251" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A251" s="18">
         <v>23</v>
       </c>
@@ -27939,7 +27936,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="252" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A252" s="18">
         <v>24</v>
       </c>
@@ -28044,7 +28041,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="253" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A253" s="18">
         <v>24</v>
       </c>
@@ -28149,7 +28146,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="254" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A254" s="18">
         <v>24</v>
       </c>
@@ -28254,7 +28251,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="255" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A255" s="18">
         <v>24</v>
       </c>
@@ -28359,7 +28356,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="256" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A256" s="18">
         <v>24</v>
       </c>
@@ -28464,7 +28461,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="257" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A257" s="18">
         <v>24</v>
       </c>
@@ -28475,7 +28472,7 @@
         <v>32</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E257" s="3">
         <f t="shared" si="15"/>
@@ -28569,7 +28566,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="258" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A258" s="18">
         <v>24</v>
       </c>
@@ -28674,7 +28671,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="259" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A259" s="18">
         <v>24</v>
       </c>
@@ -28685,7 +28682,7 @@
         <v>33</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E259" s="3">
         <f t="shared" si="15"/>
@@ -28779,7 +28776,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="260" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A260" s="18">
         <v>24</v>
       </c>
@@ -28790,7 +28787,7 @@
         <v>33</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E260" s="3">
         <f t="shared" si="15"/>
@@ -28884,7 +28881,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="261" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A261" s="18">
         <v>24</v>
       </c>
@@ -28989,7 +28986,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="262" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A262" s="18">
         <v>24</v>
       </c>
@@ -29094,7 +29091,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="263" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A263" s="18">
         <v>24</v>
       </c>
@@ -29199,7 +29196,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="264" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A264" s="18">
         <v>25</v>
       </c>
@@ -29266,7 +29263,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="265" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A265" s="18">
         <v>25</v>
       </c>
@@ -29333,7 +29330,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="266" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A266" s="18">
         <v>25</v>
       </c>
@@ -29400,7 +29397,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="267" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A267" s="18">
         <v>25</v>
       </c>
@@ -29467,7 +29464,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="268" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A268" s="18">
         <v>25</v>
       </c>
@@ -29534,7 +29531,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="269" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A269" s="18">
         <v>25</v>
       </c>
@@ -29601,7 +29598,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="270" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A270" s="18">
         <v>25</v>
       </c>
@@ -29612,7 +29609,7 @@
         <v>33</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E270" s="3">
         <f t="shared" si="15"/>
@@ -29668,7 +29665,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="271" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A271" s="18">
         <v>25</v>
       </c>
@@ -29679,7 +29676,7 @@
         <v>33</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E271" s="3">
         <f t="shared" si="15"/>
@@ -29735,7 +29732,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="272" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A272" s="18">
         <v>25</v>
       </c>
@@ -29802,7 +29799,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="273" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A273" s="18">
         <v>25</v>
       </c>
@@ -29869,7 +29866,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="274" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A274" s="18">
         <v>25</v>
       </c>
@@ -29936,7 +29933,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="275" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A275" s="18">
         <v>25</v>
       </c>
@@ -29947,7 +29944,7 @@
         <v>33</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E275" s="3">
         <f t="shared" si="15"/>
@@ -30003,7 +30000,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="276" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A276" s="18">
         <v>26</v>
       </c>
@@ -30070,7 +30067,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="277" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A277" s="18">
         <v>26</v>
       </c>
@@ -30137,7 +30134,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="278" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A278" s="18">
         <v>26</v>
       </c>
@@ -30204,7 +30201,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="279" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A279" s="18">
         <v>26</v>
       </c>
@@ -30271,7 +30268,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="280" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A280" s="18">
         <v>26</v>
       </c>
@@ -30338,7 +30335,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="281" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A281" s="18">
         <v>26</v>
       </c>
@@ -30405,7 +30402,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="282" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A282" s="18">
         <v>26</v>
       </c>
@@ -30471,7 +30468,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="283" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A283" s="18">
         <v>26</v>
       </c>
@@ -30538,7 +30535,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="284" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A284" s="18">
         <v>26</v>
       </c>
@@ -30605,7 +30602,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="285" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A285" s="18">
         <v>26</v>
       </c>
@@ -30672,7 +30669,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="286" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A286" s="18">
         <v>26</v>
       </c>
@@ -30683,7 +30680,7 @@
         <v>33</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E286" s="3">
         <f t="shared" si="18"/>
@@ -30739,7 +30736,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="287" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A287" s="18">
         <v>26</v>
       </c>
@@ -30806,7 +30803,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="288" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A288" s="18">
         <v>27</v>
       </c>
@@ -30873,7 +30870,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="289" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A289" s="18">
         <v>27</v>
       </c>
@@ -30940,7 +30937,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="290" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A290" s="18">
         <v>27</v>
       </c>
@@ -31007,7 +31004,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="291" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A291" s="18">
         <v>27</v>
       </c>
@@ -31074,7 +31071,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="292" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A292" s="18">
         <v>27</v>
       </c>
@@ -31141,7 +31138,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="293" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A293" s="18">
         <v>27</v>
       </c>
@@ -31208,7 +31205,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="294" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A294" s="18">
         <v>27</v>
       </c>
@@ -31275,7 +31272,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="295" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A295" s="18">
         <v>27</v>
       </c>
@@ -31286,7 +31283,7 @@
         <v>33</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E295" s="3">
         <f t="shared" si="18"/>
@@ -31342,7 +31339,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="296" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A296" s="18">
         <v>27</v>
       </c>
@@ -31353,7 +31350,7 @@
         <v>33</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E296" s="3">
         <f t="shared" si="18"/>
@@ -31409,7 +31406,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="297" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A297" s="18">
         <v>27</v>
       </c>
@@ -31420,7 +31417,7 @@
         <v>33</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E297" s="3">
         <f t="shared" si="18"/>
@@ -31476,7 +31473,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="298" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A298" s="18">
         <v>27</v>
       </c>
@@ -31543,7 +31540,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="299" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A299" s="18">
         <v>27</v>
       </c>
@@ -31610,7 +31607,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="300" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A300" s="18">
         <v>28</v>
       </c>
@@ -31677,7 +31674,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="301" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A301" s="18">
         <v>28</v>
       </c>
@@ -31744,7 +31741,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="302" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A302" s="18">
         <v>28</v>
       </c>
@@ -31755,7 +31752,7 @@
         <v>32</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E302" s="3">
         <f t="shared" si="18"/>
@@ -31811,7 +31808,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="303" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A303" s="18">
         <v>28</v>
       </c>
@@ -31878,7 +31875,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="304" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A304" s="18">
         <v>28</v>
       </c>
@@ -31945,7 +31942,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="305" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A305" s="18">
         <v>28</v>
       </c>
@@ -32012,7 +32009,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="306" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A306" s="18">
         <v>28</v>
       </c>
@@ -32079,7 +32076,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="307" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A307" s="18">
         <v>28</v>
       </c>
@@ -32146,7 +32143,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="308" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A308" s="18">
         <v>28</v>
       </c>
@@ -32213,7 +32210,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="309" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A309" s="18">
         <v>28</v>
       </c>
@@ -32224,7 +32221,7 @@
         <v>33</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E309" s="3">
         <f t="shared" si="18"/>
@@ -32280,7 +32277,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="310" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A310" s="18">
         <v>28</v>
       </c>
@@ -32347,7 +32344,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="311" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A311" s="18">
         <v>28</v>
       </c>
@@ -32414,7 +32411,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="312" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A312" s="18">
         <v>29</v>
       </c>
@@ -32481,7 +32478,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="313" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A313" s="18">
         <v>29</v>
       </c>
@@ -32548,7 +32545,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="314" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A314" s="18">
         <v>29</v>
       </c>
@@ -32615,7 +32612,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="315" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A315" s="18">
         <v>29</v>
       </c>
@@ -32682,7 +32679,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="316" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A316" s="18">
         <v>29</v>
       </c>
@@ -32749,7 +32746,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="317" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A317" s="18">
         <v>29</v>
       </c>
@@ -32760,7 +32757,7 @@
         <v>32</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E317" s="3">
         <f t="shared" si="18"/>
@@ -32816,7 +32813,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="318" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A318" s="18">
         <v>29</v>
       </c>
@@ -32883,7 +32880,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="319" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A319" s="18">
         <v>29</v>
       </c>
@@ -32894,7 +32891,7 @@
         <v>33</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E319" s="3">
         <f t="shared" si="18"/>
@@ -32950,7 +32947,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="320" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A320" s="18">
         <v>29</v>
       </c>
@@ -33017,7 +33014,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="321" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A321" s="18">
         <v>29</v>
       </c>
@@ -33028,7 +33025,7 @@
         <v>33</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E321" s="3">
         <f t="shared" si="18"/>
@@ -33084,7 +33081,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="322" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A322" s="18">
         <v>29</v>
       </c>
@@ -33095,7 +33092,7 @@
         <v>33</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E322" s="3">
         <f t="shared" si="18"/>
@@ -33151,7 +33148,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="323" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A323" s="18">
         <v>29</v>
       </c>
@@ -33218,7 +33215,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="324" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A324" s="18">
         <v>30</v>
       </c>
@@ -33285,7 +33282,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="325" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A325" s="18">
         <v>30</v>
       </c>
@@ -33296,7 +33293,7 @@
         <v>32</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E325" s="3">
         <f t="shared" si="18"/>
@@ -33352,7 +33349,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="326" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A326" s="18">
         <v>30</v>
       </c>
@@ -33419,7 +33416,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="327" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A327" s="18">
         <v>30</v>
       </c>
@@ -33486,7 +33483,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="328" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A328" s="18">
         <v>30</v>
       </c>
@@ -33553,7 +33550,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="329" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A329" s="18">
         <v>30</v>
       </c>
@@ -33620,7 +33617,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="330" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A330" s="18">
         <v>30</v>
       </c>
@@ -33631,7 +33628,7 @@
         <v>33</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E330" s="3">
         <f t="shared" si="18"/>
@@ -33687,7 +33684,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="331" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A331" s="18">
         <v>30</v>
       </c>
@@ -33754,7 +33751,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="332" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A332" s="18">
         <v>30</v>
       </c>
@@ -33821,7 +33818,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="333" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A333" s="18">
         <v>30</v>
       </c>
@@ -33888,7 +33885,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="334" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A334" s="18">
         <v>30</v>
       </c>
@@ -33955,7 +33952,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="335" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A335" s="18">
         <v>30</v>
       </c>
@@ -33966,7 +33963,7 @@
         <v>33</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E335" s="3">
         <f t="shared" si="18"/>
@@ -34022,7 +34019,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="336" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A336" s="39">
         <v>31</v>
       </c>
@@ -34033,7 +34030,7 @@
         <v>32</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E336" s="3">
         <f t="shared" si="18"/>
@@ -34089,7 +34086,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="337" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A337" s="39">
         <v>31</v>
       </c>
@@ -34156,7 +34153,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="338" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A338" s="39">
         <v>31</v>
       </c>
@@ -34223,7 +34220,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="339" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A339" s="39">
         <v>31</v>
       </c>
@@ -34241,7 +34238,7 @@
         <v>0</v>
       </c>
       <c r="F339" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G339" s="3"/>
       <c r="H339" s="3">
@@ -34292,7 +34289,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="340" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A340" s="39">
         <v>31</v>
       </c>
@@ -34310,7 +34307,7 @@
         <v>0</v>
       </c>
       <c r="F340" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G340" s="3"/>
       <c r="H340" s="3">
@@ -34361,7 +34358,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="341" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A341" s="39">
         <v>31</v>
       </c>
@@ -34379,7 +34376,7 @@
         <v>0</v>
       </c>
       <c r="F341" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G341" s="3"/>
       <c r="H341" s="3">
@@ -34430,7 +34427,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="342" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A342" s="39">
         <v>31</v>
       </c>
@@ -34441,7 +34438,7 @@
         <v>33</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E342" s="3">
         <f t="shared" si="21"/>
@@ -34497,7 +34494,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="343" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A343" s="39">
         <v>31</v>
       </c>
@@ -34508,7 +34505,7 @@
         <v>33</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E343" s="3">
         <f t="shared" si="21"/>
@@ -34564,7 +34561,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="344" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A344" s="39">
         <v>31</v>
       </c>
@@ -34631,7 +34628,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="345" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A345" s="39">
         <v>31</v>
       </c>
@@ -34698,7 +34695,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="346" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A346" s="39">
         <v>31</v>
       </c>
@@ -34709,7 +34706,7 @@
         <v>33</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E346" s="3">
         <f t="shared" si="21"/>
@@ -34765,7 +34762,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="347" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A347" s="39">
         <v>31</v>
       </c>
@@ -34832,7 +34829,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="348" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A348" s="18">
         <v>32</v>
       </c>
@@ -34899,7 +34896,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="349" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A349" s="18">
         <v>32</v>
       </c>
@@ -34966,7 +34963,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="350" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A350" s="18">
         <v>32</v>
       </c>
@@ -35033,7 +35030,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="351" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A351" s="18">
         <v>32</v>
       </c>
@@ -35100,7 +35097,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="352" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A352" s="18">
         <v>32</v>
       </c>
@@ -35111,7 +35108,7 @@
         <v>32</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E352" s="3">
         <f t="shared" si="21"/>
@@ -35167,7 +35164,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="353" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A353" s="18">
         <v>32</v>
       </c>
@@ -35234,7 +35231,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="354" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A354" s="18">
         <v>32</v>
       </c>
@@ -35301,7 +35298,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="355" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A355" s="18">
         <v>32</v>
       </c>
@@ -35368,7 +35365,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="356" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A356" s="18">
         <v>32</v>
       </c>
@@ -35435,7 +35432,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="357" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A357" s="18">
         <v>32</v>
       </c>
@@ -35502,7 +35499,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="358" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A358" s="18">
         <v>33</v>
       </c>
@@ -35569,7 +35566,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="359" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A359" s="18">
         <v>33</v>
       </c>
@@ -35636,7 +35633,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="360" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A360" s="18">
         <v>33</v>
       </c>
@@ -35647,7 +35644,7 @@
         <v>32</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E360" s="3">
         <f t="shared" si="21"/>
@@ -35703,7 +35700,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="361" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A361" s="18">
         <v>33</v>
       </c>
@@ -35770,7 +35767,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="362" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A362" s="18">
         <v>33</v>
       </c>
@@ -35837,7 +35834,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="363" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A363" s="18">
         <v>33</v>
       </c>
@@ -35904,7 +35901,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="364" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A364" s="18">
         <v>33</v>
       </c>
@@ -35915,7 +35912,7 @@
         <v>33</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E364" s="3">
         <f t="shared" si="21"/>
@@ -35971,7 +35968,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="365" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A365" s="18">
         <v>33</v>
       </c>
@@ -36038,7 +36035,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="366" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A366" s="18">
         <v>33</v>
       </c>
@@ -36105,7 +36102,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="367" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A367" s="18">
         <v>33</v>
       </c>
@@ -36172,7 +36169,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="368" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A368" s="18">
         <v>33</v>
       </c>
@@ -36183,7 +36180,7 @@
         <v>33</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E368" s="3">
         <f t="shared" si="21"/>
@@ -36239,7 +36236,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="369" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A369" s="19">
         <v>33</v>
       </c>
@@ -36306,7 +36303,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="370" spans="1:34" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="370" spans="1:34" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Fudbal Bezanija Termini.xlsx
+++ b/Fudbal Bezanija Termini.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beoog\Desktop\Fudbal Bezanija\Sajt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB399964-3FD8-4EE6-A60B-92875A74501F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{115DB6D5-4A32-4F3A-BC51-19A5304518D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28036,7 +28036,9 @@
       <c r="AF252" s="31">
         <v>0</v>
       </c>
-      <c r="AG252" s="32"/>
+      <c r="AG252" s="32">
+        <v>1</v>
+      </c>
       <c r="AH252" s="6">
         <v>52</v>
       </c>
@@ -28141,7 +28143,9 @@
       <c r="AF253" s="31">
         <v>0</v>
       </c>
-      <c r="AG253" s="32"/>
+      <c r="AG253" s="32">
+        <v>1</v>
+      </c>
       <c r="AH253" s="6">
         <v>52</v>
       </c>
@@ -28246,7 +28250,9 @@
       <c r="AF254" s="31">
         <v>0</v>
       </c>
-      <c r="AG254" s="32"/>
+      <c r="AG254" s="32">
+        <v>1</v>
+      </c>
       <c r="AH254" s="6">
         <v>52</v>
       </c>
@@ -28351,7 +28357,9 @@
       <c r="AF255" s="31">
         <v>0</v>
       </c>
-      <c r="AG255" s="32"/>
+      <c r="AG255" s="32">
+        <v>1</v>
+      </c>
       <c r="AH255" s="6">
         <v>52</v>
       </c>
@@ -28456,7 +28464,9 @@
       <c r="AF256" s="31">
         <v>0</v>
       </c>
-      <c r="AG256" s="32"/>
+      <c r="AG256" s="32">
+        <v>1</v>
+      </c>
       <c r="AH256" s="6">
         <v>52</v>
       </c>
@@ -28561,7 +28571,9 @@
       <c r="AF257" s="31">
         <v>0</v>
       </c>
-      <c r="AG257" s="32"/>
+      <c r="AG257" s="32">
+        <v>1</v>
+      </c>
       <c r="AH257" s="6">
         <v>52</v>
       </c>
@@ -28666,7 +28678,9 @@
       <c r="AF258" s="31">
         <v>0</v>
       </c>
-      <c r="AG258" s="32"/>
+      <c r="AG258" s="32">
+        <v>1</v>
+      </c>
       <c r="AH258" s="6">
         <v>52</v>
       </c>
@@ -28771,7 +28785,9 @@
       <c r="AF259" s="31">
         <v>0</v>
       </c>
-      <c r="AG259" s="32"/>
+      <c r="AG259" s="32">
+        <v>1</v>
+      </c>
       <c r="AH259" s="6">
         <v>52</v>
       </c>
@@ -28876,7 +28892,9 @@
       <c r="AF260" s="31">
         <v>0</v>
       </c>
-      <c r="AG260" s="32"/>
+      <c r="AG260" s="32">
+        <v>1</v>
+      </c>
       <c r="AH260" s="6">
         <v>52</v>
       </c>
@@ -28981,7 +28999,9 @@
       <c r="AF261" s="31">
         <v>0</v>
       </c>
-      <c r="AG261" s="32"/>
+      <c r="AG261" s="32">
+        <v>1</v>
+      </c>
       <c r="AH261" s="6">
         <v>52</v>
       </c>
@@ -29086,7 +29106,9 @@
       <c r="AF262" s="31">
         <v>0</v>
       </c>
-      <c r="AG262" s="32"/>
+      <c r="AG262" s="32">
+        <v>1</v>
+      </c>
       <c r="AH262" s="6">
         <v>52</v>
       </c>
@@ -29112,7 +29134,7 @@
         <v>0</v>
       </c>
       <c r="G263" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H263" s="3">
         <v>0</v>
@@ -29122,7 +29144,7 @@
       </c>
       <c r="J263" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K263" s="3">
         <v>1</v>
@@ -29191,7 +29213,9 @@
       <c r="AF263" s="31">
         <v>0</v>
       </c>
-      <c r="AG263" s="32"/>
+      <c r="AG263" s="32">
+        <v>1</v>
+      </c>
       <c r="AH263" s="6">
         <v>52</v>
       </c>
@@ -29211,10 +29235,14 @@
       </c>
       <c r="E264" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F264" s="3"/>
-      <c r="G264" s="3"/>
+        <v>117</v>
+      </c>
+      <c r="F264" s="3">
+        <v>0</v>
+      </c>
+      <c r="G264" s="3">
+        <v>0</v>
+      </c>
       <c r="H264" s="3">
         <v>0</v>
       </c>
@@ -29225,30 +29253,64 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K264" s="3"/>
-      <c r="L264" s="3"/>
-      <c r="M264" s="4"/>
+      <c r="K264" s="3">
+        <v>0</v>
+      </c>
+      <c r="L264" s="3">
+        <v>1</v>
+      </c>
+      <c r="M264" s="4">
+        <v>2</v>
+      </c>
       <c r="N264" s="7">
         <v>0</v>
       </c>
-      <c r="O264" s="5"/>
-      <c r="P264" s="5"/>
+      <c r="O264" s="5">
+        <v>3</v>
+      </c>
+      <c r="P264" s="5">
+        <v>0</v>
+      </c>
       <c r="Q264" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R264" s="4"/>
-      <c r="S264" s="4"/>
-      <c r="T264" s="5"/>
-      <c r="U264" s="4"/>
-      <c r="V264" s="5"/>
-      <c r="W264" s="4"/>
-      <c r="X264" s="4"/>
-      <c r="Y264" s="4"/>
-      <c r="Z264" s="5"/>
-      <c r="AA264" s="4"/>
-      <c r="AB264" s="5"/>
-      <c r="AC264" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="R264" s="4">
+        <v>7</v>
+      </c>
+      <c r="S264" s="4">
+        <v>60</v>
+      </c>
+      <c r="T264" s="5">
+        <v>11</v>
+      </c>
+      <c r="U264" s="4">
+        <v>6</v>
+      </c>
+      <c r="V264" s="5">
+        <v>8</v>
+      </c>
+      <c r="W264" s="4">
+        <v>7</v>
+      </c>
+      <c r="X264" s="4">
+        <v>10</v>
+      </c>
+      <c r="Y264" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z264" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA264" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB264" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC264" s="3">
+        <v>0</v>
+      </c>
       <c r="AD264" s="3">
         <v>0</v>
       </c>
@@ -29258,7 +29320,9 @@
       <c r="AF264" s="31">
         <v>0</v>
       </c>
-      <c r="AG264" s="32"/>
+      <c r="AG264" s="32">
+        <v>0</v>
+      </c>
       <c r="AH264" s="6">
         <v>61</v>
       </c>
@@ -29278,10 +29342,14 @@
       </c>
       <c r="E265" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F265" s="3"/>
-      <c r="G265" s="3"/>
+        <v>112</v>
+      </c>
+      <c r="F265" s="3">
+        <v>0</v>
+      </c>
+      <c r="G265" s="3">
+        <v>1</v>
+      </c>
       <c r="H265" s="3">
         <v>0</v>
       </c>
@@ -29290,32 +29358,66 @@
       </c>
       <c r="J265" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K265" s="3"/>
-      <c r="L265" s="3"/>
-      <c r="M265" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K265" s="3">
+        <v>2</v>
+      </c>
+      <c r="L265" s="3">
+        <v>5</v>
+      </c>
+      <c r="M265" s="4">
+        <v>8</v>
+      </c>
       <c r="N265" s="7">
         <v>0</v>
       </c>
-      <c r="O265" s="5"/>
-      <c r="P265" s="5"/>
+      <c r="O265" s="5">
+        <v>4</v>
+      </c>
+      <c r="P265" s="5">
+        <v>1</v>
+      </c>
       <c r="Q265" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R265" s="4"/>
-      <c r="S265" s="4"/>
-      <c r="T265" s="5"/>
-      <c r="U265" s="4"/>
-      <c r="V265" s="5"/>
-      <c r="W265" s="4"/>
-      <c r="X265" s="4"/>
-      <c r="Y265" s="4"/>
-      <c r="Z265" s="5"/>
-      <c r="AA265" s="4"/>
-      <c r="AB265" s="5"/>
-      <c r="AC265" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="R265" s="4">
+        <v>1</v>
+      </c>
+      <c r="S265" s="4">
+        <v>45</v>
+      </c>
+      <c r="T265" s="5">
+        <v>15</v>
+      </c>
+      <c r="U265" s="4">
+        <v>2</v>
+      </c>
+      <c r="V265" s="5">
+        <v>2</v>
+      </c>
+      <c r="W265" s="4">
+        <v>7</v>
+      </c>
+      <c r="X265" s="4">
+        <v>19</v>
+      </c>
+      <c r="Y265" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z265" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA265" s="4">
+        <v>3</v>
+      </c>
+      <c r="AB265" s="5">
+        <v>2</v>
+      </c>
+      <c r="AC265" s="3">
+        <v>2</v>
+      </c>
       <c r="AD265" s="3">
         <v>0</v>
       </c>
@@ -29325,7 +29427,9 @@
       <c r="AF265" s="31">
         <v>0</v>
       </c>
-      <c r="AG265" s="32"/>
+      <c r="AG265" s="32">
+        <v>0</v>
+      </c>
       <c r="AH265" s="6">
         <v>61</v>
       </c>
@@ -29345,10 +29449,14 @@
       </c>
       <c r="E266" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F266" s="3"/>
-      <c r="G266" s="3"/>
+        <v>98</v>
+      </c>
+      <c r="F266" s="3">
+        <v>0</v>
+      </c>
+      <c r="G266" s="3">
+        <v>0</v>
+      </c>
       <c r="H266" s="3">
         <v>0</v>
       </c>
@@ -29359,30 +29467,64 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K266" s="3"/>
-      <c r="L266" s="3"/>
-      <c r="M266" s="4"/>
+      <c r="K266" s="3">
+        <v>0</v>
+      </c>
+      <c r="L266" s="3">
+        <v>2</v>
+      </c>
+      <c r="M266" s="4">
+        <v>0</v>
+      </c>
       <c r="N266" s="7">
         <v>0</v>
       </c>
-      <c r="O266" s="5"/>
-      <c r="P266" s="5"/>
+      <c r="O266" s="5">
+        <v>1</v>
+      </c>
+      <c r="P266" s="5">
+        <v>0</v>
+      </c>
       <c r="Q266" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R266" s="4"/>
-      <c r="S266" s="4"/>
-      <c r="T266" s="5"/>
-      <c r="U266" s="4"/>
-      <c r="V266" s="5"/>
-      <c r="W266" s="4"/>
-      <c r="X266" s="4"/>
-      <c r="Y266" s="4"/>
-      <c r="Z266" s="5"/>
-      <c r="AA266" s="4"/>
-      <c r="AB266" s="5"/>
-      <c r="AC266" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="R266" s="4">
+        <v>0</v>
+      </c>
+      <c r="S266" s="4">
+        <v>52</v>
+      </c>
+      <c r="T266" s="5">
+        <v>14</v>
+      </c>
+      <c r="U266" s="4">
+        <v>0</v>
+      </c>
+      <c r="V266" s="5">
+        <v>4</v>
+      </c>
+      <c r="W266" s="4">
+        <v>1</v>
+      </c>
+      <c r="X266" s="4">
+        <v>6</v>
+      </c>
+      <c r="Y266" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z266" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA266" s="4">
+        <v>10</v>
+      </c>
+      <c r="AB266" s="5">
+        <v>6</v>
+      </c>
+      <c r="AC266" s="3">
+        <v>3</v>
+      </c>
       <c r="AD266" s="3">
         <v>0</v>
       </c>
@@ -29392,7 +29534,9 @@
       <c r="AF266" s="31">
         <v>0</v>
       </c>
-      <c r="AG266" s="32"/>
+      <c r="AG266" s="32">
+        <v>0</v>
+      </c>
       <c r="AH266" s="6">
         <v>61</v>
       </c>
@@ -29412,10 +29556,14 @@
       </c>
       <c r="E267" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F267" s="3"/>
-      <c r="G267" s="3"/>
+        <v>127</v>
+      </c>
+      <c r="F267" s="3">
+        <v>0</v>
+      </c>
+      <c r="G267" s="3">
+        <v>1</v>
+      </c>
       <c r="H267" s="3">
         <v>0</v>
       </c>
@@ -29424,32 +29572,66 @@
       </c>
       <c r="J267" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K267" s="3"/>
-      <c r="L267" s="3"/>
-      <c r="M267" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K267" s="3">
+        <v>2</v>
+      </c>
+      <c r="L267" s="3">
+        <v>4</v>
+      </c>
+      <c r="M267" s="4">
+        <v>3</v>
+      </c>
       <c r="N267" s="7">
         <v>0</v>
       </c>
-      <c r="O267" s="5"/>
-      <c r="P267" s="5"/>
+      <c r="O267" s="5">
+        <v>3</v>
+      </c>
+      <c r="P267" s="5">
+        <v>3</v>
+      </c>
       <c r="Q267" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R267" s="4"/>
-      <c r="S267" s="4"/>
-      <c r="T267" s="5"/>
-      <c r="U267" s="4"/>
-      <c r="V267" s="5"/>
-      <c r="W267" s="4"/>
-      <c r="X267" s="4"/>
-      <c r="Y267" s="4"/>
-      <c r="Z267" s="5"/>
-      <c r="AA267" s="4"/>
-      <c r="AB267" s="5"/>
-      <c r="AC267" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="R267" s="4">
+        <v>2</v>
+      </c>
+      <c r="S267" s="4">
+        <v>66</v>
+      </c>
+      <c r="T267" s="5">
+        <v>19</v>
+      </c>
+      <c r="U267" s="4">
+        <v>5</v>
+      </c>
+      <c r="V267" s="5">
+        <v>9</v>
+      </c>
+      <c r="W267" s="4">
+        <v>3</v>
+      </c>
+      <c r="X267" s="4">
+        <v>12</v>
+      </c>
+      <c r="Y267" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z267" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA267" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB267" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC267" s="3">
+        <v>2</v>
+      </c>
       <c r="AD267" s="3">
         <v>0</v>
       </c>
@@ -29459,7 +29641,9 @@
       <c r="AF267" s="31">
         <v>0</v>
       </c>
-      <c r="AG267" s="32"/>
+      <c r="AG267" s="32">
+        <v>0</v>
+      </c>
       <c r="AH267" s="6">
         <v>61</v>
       </c>
@@ -29479,10 +29663,14 @@
       </c>
       <c r="E268" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F268" s="3"/>
-      <c r="G268" s="3"/>
+        <v>95</v>
+      </c>
+      <c r="F268" s="3">
+        <v>0</v>
+      </c>
+      <c r="G268" s="3">
+        <v>2</v>
+      </c>
       <c r="H268" s="3">
         <v>0</v>
       </c>
@@ -29491,32 +29679,66 @@
       </c>
       <c r="J268" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K268" s="3"/>
-      <c r="L268" s="3"/>
-      <c r="M268" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="K268" s="3">
+        <v>0</v>
+      </c>
+      <c r="L268" s="3">
+        <v>2</v>
+      </c>
+      <c r="M268" s="4">
+        <v>3</v>
+      </c>
       <c r="N268" s="7">
         <v>0</v>
       </c>
-      <c r="O268" s="5"/>
-      <c r="P268" s="5"/>
+      <c r="O268" s="5">
+        <v>0</v>
+      </c>
+      <c r="P268" s="5">
+        <v>3</v>
+      </c>
       <c r="Q268" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R268" s="4"/>
-      <c r="S268" s="4"/>
-      <c r="T268" s="5"/>
-      <c r="U268" s="4"/>
-      <c r="V268" s="5"/>
-      <c r="W268" s="4"/>
-      <c r="X268" s="4"/>
-      <c r="Y268" s="4"/>
-      <c r="Z268" s="5"/>
-      <c r="AA268" s="4"/>
-      <c r="AB268" s="5"/>
-      <c r="AC268" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="R268" s="4">
+        <v>2</v>
+      </c>
+      <c r="S268" s="4">
+        <v>42</v>
+      </c>
+      <c r="T268" s="5">
+        <v>15</v>
+      </c>
+      <c r="U268" s="4">
+        <v>2</v>
+      </c>
+      <c r="V268" s="5">
+        <v>5</v>
+      </c>
+      <c r="W268" s="4">
+        <v>6</v>
+      </c>
+      <c r="X268" s="4">
+        <v>13</v>
+      </c>
+      <c r="Y268" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z268" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA268" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB268" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC268" s="3">
+        <v>1</v>
+      </c>
       <c r="AD268" s="3">
         <v>0</v>
       </c>
@@ -29526,7 +29748,9 @@
       <c r="AF268" s="31">
         <v>0</v>
       </c>
-      <c r="AG268" s="32"/>
+      <c r="AG268" s="32">
+        <v>0</v>
+      </c>
       <c r="AH268" s="6">
         <v>61</v>
       </c>
@@ -29546,10 +29770,14 @@
       </c>
       <c r="E269" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F269" s="3"/>
-      <c r="G269" s="3"/>
+        <v>109</v>
+      </c>
+      <c r="F269" s="3">
+        <v>1</v>
+      </c>
+      <c r="G269" s="3">
+        <v>1</v>
+      </c>
       <c r="H269" s="3">
         <v>0</v>
       </c>
@@ -29558,32 +29786,66 @@
       </c>
       <c r="J269" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K269" s="3"/>
-      <c r="L269" s="3"/>
-      <c r="M269" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="K269" s="3">
+        <v>0</v>
+      </c>
+      <c r="L269" s="3">
+        <v>0</v>
+      </c>
+      <c r="M269" s="4">
+        <v>7</v>
+      </c>
       <c r="N269" s="7">
         <v>0</v>
       </c>
-      <c r="O269" s="5"/>
-      <c r="P269" s="5"/>
+      <c r="O269" s="5">
+        <v>3</v>
+      </c>
+      <c r="P269" s="5">
+        <v>3</v>
+      </c>
       <c r="Q269" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R269" s="4"/>
-      <c r="S269" s="4"/>
-      <c r="T269" s="5"/>
-      <c r="U269" s="4"/>
-      <c r="V269" s="5"/>
-      <c r="W269" s="4"/>
-      <c r="X269" s="4"/>
-      <c r="Y269" s="4"/>
-      <c r="Z269" s="5"/>
-      <c r="AA269" s="4"/>
-      <c r="AB269" s="5"/>
-      <c r="AC269" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="R269" s="4">
+        <v>0</v>
+      </c>
+      <c r="S269" s="4">
+        <v>62</v>
+      </c>
+      <c r="T269" s="5">
+        <v>8</v>
+      </c>
+      <c r="U269" s="4">
+        <v>2</v>
+      </c>
+      <c r="V269" s="5">
+        <v>5</v>
+      </c>
+      <c r="W269" s="4">
+        <v>2</v>
+      </c>
+      <c r="X269" s="4">
+        <v>5</v>
+      </c>
+      <c r="Y269" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z269" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA269" s="4">
+        <v>9</v>
+      </c>
+      <c r="AB269" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC269" s="3">
+        <v>2</v>
+      </c>
       <c r="AD269" s="3">
         <v>0</v>
       </c>
@@ -29593,7 +29855,9 @@
       <c r="AF269" s="31">
         <v>0</v>
       </c>
-      <c r="AG269" s="32"/>
+      <c r="AG269" s="32">
+        <v>0</v>
+      </c>
       <c r="AH269" s="6">
         <v>61</v>
       </c>
@@ -29613,10 +29877,14 @@
       </c>
       <c r="E270" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F270" s="3"/>
-      <c r="G270" s="3"/>
+        <v>84</v>
+      </c>
+      <c r="F270" s="3">
+        <v>0</v>
+      </c>
+      <c r="G270" s="3">
+        <v>1</v>
+      </c>
       <c r="H270" s="3">
         <v>0</v>
       </c>
@@ -29625,32 +29893,66 @@
       </c>
       <c r="J270" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K270" s="3"/>
-      <c r="L270" s="3"/>
-      <c r="M270" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K270" s="3">
+        <v>0</v>
+      </c>
+      <c r="L270" s="3">
+        <v>2</v>
+      </c>
+      <c r="M270" s="4">
+        <v>6</v>
+      </c>
       <c r="N270" s="7">
         <v>0</v>
       </c>
-      <c r="O270" s="5"/>
-      <c r="P270" s="5"/>
+      <c r="O270" s="5">
+        <v>2</v>
+      </c>
+      <c r="P270" s="5">
+        <v>0</v>
+      </c>
       <c r="Q270" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R270" s="4"/>
-      <c r="S270" s="4"/>
-      <c r="T270" s="5"/>
-      <c r="U270" s="4"/>
-      <c r="V270" s="5"/>
-      <c r="W270" s="4"/>
-      <c r="X270" s="4"/>
-      <c r="Y270" s="4"/>
-      <c r="Z270" s="5"/>
-      <c r="AA270" s="4"/>
-      <c r="AB270" s="5"/>
-      <c r="AC270" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="R270" s="4">
+        <v>0</v>
+      </c>
+      <c r="S270" s="4">
+        <v>39</v>
+      </c>
+      <c r="T270" s="5">
+        <v>9</v>
+      </c>
+      <c r="U270" s="4">
+        <v>3</v>
+      </c>
+      <c r="V270" s="5">
+        <v>5</v>
+      </c>
+      <c r="W270" s="4">
+        <v>6</v>
+      </c>
+      <c r="X270" s="4">
+        <v>6</v>
+      </c>
+      <c r="Y270" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z270" s="5">
+        <v>3</v>
+      </c>
+      <c r="AA270" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB270" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC270" s="3">
+        <v>3</v>
+      </c>
       <c r="AD270" s="3">
         <v>0</v>
       </c>
@@ -29660,7 +29962,9 @@
       <c r="AF270" s="31">
         <v>0</v>
       </c>
-      <c r="AG270" s="32"/>
+      <c r="AG270" s="32">
+        <v>3</v>
+      </c>
       <c r="AH270" s="6">
         <v>61</v>
       </c>
@@ -29680,10 +29984,14 @@
       </c>
       <c r="E271" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F271" s="3"/>
-      <c r="G271" s="3"/>
+        <v>126</v>
+      </c>
+      <c r="F271" s="3">
+        <v>0</v>
+      </c>
+      <c r="G271" s="3">
+        <v>3</v>
+      </c>
       <c r="H271" s="3">
         <v>0</v>
       </c>
@@ -29692,32 +30000,66 @@
       </c>
       <c r="J271" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K271" s="3"/>
-      <c r="L271" s="3"/>
-      <c r="M271" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="K271" s="3">
+        <v>1</v>
+      </c>
+      <c r="L271" s="3">
+        <v>7</v>
+      </c>
+      <c r="M271" s="4">
+        <v>5</v>
+      </c>
       <c r="N271" s="7">
         <v>0</v>
       </c>
-      <c r="O271" s="5"/>
-      <c r="P271" s="5"/>
+      <c r="O271" s="5">
+        <v>4</v>
+      </c>
+      <c r="P271" s="5">
+        <v>3</v>
+      </c>
       <c r="Q271" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R271" s="4"/>
-      <c r="S271" s="4"/>
-      <c r="T271" s="5"/>
-      <c r="U271" s="4"/>
-      <c r="V271" s="5"/>
-      <c r="W271" s="4"/>
-      <c r="X271" s="4"/>
-      <c r="Y271" s="4"/>
-      <c r="Z271" s="5"/>
-      <c r="AA271" s="4"/>
-      <c r="AB271" s="5"/>
-      <c r="AC271" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="R271" s="4">
+        <v>3</v>
+      </c>
+      <c r="S271" s="4">
+        <v>49</v>
+      </c>
+      <c r="T271" s="5">
+        <v>25</v>
+      </c>
+      <c r="U271" s="4">
+        <v>2</v>
+      </c>
+      <c r="V271" s="5">
+        <v>6</v>
+      </c>
+      <c r="W271" s="4">
+        <v>5</v>
+      </c>
+      <c r="X271" s="4">
+        <v>17</v>
+      </c>
+      <c r="Y271" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z271" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA271" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB271" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC271" s="3">
+        <v>6</v>
+      </c>
       <c r="AD271" s="3">
         <v>0</v>
       </c>
@@ -29727,7 +30069,9 @@
       <c r="AF271" s="31">
         <v>0</v>
       </c>
-      <c r="AG271" s="32"/>
+      <c r="AG271" s="32">
+        <v>3</v>
+      </c>
       <c r="AH271" s="6">
         <v>61</v>
       </c>
@@ -29747,10 +30091,14 @@
       </c>
       <c r="E272" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F272" s="3"/>
-      <c r="G272" s="3"/>
+        <v>106</v>
+      </c>
+      <c r="F272" s="3">
+        <v>0</v>
+      </c>
+      <c r="G272" s="3">
+        <v>1</v>
+      </c>
       <c r="H272" s="3">
         <v>0</v>
       </c>
@@ -29759,32 +30107,66 @@
       </c>
       <c r="J272" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K272" s="3"/>
-      <c r="L272" s="3"/>
-      <c r="M272" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K272" s="3">
+        <v>0</v>
+      </c>
+      <c r="L272" s="3">
+        <v>1</v>
+      </c>
+      <c r="M272" s="4">
+        <v>6</v>
+      </c>
       <c r="N272" s="7">
         <v>0</v>
       </c>
-      <c r="O272" s="5"/>
-      <c r="P272" s="5"/>
+      <c r="O272" s="5">
+        <v>7</v>
+      </c>
+      <c r="P272" s="5">
+        <v>2</v>
+      </c>
       <c r="Q272" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R272" s="4"/>
-      <c r="S272" s="4"/>
-      <c r="T272" s="5"/>
-      <c r="U272" s="4"/>
-      <c r="V272" s="5"/>
-      <c r="W272" s="4"/>
-      <c r="X272" s="4"/>
-      <c r="Y272" s="4"/>
-      <c r="Z272" s="5"/>
-      <c r="AA272" s="4"/>
-      <c r="AB272" s="5"/>
-      <c r="AC272" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="R272" s="4">
+        <v>0</v>
+      </c>
+      <c r="S272" s="4">
+        <v>42</v>
+      </c>
+      <c r="T272" s="5">
+        <v>19</v>
+      </c>
+      <c r="U272" s="4">
+        <v>0</v>
+      </c>
+      <c r="V272" s="5">
+        <v>2</v>
+      </c>
+      <c r="W272" s="4">
+        <v>0</v>
+      </c>
+      <c r="X272" s="4">
+        <v>8</v>
+      </c>
+      <c r="Y272" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z272" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA272" s="4">
+        <v>14</v>
+      </c>
+      <c r="AB272" s="5">
+        <v>4</v>
+      </c>
+      <c r="AC272" s="3">
+        <v>1</v>
+      </c>
       <c r="AD272" s="3">
         <v>0</v>
       </c>
@@ -29794,7 +30176,9 @@
       <c r="AF272" s="31">
         <v>0</v>
       </c>
-      <c r="AG272" s="32"/>
+      <c r="AG272" s="32">
+        <v>3</v>
+      </c>
       <c r="AH272" s="6">
         <v>61</v>
       </c>
@@ -29814,10 +30198,14 @@
       </c>
       <c r="E273" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F273" s="3"/>
-      <c r="G273" s="3"/>
+        <v>110</v>
+      </c>
+      <c r="F273" s="3">
+        <v>0</v>
+      </c>
+      <c r="G273" s="3">
+        <v>3</v>
+      </c>
       <c r="H273" s="3">
         <v>0</v>
       </c>
@@ -29826,32 +30214,66 @@
       </c>
       <c r="J273" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K273" s="3"/>
-      <c r="L273" s="3"/>
-      <c r="M273" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="K273" s="3">
+        <v>2</v>
+      </c>
+      <c r="L273" s="3">
+        <v>3</v>
+      </c>
+      <c r="M273" s="4">
+        <v>5</v>
+      </c>
       <c r="N273" s="7">
-        <v>0</v>
-      </c>
-      <c r="O273" s="5"/>
-      <c r="P273" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="O273" s="5">
+        <v>7</v>
+      </c>
+      <c r="P273" s="5">
+        <v>1</v>
+      </c>
       <c r="Q273" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R273" s="4"/>
-      <c r="S273" s="4"/>
-      <c r="T273" s="5"/>
-      <c r="U273" s="4"/>
-      <c r="V273" s="5"/>
-      <c r="W273" s="4"/>
-      <c r="X273" s="4"/>
-      <c r="Y273" s="4"/>
-      <c r="Z273" s="5"/>
-      <c r="AA273" s="4"/>
-      <c r="AB273" s="5"/>
-      <c r="AC273" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="R273" s="4">
+        <v>2</v>
+      </c>
+      <c r="S273" s="4">
+        <v>50</v>
+      </c>
+      <c r="T273" s="5">
+        <v>13</v>
+      </c>
+      <c r="U273" s="4">
+        <v>1</v>
+      </c>
+      <c r="V273" s="5">
+        <v>3</v>
+      </c>
+      <c r="W273" s="4">
+        <v>7</v>
+      </c>
+      <c r="X273" s="4">
+        <v>17</v>
+      </c>
+      <c r="Y273" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z273" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA273" s="4">
+        <v>2</v>
+      </c>
+      <c r="AB273" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC273" s="3">
+        <v>0</v>
+      </c>
       <c r="AD273" s="3">
         <v>0</v>
       </c>
@@ -29861,7 +30283,9 @@
       <c r="AF273" s="31">
         <v>0</v>
       </c>
-      <c r="AG273" s="32"/>
+      <c r="AG273" s="32">
+        <v>3</v>
+      </c>
       <c r="AH273" s="6">
         <v>61</v>
       </c>
@@ -29881,10 +30305,14 @@
       </c>
       <c r="E274" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F274" s="3"/>
-      <c r="G274" s="3"/>
+        <v>91</v>
+      </c>
+      <c r="F274" s="3">
+        <v>0</v>
+      </c>
+      <c r="G274" s="3">
+        <v>1</v>
+      </c>
       <c r="H274" s="3">
         <v>0</v>
       </c>
@@ -29893,32 +30321,66 @@
       </c>
       <c r="J274" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K274" s="3"/>
-      <c r="L274" s="3"/>
-      <c r="M274" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K274" s="3">
+        <v>1</v>
+      </c>
+      <c r="L274" s="3">
+        <v>3</v>
+      </c>
+      <c r="M274" s="4">
+        <v>8</v>
+      </c>
       <c r="N274" s="7">
-        <v>0</v>
-      </c>
-      <c r="O274" s="5"/>
-      <c r="P274" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="O274" s="5">
+        <v>5</v>
+      </c>
+      <c r="P274" s="5">
+        <v>4</v>
+      </c>
       <c r="Q274" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R274" s="4"/>
-      <c r="S274" s="4"/>
-      <c r="T274" s="5"/>
-      <c r="U274" s="4"/>
-      <c r="V274" s="5"/>
-      <c r="W274" s="4"/>
-      <c r="X274" s="4"/>
-      <c r="Y274" s="4"/>
-      <c r="Z274" s="5"/>
-      <c r="AA274" s="4"/>
-      <c r="AB274" s="5"/>
-      <c r="AC274" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="R274" s="4">
+        <v>2</v>
+      </c>
+      <c r="S274" s="4">
+        <v>32</v>
+      </c>
+      <c r="T274" s="5">
+        <v>8</v>
+      </c>
+      <c r="U274" s="4">
+        <v>4</v>
+      </c>
+      <c r="V274" s="5">
+        <v>6</v>
+      </c>
+      <c r="W274" s="4">
+        <v>8</v>
+      </c>
+      <c r="X274" s="4">
+        <v>10</v>
+      </c>
+      <c r="Y274" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z274" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA274" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB274" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC274" s="3">
+        <v>3</v>
+      </c>
       <c r="AD274" s="3">
         <v>0</v>
       </c>
@@ -29928,7 +30390,9 @@
       <c r="AF274" s="31">
         <v>0</v>
       </c>
-      <c r="AG274" s="32"/>
+      <c r="AG274" s="32">
+        <v>3</v>
+      </c>
       <c r="AH274" s="6">
         <v>61</v>
       </c>
@@ -29948,10 +30412,14 @@
       </c>
       <c r="E275" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F275" s="3"/>
-      <c r="G275" s="3"/>
+        <v>79</v>
+      </c>
+      <c r="F275" s="3">
+        <v>0</v>
+      </c>
+      <c r="G275" s="3">
+        <v>0</v>
+      </c>
       <c r="H275" s="3">
         <v>0</v>
       </c>
@@ -29962,30 +30430,64 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K275" s="3"/>
-      <c r="L275" s="3"/>
-      <c r="M275" s="4"/>
+      <c r="K275" s="3">
+        <v>3</v>
+      </c>
+      <c r="L275" s="3">
+        <v>3</v>
+      </c>
+      <c r="M275" s="4">
+        <v>2</v>
+      </c>
       <c r="N275" s="7">
         <v>0</v>
       </c>
-      <c r="O275" s="5"/>
-      <c r="P275" s="5"/>
+      <c r="O275" s="5">
+        <v>2</v>
+      </c>
+      <c r="P275" s="5">
+        <v>2</v>
+      </c>
       <c r="Q275" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="R275" s="4"/>
-      <c r="S275" s="4"/>
-      <c r="T275" s="5"/>
-      <c r="U275" s="4"/>
-      <c r="V275" s="5"/>
-      <c r="W275" s="4"/>
-      <c r="X275" s="4"/>
-      <c r="Y275" s="4"/>
-      <c r="Z275" s="5"/>
-      <c r="AA275" s="4"/>
-      <c r="AB275" s="5"/>
-      <c r="AC275" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="R275" s="4">
+        <v>3</v>
+      </c>
+      <c r="S275" s="4">
+        <v>31</v>
+      </c>
+      <c r="T275" s="5">
+        <v>10</v>
+      </c>
+      <c r="U275" s="4">
+        <v>3</v>
+      </c>
+      <c r="V275" s="5">
+        <v>4</v>
+      </c>
+      <c r="W275" s="4">
+        <v>6</v>
+      </c>
+      <c r="X275" s="4">
+        <v>12</v>
+      </c>
+      <c r="Y275" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z275" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA275" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB275" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC275" s="3">
+        <v>3</v>
+      </c>
       <c r="AD275" s="3">
         <v>0</v>
       </c>
@@ -29995,7 +30497,9 @@
       <c r="AF275" s="31">
         <v>0</v>
       </c>
-      <c r="AG275" s="32"/>
+      <c r="AG275" s="32">
+        <v>3</v>
+      </c>
       <c r="AH275" s="6">
         <v>61</v>
       </c>

--- a/Fudbal Bezanija Termini.xlsx
+++ b/Fudbal Bezanija Termini.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beoog\Desktop\Fudbal Bezanija\Sajt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{115DB6D5-4A32-4F3A-BC51-19A5304518D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A55294-08C0-4C52-8B3C-1CFC241D821C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27405" yWindow="1395" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fudbal Bezanija Termini" sheetId="1" r:id="rId1"/>
@@ -20908,10 +20908,10 @@
         <v>0</v>
       </c>
       <c r="K186" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L186" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M186" s="4">
         <v>6</v>
@@ -25062,7 +25062,7 @@
       </c>
       <c r="E225" s="3">
         <f t="shared" si="15"/>
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F225" s="3">
         <v>0</v>
@@ -25133,7 +25133,7 @@
         <v>1</v>
       </c>
       <c r="AB225" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC225" s="3">
         <v>0</v>

--- a/Fudbal Bezanija Termini.xlsx
+++ b/Fudbal Bezanija Termini.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beoog\Desktop\Fudbal Bezanija\Sajt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A55294-08C0-4C52-8B3C-1CFC241D821C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B67471-3706-481E-863D-C2BA45D04B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27405" yWindow="1395" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fudbal Bezanija Termini" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="74">
   <si>
     <t>No.</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>Nenad Tegijev Vidakovic</t>
+  </si>
+  <si>
+    <t>Players</t>
   </si>
 </sst>
 </file>
@@ -1033,7 +1036,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ370"/>
+  <dimension ref="A1:AK370"/>
   <sheetFormatPr defaultColWidth="7.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.109375" style="1" bestFit="1" customWidth="1"/>
@@ -1069,11 +1072,12 @@
     <col min="31" max="31" width="9.33203125" style="1" customWidth="1"/>
     <col min="32" max="32" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="7.44140625" style="1"/>
+    <col min="34" max="34" width="7.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="7.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="2" customFormat="1" ht="31.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" s="2" customFormat="1" ht="31.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1173,11 +1177,14 @@
       <c r="AG1" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="AH1" s="15" t="s">
+      <c r="AH1" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI1" s="15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="25">
         <v>1</v>
       </c>
@@ -1280,11 +1287,14 @@
       <c r="AG2" s="31">
         <v>3</v>
       </c>
-      <c r="AH2" s="12">
+      <c r="AH2" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI2" s="12">
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="18">
         <v>1</v>
       </c>
@@ -1387,11 +1397,14 @@
       <c r="AG3" s="32">
         <v>3</v>
       </c>
-      <c r="AH3" s="12">
+      <c r="AH3" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI3" s="12">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="25">
         <v>1</v>
       </c>
@@ -1494,11 +1507,14 @@
       <c r="AG4" s="32">
         <v>3</v>
       </c>
-      <c r="AH4" s="12">
+      <c r="AH4" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI4" s="12">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>1</v>
       </c>
@@ -1601,11 +1617,14 @@
       <c r="AG5" s="32">
         <v>3</v>
       </c>
-      <c r="AH5" s="12">
+      <c r="AH5" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI5" s="12">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
         <v>1</v>
       </c>
@@ -1708,11 +1727,14 @@
       <c r="AG6" s="32">
         <v>3</v>
       </c>
-      <c r="AH6" s="12">
+      <c r="AH6" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI6" s="12">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="18">
         <v>1</v>
       </c>
@@ -1815,11 +1837,14 @@
       <c r="AG7" s="32">
         <v>0</v>
       </c>
-      <c r="AH7" s="12">
+      <c r="AH7" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI7" s="12">
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
         <v>1</v>
       </c>
@@ -1922,11 +1947,14 @@
       <c r="AG8" s="32">
         <v>0</v>
       </c>
-      <c r="AH8" s="12">
+      <c r="AH8" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI8" s="12">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="18">
         <v>1</v>
       </c>
@@ -2029,11 +2057,14 @@
       <c r="AG9" s="32">
         <v>0</v>
       </c>
-      <c r="AH9" s="12">
+      <c r="AH9" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI9" s="12">
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
         <v>1</v>
       </c>
@@ -2136,11 +2167,14 @@
       <c r="AG10" s="32">
         <v>0</v>
       </c>
-      <c r="AH10" s="12">
+      <c r="AH10" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI10" s="12">
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="18">
         <v>1</v>
       </c>
@@ -2243,11 +2277,14 @@
       <c r="AG11" s="32">
         <v>0</v>
       </c>
-      <c r="AH11" s="12">
+      <c r="AH11" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI11" s="12">
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="18">
         <v>2</v>
       </c>
@@ -2350,11 +2387,14 @@
       <c r="AG12" s="32">
         <v>0</v>
       </c>
-      <c r="AH12" s="6">
+      <c r="AH12" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI12" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="18">
         <v>2</v>
       </c>
@@ -2457,11 +2497,14 @@
       <c r="AG13" s="32">
         <v>0</v>
       </c>
-      <c r="AH13" s="6">
+      <c r="AH13" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI13" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" s="18">
         <v>2</v>
       </c>
@@ -2564,11 +2607,14 @@
       <c r="AG14" s="32">
         <v>0</v>
       </c>
-      <c r="AH14" s="6">
+      <c r="AH14" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI14" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" s="18">
         <v>2</v>
       </c>
@@ -2671,11 +2717,14 @@
       <c r="AG15" s="32">
         <v>0</v>
       </c>
-      <c r="AH15" s="6">
+      <c r="AH15" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI15" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" s="18">
         <v>2</v>
       </c>
@@ -2778,11 +2827,14 @@
       <c r="AG16" s="32">
         <v>0</v>
       </c>
-      <c r="AH16" s="6">
+      <c r="AH16" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI16" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" s="18">
         <v>2</v>
       </c>
@@ -2885,11 +2937,14 @@
       <c r="AG17" s="32">
         <v>3</v>
       </c>
-      <c r="AH17" s="6">
+      <c r="AH17" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI17" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" s="18">
         <v>2</v>
       </c>
@@ -2992,11 +3047,14 @@
       <c r="AG18" s="32">
         <v>3</v>
       </c>
-      <c r="AH18" s="6">
+      <c r="AH18" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI18" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" s="18">
         <v>2</v>
       </c>
@@ -3099,11 +3157,14 @@
       <c r="AG19" s="32">
         <v>3</v>
       </c>
-      <c r="AH19" s="6">
+      <c r="AH19" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI19" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A20" s="18">
         <v>2</v>
       </c>
@@ -3206,11 +3267,14 @@
       <c r="AG20" s="32">
         <v>3</v>
       </c>
-      <c r="AH20" s="6">
+      <c r="AH20" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI20" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A21" s="18">
         <v>2</v>
       </c>
@@ -3313,11 +3377,14 @@
       <c r="AG21" s="32">
         <v>3</v>
       </c>
-      <c r="AH21" s="6">
+      <c r="AH21" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI21" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A22" s="18">
         <v>3</v>
       </c>
@@ -3420,11 +3487,14 @@
       <c r="AG22" s="32">
         <v>0</v>
       </c>
-      <c r="AH22" s="6">
+      <c r="AH22" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI22" s="6">
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A23" s="18">
         <v>3</v>
       </c>
@@ -3527,11 +3597,14 @@
       <c r="AG23" s="32">
         <v>0</v>
       </c>
-      <c r="AH23" s="6">
+      <c r="AH23" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI23" s="6">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A24" s="18">
         <v>3</v>
       </c>
@@ -3634,11 +3707,14 @@
       <c r="AG24" s="32">
         <v>0</v>
       </c>
-      <c r="AH24" s="6">
+      <c r="AH24" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI24" s="6">
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
         <v>3</v>
       </c>
@@ -3741,11 +3817,14 @@
       <c r="AG25" s="32">
         <v>0</v>
       </c>
-      <c r="AH25" s="6">
+      <c r="AH25" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI25" s="6">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A26" s="18">
         <v>3</v>
       </c>
@@ -3848,11 +3927,14 @@
       <c r="AG26" s="32">
         <v>0</v>
       </c>
-      <c r="AH26" s="6">
+      <c r="AH26" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI26" s="6">
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A27" s="18">
         <v>3</v>
       </c>
@@ -3955,11 +4037,14 @@
       <c r="AG27" s="32">
         <v>3</v>
       </c>
-      <c r="AH27" s="6">
+      <c r="AH27" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI27" s="6">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A28" s="18">
         <v>3</v>
       </c>
@@ -4062,11 +4147,14 @@
       <c r="AG28" s="32">
         <v>3</v>
       </c>
-      <c r="AH28" s="6">
+      <c r="AH28" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI28" s="6">
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A29" s="18">
         <v>3</v>
       </c>
@@ -4169,11 +4257,14 @@
       <c r="AG29" s="32">
         <v>3</v>
       </c>
-      <c r="AH29" s="6">
+      <c r="AH29" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI29" s="6">
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A30" s="18">
         <v>3</v>
       </c>
@@ -4276,11 +4367,14 @@
       <c r="AG30" s="32">
         <v>3</v>
       </c>
-      <c r="AH30" s="6">
+      <c r="AH30" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI30" s="6">
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A31" s="18">
         <v>3</v>
       </c>
@@ -4383,11 +4477,14 @@
       <c r="AG31" s="32">
         <v>3</v>
       </c>
-      <c r="AH31" s="6">
+      <c r="AH31" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI31" s="6">
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A32" s="18">
         <v>4</v>
       </c>
@@ -4490,11 +4587,14 @@
       <c r="AG32" s="32">
         <v>0</v>
       </c>
-      <c r="AH32" s="6">
+      <c r="AH32" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI32" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A33" s="18">
         <v>4</v>
       </c>
@@ -4597,11 +4697,14 @@
       <c r="AG33" s="32">
         <v>0</v>
       </c>
-      <c r="AH33" s="6">
+      <c r="AH33" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI33" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A34" s="18">
         <v>4</v>
       </c>
@@ -4704,11 +4807,14 @@
       <c r="AG34" s="32">
         <v>0</v>
       </c>
-      <c r="AH34" s="6">
+      <c r="AH34" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI34" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A35" s="18">
         <v>4</v>
       </c>
@@ -4811,11 +4917,14 @@
       <c r="AG35" s="32">
         <v>0</v>
       </c>
-      <c r="AH35" s="6">
+      <c r="AH35" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI35" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A36" s="18">
         <v>4</v>
       </c>
@@ -4918,11 +5027,14 @@
       <c r="AG36" s="32">
         <v>0</v>
       </c>
-      <c r="AH36" s="6">
+      <c r="AH36" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI36" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A37" s="18">
         <v>4</v>
       </c>
@@ -5025,11 +5137,14 @@
       <c r="AG37" s="32">
         <v>3</v>
       </c>
-      <c r="AH37" s="6">
+      <c r="AH37" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI37" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A38" s="18">
         <v>4</v>
       </c>
@@ -5132,11 +5247,14 @@
       <c r="AG38" s="32">
         <v>3</v>
       </c>
-      <c r="AH38" s="6">
+      <c r="AH38" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI38" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A39" s="18">
         <v>4</v>
       </c>
@@ -5239,11 +5357,14 @@
       <c r="AG39" s="32">
         <v>3</v>
       </c>
-      <c r="AH39" s="6">
+      <c r="AH39" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI39" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A40" s="18">
         <v>4</v>
       </c>
@@ -5346,11 +5467,14 @@
       <c r="AG40" s="32">
         <v>3</v>
       </c>
-      <c r="AH40" s="6">
+      <c r="AH40" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI40" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A41" s="18">
         <v>4</v>
       </c>
@@ -5453,11 +5577,14 @@
       <c r="AG41" s="32">
         <v>3</v>
       </c>
-      <c r="AH41" s="6">
+      <c r="AH41" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI41" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A42" s="18">
         <v>5</v>
       </c>
@@ -5560,11 +5687,14 @@
       <c r="AG42" s="32">
         <v>0</v>
       </c>
-      <c r="AH42" s="6">
+      <c r="AH42" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI42" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A43" s="18">
         <v>5</v>
       </c>
@@ -5667,11 +5797,14 @@
       <c r="AG43" s="32">
         <v>0</v>
       </c>
-      <c r="AH43" s="6">
+      <c r="AH43" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI43" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A44" s="18">
         <v>5</v>
       </c>
@@ -5774,11 +5907,14 @@
       <c r="AG44" s="32">
         <v>0</v>
       </c>
-      <c r="AH44" s="6">
+      <c r="AH44" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI44" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A45" s="18">
         <v>5</v>
       </c>
@@ -5881,11 +6017,14 @@
       <c r="AG45" s="32">
         <v>0</v>
       </c>
-      <c r="AH45" s="6">
+      <c r="AH45" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI45" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A46" s="18">
         <v>5</v>
       </c>
@@ -5988,11 +6127,14 @@
       <c r="AG46" s="32">
         <v>0</v>
       </c>
-      <c r="AH46" s="6">
+      <c r="AH46" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI46" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A47" s="18">
         <v>5</v>
       </c>
@@ -6095,11 +6237,14 @@
       <c r="AG47" s="32">
         <v>3</v>
       </c>
-      <c r="AH47" s="6">
+      <c r="AH47" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI47" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A48" s="18">
         <v>5</v>
       </c>
@@ -6202,11 +6347,14 @@
       <c r="AG48" s="32">
         <v>3</v>
       </c>
-      <c r="AH48" s="6">
+      <c r="AH48" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI48" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A49" s="18">
         <v>5</v>
       </c>
@@ -6309,11 +6457,14 @@
       <c r="AG49" s="32">
         <v>3</v>
       </c>
-      <c r="AH49" s="6">
+      <c r="AH49" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI49" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A50" s="18">
         <v>5</v>
       </c>
@@ -6416,11 +6567,14 @@
       <c r="AG50" s="32">
         <v>3</v>
       </c>
-      <c r="AH50" s="6">
+      <c r="AH50" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI50" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A51" s="18">
         <v>5</v>
       </c>
@@ -6523,11 +6677,14 @@
       <c r="AG51" s="32">
         <v>3</v>
       </c>
-      <c r="AH51" s="6">
+      <c r="AH51" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI51" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A52" s="18">
         <v>6</v>
       </c>
@@ -6630,11 +6787,14 @@
       <c r="AG52" s="32">
         <v>3</v>
       </c>
-      <c r="AH52" s="6">
+      <c r="AH52" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI52" s="6">
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A53" s="18">
         <v>6</v>
       </c>
@@ -6737,11 +6897,14 @@
       <c r="AG53" s="32">
         <v>3</v>
       </c>
-      <c r="AH53" s="6">
+      <c r="AH53" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI53" s="6">
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A54" s="18">
         <v>6</v>
       </c>
@@ -6844,11 +7007,14 @@
       <c r="AG54" s="32">
         <v>3</v>
       </c>
-      <c r="AH54" s="6">
+      <c r="AH54" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI54" s="6">
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A55" s="18">
         <v>6</v>
       </c>
@@ -6951,11 +7117,14 @@
       <c r="AG55" s="32">
         <v>3</v>
       </c>
-      <c r="AH55" s="6">
+      <c r="AH55" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI55" s="6">
         <v>56</v>
       </c>
     </row>
-    <row r="56" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A56" s="18">
         <v>6</v>
       </c>
@@ -7058,11 +7227,14 @@
       <c r="AG56" s="32">
         <v>3</v>
       </c>
-      <c r="AH56" s="6">
+      <c r="AH56" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI56" s="6">
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A57" s="18">
         <v>6</v>
       </c>
@@ -7165,11 +7337,14 @@
       <c r="AG57" s="32">
         <v>0</v>
       </c>
-      <c r="AH57" s="6">
+      <c r="AH57" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI57" s="6">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A58" s="18">
         <v>6</v>
       </c>
@@ -7272,11 +7447,14 @@
       <c r="AG58" s="32">
         <v>0</v>
       </c>
-      <c r="AH58" s="6">
+      <c r="AH58" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI58" s="6">
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A59" s="18">
         <v>6</v>
       </c>
@@ -7379,11 +7557,14 @@
       <c r="AG59" s="32">
         <v>0</v>
       </c>
-      <c r="AH59" s="6">
+      <c r="AH59" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI59" s="6">
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A60" s="18">
         <v>6</v>
       </c>
@@ -7486,11 +7667,14 @@
       <c r="AG60" s="32">
         <v>0</v>
       </c>
-      <c r="AH60" s="6">
+      <c r="AH60" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI60" s="6">
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A61" s="18">
         <v>6</v>
       </c>
@@ -7593,11 +7777,14 @@
       <c r="AG61" s="32">
         <v>0</v>
       </c>
-      <c r="AH61" s="6">
+      <c r="AH61" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI61" s="6">
         <v>56</v>
       </c>
     </row>
-    <row r="62" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A62" s="18">
         <v>7</v>
       </c>
@@ -7700,11 +7887,14 @@
       <c r="AG62" s="32">
         <v>0</v>
       </c>
-      <c r="AH62" s="6">
+      <c r="AH62" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI62" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="63" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A63" s="18">
         <v>7</v>
       </c>
@@ -7807,11 +7997,14 @@
       <c r="AG63" s="32">
         <v>0</v>
       </c>
-      <c r="AH63" s="6">
+      <c r="AH63" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI63" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="64" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A64" s="18">
         <v>7</v>
       </c>
@@ -7914,11 +8107,14 @@
       <c r="AG64" s="32">
         <v>0</v>
       </c>
-      <c r="AH64" s="6">
+      <c r="AH64" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI64" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="65" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A65" s="18">
         <v>7</v>
       </c>
@@ -8021,11 +8217,14 @@
       <c r="AG65" s="32">
         <v>0</v>
       </c>
-      <c r="AH65" s="6">
+      <c r="AH65" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI65" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="66" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A66" s="18">
         <v>7</v>
       </c>
@@ -8128,11 +8327,14 @@
       <c r="AG66" s="32">
         <v>0</v>
       </c>
-      <c r="AH66" s="6">
+      <c r="AH66" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI66" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="67" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A67" s="18">
         <v>7</v>
       </c>
@@ -8235,11 +8437,14 @@
       <c r="AG67" s="32">
         <v>3</v>
       </c>
-      <c r="AH67" s="6">
+      <c r="AH67" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI67" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="68" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A68" s="18">
         <v>7</v>
       </c>
@@ -8342,11 +8547,14 @@
       <c r="AG68" s="32">
         <v>3</v>
       </c>
-      <c r="AH68" s="6">
+      <c r="AH68" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI68" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A69" s="18">
         <v>7</v>
       </c>
@@ -8449,11 +8657,14 @@
       <c r="AG69" s="32">
         <v>3</v>
       </c>
-      <c r="AH69" s="6">
+      <c r="AH69" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI69" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="70" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A70" s="18">
         <v>7</v>
       </c>
@@ -8556,11 +8767,14 @@
       <c r="AG70" s="32">
         <v>3</v>
       </c>
-      <c r="AH70" s="6">
+      <c r="AH70" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI70" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="71" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A71" s="18">
         <v>7</v>
       </c>
@@ -8663,11 +8877,14 @@
       <c r="AG71" s="32">
         <v>3</v>
       </c>
-      <c r="AH71" s="6">
+      <c r="AH71" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI71" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="72" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A72" s="18">
         <v>8</v>
       </c>
@@ -8770,11 +8987,14 @@
       <c r="AG72" s="32">
         <v>1</v>
       </c>
-      <c r="AH72" s="6">
+      <c r="AH72" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI72" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="73" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A73" s="18">
         <v>8</v>
       </c>
@@ -8877,11 +9097,14 @@
       <c r="AG73" s="32">
         <v>1</v>
       </c>
-      <c r="AH73" s="6">
+      <c r="AH73" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI73" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="74" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A74" s="18">
         <v>8</v>
       </c>
@@ -8984,11 +9207,14 @@
       <c r="AG74" s="32">
         <v>1</v>
       </c>
-      <c r="AH74" s="6">
+      <c r="AH74" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI74" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="75" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A75" s="18">
         <v>8</v>
       </c>
@@ -9091,11 +9317,14 @@
       <c r="AG75" s="32">
         <v>1</v>
       </c>
-      <c r="AH75" s="6">
+      <c r="AH75" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI75" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="76" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A76" s="18">
         <v>8</v>
       </c>
@@ -9198,11 +9427,14 @@
       <c r="AG76" s="32">
         <v>1</v>
       </c>
-      <c r="AH76" s="6">
+      <c r="AH76" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI76" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="77" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A77" s="18">
         <v>8</v>
       </c>
@@ -9305,11 +9537,14 @@
       <c r="AG77" s="32">
         <v>1</v>
       </c>
-      <c r="AH77" s="6">
+      <c r="AH77" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI77" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="78" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A78" s="18">
         <v>8</v>
       </c>
@@ -9412,11 +9647,14 @@
       <c r="AG78" s="32">
         <v>1</v>
       </c>
-      <c r="AH78" s="6">
+      <c r="AH78" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI78" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="79" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A79" s="18">
         <v>8</v>
       </c>
@@ -9519,11 +9757,14 @@
       <c r="AG79" s="32">
         <v>1</v>
       </c>
-      <c r="AH79" s="6">
+      <c r="AH79" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI79" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="80" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A80" s="18">
         <v>8</v>
       </c>
@@ -9626,11 +9867,14 @@
       <c r="AG80" s="32">
         <v>1</v>
       </c>
-      <c r="AH80" s="6">
+      <c r="AH80" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI80" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="81" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A81" s="18">
         <v>8</v>
       </c>
@@ -9733,11 +9977,14 @@
       <c r="AG81" s="32">
         <v>1</v>
       </c>
-      <c r="AH81" s="6">
+      <c r="AH81" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI81" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="82" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A82" s="18">
         <v>9</v>
       </c>
@@ -9840,11 +10087,14 @@
       <c r="AG82" s="32">
         <v>0</v>
       </c>
-      <c r="AH82" s="6">
+      <c r="AH82" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI82" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="83" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A83" s="18">
         <v>9</v>
       </c>
@@ -9947,11 +10197,14 @@
       <c r="AG83" s="32">
         <v>0</v>
       </c>
-      <c r="AH83" s="6">
+      <c r="AH83" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI83" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="84" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A84" s="18">
         <v>9</v>
       </c>
@@ -10054,11 +10307,14 @@
       <c r="AG84" s="32">
         <v>0</v>
       </c>
-      <c r="AH84" s="6">
+      <c r="AH84" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI84" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="85" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A85" s="18">
         <v>9</v>
       </c>
@@ -10161,11 +10417,14 @@
       <c r="AG85" s="32">
         <v>0</v>
       </c>
-      <c r="AH85" s="6">
+      <c r="AH85" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI85" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="86" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A86" s="18">
         <v>9</v>
       </c>
@@ -10268,11 +10527,14 @@
       <c r="AG86" s="32">
         <v>0</v>
       </c>
-      <c r="AH86" s="6">
+      <c r="AH86" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI86" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="87" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A87" s="18">
         <v>9</v>
       </c>
@@ -10375,11 +10637,14 @@
       <c r="AG87" s="32">
         <v>3</v>
       </c>
-      <c r="AH87" s="6">
+      <c r="AH87" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI87" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="88" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A88" s="18">
         <v>9</v>
       </c>
@@ -10482,11 +10747,14 @@
       <c r="AG88" s="32">
         <v>3</v>
       </c>
-      <c r="AH88" s="6">
+      <c r="AH88" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI88" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="89" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A89" s="18">
         <v>9</v>
       </c>
@@ -10589,11 +10857,14 @@
       <c r="AG89" s="32">
         <v>3</v>
       </c>
-      <c r="AH89" s="6">
+      <c r="AH89" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI89" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="90" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A90" s="18">
         <v>9</v>
       </c>
@@ -10696,11 +10967,14 @@
       <c r="AG90" s="32">
         <v>3</v>
       </c>
-      <c r="AH90" s="6">
+      <c r="AH90" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI90" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="91" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A91" s="18">
         <v>9</v>
       </c>
@@ -10803,11 +11077,14 @@
       <c r="AG91" s="32">
         <v>3</v>
       </c>
-      <c r="AH91" s="6">
+      <c r="AH91" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI91" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="92" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A92" s="18">
         <v>10</v>
       </c>
@@ -10910,11 +11187,14 @@
       <c r="AG92" s="32">
         <v>0</v>
       </c>
-      <c r="AH92" s="6">
+      <c r="AH92" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI92" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="93" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A93" s="18">
         <v>10</v>
       </c>
@@ -11017,11 +11297,14 @@
       <c r="AG93" s="32">
         <v>0</v>
       </c>
-      <c r="AH93" s="6">
+      <c r="AH93" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI93" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="94" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A94" s="18">
         <v>10</v>
       </c>
@@ -11124,11 +11407,14 @@
       <c r="AG94" s="32">
         <v>0</v>
       </c>
-      <c r="AH94" s="6">
+      <c r="AH94" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI94" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="95" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A95" s="18">
         <v>10</v>
       </c>
@@ -11231,11 +11517,14 @@
       <c r="AG95" s="32">
         <v>0</v>
       </c>
-      <c r="AH95" s="6">
+      <c r="AH95" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI95" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="96" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A96" s="18">
         <v>10</v>
       </c>
@@ -11338,11 +11627,14 @@
       <c r="AG96" s="32">
         <v>0</v>
       </c>
-      <c r="AH96" s="6">
+      <c r="AH96" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI96" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="97" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A97" s="18">
         <v>10</v>
       </c>
@@ -11445,11 +11737,14 @@
       <c r="AG97" s="32">
         <v>3</v>
       </c>
-      <c r="AH97" s="6">
+      <c r="AH97" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI97" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="98" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A98" s="18">
         <v>10</v>
       </c>
@@ -11552,11 +11847,14 @@
       <c r="AG98" s="32">
         <v>3</v>
       </c>
-      <c r="AH98" s="6">
+      <c r="AH98" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI98" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="99" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A99" s="18">
         <v>10</v>
       </c>
@@ -11659,11 +11957,14 @@
       <c r="AG99" s="32">
         <v>3</v>
       </c>
-      <c r="AH99" s="6">
+      <c r="AH99" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI99" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="100" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A100" s="18">
         <v>10</v>
       </c>
@@ -11766,11 +12067,14 @@
       <c r="AG100" s="32">
         <v>3</v>
       </c>
-      <c r="AH100" s="6">
+      <c r="AH100" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI100" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="101" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A101" s="18">
         <v>10</v>
       </c>
@@ -11873,11 +12177,14 @@
       <c r="AG101" s="32">
         <v>3</v>
       </c>
-      <c r="AH101" s="6">
+      <c r="AH101" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI101" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="102" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A102" s="18">
         <v>11</v>
       </c>
@@ -11980,11 +12287,14 @@
       <c r="AG102" s="32">
         <v>3</v>
       </c>
-      <c r="AH102" s="6">
+      <c r="AH102" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI102" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="103" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A103" s="18">
         <v>11</v>
       </c>
@@ -12087,11 +12397,14 @@
       <c r="AG103" s="32">
         <v>3</v>
       </c>
-      <c r="AH103" s="6">
+      <c r="AH103" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI103" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="104" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A104" s="18">
         <v>11</v>
       </c>
@@ -12194,11 +12507,14 @@
       <c r="AG104" s="32">
         <v>3</v>
       </c>
-      <c r="AH104" s="6">
+      <c r="AH104" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI104" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="105" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A105" s="18">
         <v>11</v>
       </c>
@@ -12301,11 +12617,14 @@
       <c r="AG105" s="32">
         <v>3</v>
       </c>
-      <c r="AH105" s="6">
+      <c r="AH105" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI105" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="106" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A106" s="18">
         <v>11</v>
       </c>
@@ -12408,11 +12727,14 @@
       <c r="AG106" s="32">
         <v>3</v>
       </c>
-      <c r="AH106" s="6">
+      <c r="AH106" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI106" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="107" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A107" s="18">
         <v>11</v>
       </c>
@@ -12515,11 +12837,14 @@
       <c r="AG107" s="32">
         <v>3</v>
       </c>
-      <c r="AH107" s="6">
+      <c r="AH107" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI107" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="108" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A108" s="18">
         <v>11</v>
       </c>
@@ -12622,11 +12947,14 @@
       <c r="AG108" s="32">
         <v>0</v>
       </c>
-      <c r="AH108" s="6">
+      <c r="AH108" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI108" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="109" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A109" s="18">
         <v>11</v>
       </c>
@@ -12729,11 +13057,14 @@
       <c r="AG109" s="32">
         <v>0</v>
       </c>
-      <c r="AH109" s="6">
+      <c r="AH109" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI109" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="110" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A110" s="18">
         <v>11</v>
       </c>
@@ -12836,11 +13167,14 @@
       <c r="AG110" s="32">
         <v>0</v>
       </c>
-      <c r="AH110" s="6">
+      <c r="AH110" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI110" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="111" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A111" s="18">
         <v>11</v>
       </c>
@@ -12943,11 +13277,14 @@
       <c r="AG111" s="32">
         <v>0</v>
       </c>
-      <c r="AH111" s="6">
+      <c r="AH111" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI111" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="112" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A112" s="18">
         <v>11</v>
       </c>
@@ -13050,11 +13387,14 @@
       <c r="AG112" s="32">
         <v>0</v>
       </c>
-      <c r="AH112" s="6">
+      <c r="AH112" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI112" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="113" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A113" s="18">
         <v>11</v>
       </c>
@@ -13157,11 +13497,14 @@
       <c r="AG113" s="32">
         <v>0</v>
       </c>
-      <c r="AH113" s="6">
+      <c r="AH113" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI113" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="114" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A114" s="18">
         <v>12</v>
       </c>
@@ -13264,11 +13607,14 @@
       <c r="AG114" s="32">
         <v>3</v>
       </c>
-      <c r="AH114" s="6">
+      <c r="AH114" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI114" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="115" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A115" s="18">
         <v>12</v>
       </c>
@@ -13371,11 +13717,14 @@
       <c r="AG115" s="32">
         <v>3</v>
       </c>
-      <c r="AH115" s="6">
+      <c r="AH115" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI115" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="116" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A116" s="18">
         <v>12</v>
       </c>
@@ -13478,11 +13827,14 @@
       <c r="AG116" s="32">
         <v>3</v>
       </c>
-      <c r="AH116" s="6">
+      <c r="AH116" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI116" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="117" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A117" s="18">
         <v>12</v>
       </c>
@@ -13585,11 +13937,14 @@
       <c r="AG117" s="32">
         <v>3</v>
       </c>
-      <c r="AH117" s="6">
+      <c r="AH117" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI117" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="118" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A118" s="18">
         <v>12</v>
       </c>
@@ -13692,11 +14047,14 @@
       <c r="AG118" s="32">
         <v>3</v>
       </c>
-      <c r="AH118" s="6">
+      <c r="AH118" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI118" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A119" s="18">
         <v>12</v>
       </c>
@@ -13799,11 +14157,14 @@
       <c r="AG119" s="32">
         <v>0</v>
       </c>
-      <c r="AH119" s="6">
+      <c r="AH119" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI119" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="120" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A120" s="18">
         <v>12</v>
       </c>
@@ -13906,11 +14267,14 @@
       <c r="AG120" s="32">
         <v>0</v>
       </c>
-      <c r="AH120" s="6">
+      <c r="AH120" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI120" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="121" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A121" s="18">
         <v>12</v>
       </c>
@@ -14013,11 +14377,14 @@
       <c r="AG121" s="32">
         <v>0</v>
       </c>
-      <c r="AH121" s="6">
+      <c r="AH121" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI121" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="122" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A122" s="18">
         <v>12</v>
       </c>
@@ -14120,11 +14487,14 @@
       <c r="AG122" s="32">
         <v>0</v>
       </c>
-      <c r="AH122" s="6">
+      <c r="AH122" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI122" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="123" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A123" s="18">
         <v>12</v>
       </c>
@@ -14227,11 +14597,14 @@
       <c r="AG123" s="32">
         <v>0</v>
       </c>
-      <c r="AH123" s="6">
+      <c r="AH123" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI123" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="124" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A124" s="18">
         <v>13</v>
       </c>
@@ -14334,11 +14707,14 @@
       <c r="AG124" s="32">
         <v>0</v>
       </c>
-      <c r="AH124" s="6">
+      <c r="AH124" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI124" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="125" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A125" s="18">
         <v>13</v>
       </c>
@@ -14441,11 +14817,14 @@
       <c r="AG125" s="32">
         <v>0</v>
       </c>
-      <c r="AH125" s="6">
+      <c r="AH125" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI125" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="126" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A126" s="18">
         <v>13</v>
       </c>
@@ -14548,11 +14927,14 @@
       <c r="AG126" s="32">
         <v>0</v>
       </c>
-      <c r="AH126" s="6">
+      <c r="AH126" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI126" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="127" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A127" s="18">
         <v>13</v>
       </c>
@@ -14655,14 +15037,17 @@
       <c r="AG127" s="32">
         <v>0</v>
       </c>
-      <c r="AH127" s="6">
+      <c r="AH127" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI127" s="6">
         <v>60</v>
       </c>
-      <c r="AJ127" s="1" t="s">
+      <c r="AK127" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="128" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A128" s="18">
         <v>13</v>
       </c>
@@ -14765,14 +15150,17 @@
       <c r="AG128" s="32">
         <v>0</v>
       </c>
-      <c r="AH128" s="6">
+      <c r="AH128" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI128" s="6">
         <v>60</v>
       </c>
-      <c r="AJ128" s="1" t="s">
+      <c r="AK128" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="129" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A129" s="18">
         <v>13</v>
       </c>
@@ -14875,14 +15263,17 @@
       <c r="AG129" s="32">
         <v>0</v>
       </c>
-      <c r="AH129" s="6">
+      <c r="AH129" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI129" s="6">
         <v>60</v>
       </c>
-      <c r="AJ129" s="1" t="s">
+      <c r="AK129" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="130" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A130" s="18">
         <v>13</v>
       </c>
@@ -14985,11 +15376,14 @@
       <c r="AG130" s="32">
         <v>3</v>
       </c>
-      <c r="AH130" s="6">
+      <c r="AH130" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI130" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="131" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A131" s="18">
         <v>13</v>
       </c>
@@ -15092,11 +15486,14 @@
       <c r="AG131" s="32">
         <v>3</v>
       </c>
-      <c r="AH131" s="6">
+      <c r="AH131" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI131" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="132" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A132" s="18">
         <v>13</v>
       </c>
@@ -15199,11 +15596,14 @@
       <c r="AG132" s="32">
         <v>3</v>
       </c>
-      <c r="AH132" s="6">
+      <c r="AH132" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI132" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="133" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A133" s="18">
         <v>13</v>
       </c>
@@ -15306,11 +15706,14 @@
       <c r="AG133" s="32">
         <v>3</v>
       </c>
-      <c r="AH133" s="6">
+      <c r="AH133" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI133" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="134" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A134" s="18">
         <v>13</v>
       </c>
@@ -15413,11 +15816,14 @@
       <c r="AG134" s="32">
         <v>3</v>
       </c>
-      <c r="AH134" s="6">
+      <c r="AH134" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI134" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="135" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A135" s="18">
         <v>13</v>
       </c>
@@ -15520,11 +15926,14 @@
       <c r="AG135" s="32">
         <v>3</v>
       </c>
-      <c r="AH135" s="6">
+      <c r="AH135" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI135" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="136" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A136" s="18">
         <v>14</v>
       </c>
@@ -15627,11 +16036,14 @@
       <c r="AG136" s="32">
         <v>0</v>
       </c>
-      <c r="AH136" s="6">
+      <c r="AH136" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI136" s="6">
         <v>53</v>
       </c>
     </row>
-    <row r="137" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A137" s="18">
         <v>14</v>
       </c>
@@ -15734,11 +16146,14 @@
       <c r="AG137" s="32">
         <v>0</v>
       </c>
-      <c r="AH137" s="6">
+      <c r="AH137" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI137" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="138" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A138" s="18">
         <v>14</v>
       </c>
@@ -15841,11 +16256,14 @@
       <c r="AG138" s="32">
         <v>0</v>
       </c>
-      <c r="AH138" s="6">
+      <c r="AH138" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI138" s="6">
         <v>54</v>
       </c>
     </row>
-    <row r="139" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A139" s="18">
         <v>14</v>
       </c>
@@ -15948,11 +16366,14 @@
       <c r="AG139" s="32">
         <v>0</v>
       </c>
-      <c r="AH139" s="6">
+      <c r="AH139" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI139" s="6">
         <v>54</v>
       </c>
     </row>
-    <row r="140" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A140" s="18">
         <v>14</v>
       </c>
@@ -16055,11 +16476,14 @@
       <c r="AG140" s="32">
         <v>0</v>
       </c>
-      <c r="AH140" s="6">
+      <c r="AH140" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI140" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="141" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A141" s="18">
         <v>14</v>
       </c>
@@ -16162,11 +16586,14 @@
       <c r="AG141" s="32">
         <v>0</v>
       </c>
-      <c r="AH141" s="6">
+      <c r="AH141" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI141" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="142" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A142" s="18">
         <v>14</v>
       </c>
@@ -16269,11 +16696,14 @@
       <c r="AG142" s="32">
         <v>3</v>
       </c>
-      <c r="AH142" s="6">
+      <c r="AH142" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI142" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="143" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A143" s="18">
         <v>14</v>
       </c>
@@ -16376,11 +16806,14 @@
       <c r="AG143" s="32">
         <v>3</v>
       </c>
-      <c r="AH143" s="6">
+      <c r="AH143" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI143" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="144" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A144" s="18">
         <v>14</v>
       </c>
@@ -16483,11 +16916,14 @@
       <c r="AG144" s="32">
         <v>3</v>
       </c>
-      <c r="AH144" s="6">
+      <c r="AH144" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI144" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="145" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A145" s="18">
         <v>14</v>
       </c>
@@ -16590,11 +17026,14 @@
       <c r="AG145" s="32">
         <v>3</v>
       </c>
-      <c r="AH145" s="6">
+      <c r="AH145" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI145" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="146" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A146" s="18">
         <v>14</v>
       </c>
@@ -16697,11 +17136,14 @@
       <c r="AG146" s="32">
         <v>3</v>
       </c>
-      <c r="AH146" s="6">
+      <c r="AH146" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI146" s="6">
         <v>16</v>
       </c>
     </row>
-    <row r="147" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A147" s="18">
         <v>14</v>
       </c>
@@ -16804,11 +17246,14 @@
       <c r="AG147" s="32">
         <v>3</v>
       </c>
-      <c r="AH147" s="6">
+      <c r="AH147" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI147" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="148" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A148" s="18">
         <v>14</v>
       </c>
@@ -16911,11 +17356,14 @@
       <c r="AG148" s="32">
         <v>3</v>
       </c>
-      <c r="AH148" s="6">
+      <c r="AH148" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI148" s="6">
         <v>41</v>
       </c>
     </row>
-    <row r="149" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A149" s="25">
         <v>15</v>
       </c>
@@ -17018,11 +17466,14 @@
       <c r="AG149" s="31">
         <v>0</v>
       </c>
-      <c r="AH149" s="12">
+      <c r="AH149" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI149" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="150" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A150" s="25">
         <v>15</v>
       </c>
@@ -17125,11 +17576,14 @@
       <c r="AG150" s="31">
         <v>0</v>
       </c>
-      <c r="AH150" s="12">
+      <c r="AH150" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI150" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="151" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A151" s="25">
         <v>15</v>
       </c>
@@ -17232,11 +17686,14 @@
       <c r="AG151" s="31">
         <v>0</v>
       </c>
-      <c r="AH151" s="12">
+      <c r="AH151" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI151" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="152" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A152" s="25">
         <v>15</v>
       </c>
@@ -17339,11 +17796,14 @@
       <c r="AG152" s="31">
         <v>0</v>
       </c>
-      <c r="AH152" s="12">
+      <c r="AH152" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI152" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="153" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A153" s="25">
         <v>15</v>
       </c>
@@ -17446,11 +17906,14 @@
       <c r="AG153" s="31">
         <v>0</v>
       </c>
-      <c r="AH153" s="12">
+      <c r="AH153" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI153" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="154" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A154" s="25">
         <v>15</v>
       </c>
@@ -17553,11 +18016,14 @@
       <c r="AG154" s="32">
         <v>3</v>
       </c>
-      <c r="AH154" s="12">
+      <c r="AH154" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI154" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="155" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A155" s="25">
         <v>15</v>
       </c>
@@ -17660,11 +18126,14 @@
       <c r="AG155" s="32">
         <v>3</v>
       </c>
-      <c r="AH155" s="12">
+      <c r="AH155" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI155" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="156" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A156" s="25">
         <v>15</v>
       </c>
@@ -17767,11 +18236,14 @@
       <c r="AG156" s="32">
         <v>3</v>
       </c>
-      <c r="AH156" s="12">
+      <c r="AH156" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI156" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="157" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A157" s="25">
         <v>15</v>
       </c>
@@ -17874,11 +18346,14 @@
       <c r="AG157" s="32">
         <v>3</v>
       </c>
-      <c r="AH157" s="12">
+      <c r="AH157" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI157" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="158" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A158" s="25">
         <v>15</v>
       </c>
@@ -17981,11 +18456,14 @@
       <c r="AG158" s="32">
         <v>3</v>
       </c>
-      <c r="AH158" s="12">
+      <c r="AH158" s="31">
+        <v>10</v>
+      </c>
+      <c r="AI158" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="159" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A159" s="18">
         <v>16</v>
       </c>
@@ -18088,11 +18566,14 @@
       <c r="AG159" s="32">
         <v>3</v>
       </c>
-      <c r="AH159" s="12">
+      <c r="AH159" s="31">
+        <v>12</v>
+      </c>
+      <c r="AI159" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="160" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A160" s="18">
         <v>16</v>
       </c>
@@ -18195,11 +18676,14 @@
       <c r="AG160" s="32">
         <v>3</v>
       </c>
-      <c r="AH160" s="12">
+      <c r="AH160" s="31">
+        <v>12</v>
+      </c>
+      <c r="AI160" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="161" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A161" s="18">
         <v>16</v>
       </c>
@@ -18302,11 +18786,14 @@
       <c r="AG161" s="32">
         <v>3</v>
       </c>
-      <c r="AH161" s="12">
+      <c r="AH161" s="31">
+        <v>12</v>
+      </c>
+      <c r="AI161" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="162" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A162" s="18">
         <v>16</v>
       </c>
@@ -18409,11 +18896,14 @@
       <c r="AG162" s="32">
         <v>3</v>
       </c>
-      <c r="AH162" s="12">
+      <c r="AH162" s="31">
+        <v>12</v>
+      </c>
+      <c r="AI162" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="163" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A163" s="18">
         <v>16</v>
       </c>
@@ -18516,11 +19006,14 @@
       <c r="AG163" s="32">
         <v>3</v>
       </c>
-      <c r="AH163" s="12">
+      <c r="AH163" s="31">
+        <v>12</v>
+      </c>
+      <c r="AI163" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="164" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A164" s="18">
         <v>16</v>
       </c>
@@ -18623,11 +19116,14 @@
       <c r="AG164" s="32">
         <v>3</v>
       </c>
-      <c r="AH164" s="12">
+      <c r="AH164" s="31">
+        <v>12</v>
+      </c>
+      <c r="AI164" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="165" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A165" s="18">
         <v>16</v>
       </c>
@@ -18730,11 +19226,14 @@
       <c r="AG165" s="32">
         <v>0</v>
       </c>
-      <c r="AH165" s="12">
+      <c r="AH165" s="31">
+        <v>12</v>
+      </c>
+      <c r="AI165" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="166" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A166" s="18">
         <v>16</v>
       </c>
@@ -18837,11 +19336,14 @@
       <c r="AG166" s="32">
         <v>0</v>
       </c>
-      <c r="AH166" s="12">
+      <c r="AH166" s="31">
+        <v>12</v>
+      </c>
+      <c r="AI166" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="167" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A167" s="18">
         <v>16</v>
       </c>
@@ -18944,11 +19446,14 @@
       <c r="AG167" s="32">
         <v>0</v>
       </c>
-      <c r="AH167" s="12">
+      <c r="AH167" s="31">
+        <v>12</v>
+      </c>
+      <c r="AI167" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="168" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A168" s="18">
         <v>16</v>
       </c>
@@ -19051,11 +19556,14 @@
       <c r="AG168" s="32">
         <v>0</v>
       </c>
-      <c r="AH168" s="12">
+      <c r="AH168" s="31">
+        <v>12</v>
+      </c>
+      <c r="AI168" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="169" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A169" s="18">
         <v>16</v>
       </c>
@@ -19158,11 +19666,14 @@
       <c r="AG169" s="32">
         <v>0</v>
       </c>
-      <c r="AH169" s="12">
+      <c r="AH169" s="31">
+        <v>12</v>
+      </c>
+      <c r="AI169" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="170" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A170" s="18">
         <v>16</v>
       </c>
@@ -19265,11 +19776,14 @@
       <c r="AG170" s="32">
         <v>0</v>
       </c>
-      <c r="AH170" s="12">
+      <c r="AH170" s="31">
+        <v>12</v>
+      </c>
+      <c r="AI170" s="12">
         <v>62</v>
       </c>
     </row>
-    <row r="171" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A171" s="18">
         <v>17</v>
       </c>
@@ -19372,11 +19886,14 @@
       <c r="AG171" s="32">
         <v>0</v>
       </c>
-      <c r="AH171" s="6">
+      <c r="AH171" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI171" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="172" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A172" s="18">
         <v>17</v>
       </c>
@@ -19479,11 +19996,14 @@
       <c r="AG172" s="32">
         <v>0</v>
       </c>
-      <c r="AH172" s="6">
+      <c r="AH172" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI172" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="173" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A173" s="18">
         <v>17</v>
       </c>
@@ -19586,11 +20106,14 @@
       <c r="AG173" s="32">
         <v>0</v>
       </c>
-      <c r="AH173" s="6">
+      <c r="AH173" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI173" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="174" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A174" s="18">
         <v>17</v>
       </c>
@@ -19693,11 +20216,14 @@
       <c r="AG174" s="32">
         <v>0</v>
       </c>
-      <c r="AH174" s="6">
+      <c r="AH174" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI174" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="175" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A175" s="18">
         <v>17</v>
       </c>
@@ -19800,11 +20326,14 @@
       <c r="AG175" s="32">
         <v>0</v>
       </c>
-      <c r="AH175" s="6">
+      <c r="AH175" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI175" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="176" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A176" s="18">
         <v>17</v>
       </c>
@@ -19907,11 +20436,14 @@
       <c r="AG176" s="32">
         <v>0</v>
       </c>
-      <c r="AH176" s="6">
+      <c r="AH176" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI176" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="177" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A177" s="18">
         <v>17</v>
       </c>
@@ -20014,11 +20546,14 @@
       <c r="AG177" s="32">
         <v>3</v>
       </c>
-      <c r="AH177" s="6">
+      <c r="AH177" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI177" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="178" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A178" s="18">
         <v>17</v>
       </c>
@@ -20121,11 +20656,14 @@
       <c r="AG178" s="32">
         <v>3</v>
       </c>
-      <c r="AH178" s="6">
+      <c r="AH178" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI178" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="179" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A179" s="18">
         <v>17</v>
       </c>
@@ -20228,11 +20766,14 @@
       <c r="AG179" s="32">
         <v>3</v>
       </c>
-      <c r="AH179" s="6">
+      <c r="AH179" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI179" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="180" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A180" s="18">
         <v>17</v>
       </c>
@@ -20335,11 +20876,14 @@
       <c r="AG180" s="32">
         <v>3</v>
       </c>
-      <c r="AH180" s="6">
+      <c r="AH180" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI180" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="181" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A181" s="18">
         <v>17</v>
       </c>
@@ -20442,11 +20986,14 @@
       <c r="AG181" s="32">
         <v>3</v>
       </c>
-      <c r="AH181" s="6">
+      <c r="AH181" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI181" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="182" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A182" s="18">
         <v>17</v>
       </c>
@@ -20549,11 +21096,14 @@
       <c r="AG182" s="32">
         <v>3</v>
       </c>
-      <c r="AH182" s="6">
+      <c r="AH182" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI182" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="183" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A183" s="18">
         <v>18</v>
       </c>
@@ -20656,11 +21206,14 @@
       <c r="AG183" s="32">
         <v>3</v>
       </c>
-      <c r="AH183" s="6">
+      <c r="AH183" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI183" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="184" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A184" s="18">
         <v>18</v>
       </c>
@@ -20763,11 +21316,14 @@
       <c r="AG184" s="32">
         <v>3</v>
       </c>
-      <c r="AH184" s="6">
+      <c r="AH184" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI184" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="185" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A185" s="18">
         <v>18</v>
       </c>
@@ -20870,11 +21426,14 @@
       <c r="AG185" s="32">
         <v>3</v>
       </c>
-      <c r="AH185" s="6">
+      <c r="AH185" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI185" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="186" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A186" s="18">
         <v>18</v>
       </c>
@@ -20977,11 +21536,14 @@
       <c r="AG186" s="32">
         <v>3</v>
       </c>
-      <c r="AH186" s="6">
+      <c r="AH186" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI186" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="187" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A187" s="18">
         <v>18</v>
       </c>
@@ -21084,11 +21646,14 @@
       <c r="AG187" s="32">
         <v>3</v>
       </c>
-      <c r="AH187" s="6">
+      <c r="AH187" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI187" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="188" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A188" s="18">
         <v>18</v>
       </c>
@@ -21191,11 +21756,14 @@
       <c r="AG188" s="32">
         <v>0</v>
       </c>
-      <c r="AH188" s="6">
+      <c r="AH188" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI188" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="189" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A189" s="18">
         <v>18</v>
       </c>
@@ -21298,11 +21866,14 @@
       <c r="AG189" s="32">
         <v>0</v>
       </c>
-      <c r="AH189" s="6">
+      <c r="AH189" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI189" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="190" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A190" s="18">
         <v>18</v>
       </c>
@@ -21405,11 +21976,14 @@
       <c r="AG190" s="32">
         <v>0</v>
       </c>
-      <c r="AH190" s="6">
+      <c r="AH190" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI190" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="191" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A191" s="18">
         <v>18</v>
       </c>
@@ -21512,11 +22086,14 @@
       <c r="AG191" s="32">
         <v>0</v>
       </c>
-      <c r="AH191" s="6">
+      <c r="AH191" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI191" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="192" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A192" s="18">
         <v>18</v>
       </c>
@@ -21619,11 +22196,14 @@
       <c r="AG192" s="32">
         <v>0</v>
       </c>
-      <c r="AH192" s="6">
+      <c r="AH192" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI192" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="193" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A193" s="18">
         <v>19</v>
       </c>
@@ -21726,11 +22306,14 @@
       <c r="AG193" s="32">
         <v>0</v>
       </c>
-      <c r="AH193" s="6">
+      <c r="AH193" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI193" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="194" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A194" s="18">
         <v>19</v>
       </c>
@@ -21833,11 +22416,14 @@
       <c r="AG194" s="32">
         <v>0</v>
       </c>
-      <c r="AH194" s="6">
+      <c r="AH194" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI194" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="195" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A195" s="18">
         <v>19</v>
       </c>
@@ -21940,11 +22526,14 @@
       <c r="AG195" s="32">
         <v>0</v>
       </c>
-      <c r="AH195" s="6">
+      <c r="AH195" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI195" s="6">
         <v>53</v>
       </c>
     </row>
-    <row r="196" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A196" s="18">
         <v>19</v>
       </c>
@@ -22047,11 +22636,14 @@
       <c r="AG196" s="32">
         <v>0</v>
       </c>
-      <c r="AH196" s="6">
+      <c r="AH196" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI196" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="197" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A197" s="18">
         <v>19</v>
       </c>
@@ -22154,11 +22746,14 @@
       <c r="AG197" s="32">
         <v>0</v>
       </c>
-      <c r="AH197" s="6">
+      <c r="AH197" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI197" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="198" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A198" s="18">
         <v>19</v>
       </c>
@@ -22261,11 +22856,14 @@
       <c r="AG198" s="32">
         <v>0</v>
       </c>
-      <c r="AH198" s="6">
+      <c r="AH198" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI198" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="199" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A199" s="18">
         <v>19</v>
       </c>
@@ -22368,11 +22966,14 @@
       <c r="AG199" s="32">
         <v>3</v>
       </c>
-      <c r="AH199" s="6">
+      <c r="AH199" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI199" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="200" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A200" s="18">
         <v>19</v>
       </c>
@@ -22475,11 +23076,14 @@
       <c r="AG200" s="32">
         <v>3</v>
       </c>
-      <c r="AH200" s="6">
+      <c r="AH200" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI200" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="201" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A201" s="18">
         <v>19</v>
       </c>
@@ -22582,11 +23186,14 @@
       <c r="AG201" s="32">
         <v>3</v>
       </c>
-      <c r="AH201" s="6">
+      <c r="AH201" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI201" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="202" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A202" s="18">
         <v>19</v>
       </c>
@@ -22689,11 +23296,14 @@
       <c r="AG202" s="32">
         <v>3</v>
       </c>
-      <c r="AH202" s="6">
+      <c r="AH202" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI202" s="6">
         <v>53</v>
       </c>
     </row>
-    <row r="203" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A203" s="18">
         <v>19</v>
       </c>
@@ -22796,11 +23406,14 @@
       <c r="AG203" s="32">
         <v>3</v>
       </c>
-      <c r="AH203" s="6">
+      <c r="AH203" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI203" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="204" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A204" s="18">
         <v>19</v>
       </c>
@@ -22903,11 +23516,14 @@
       <c r="AG204" s="32">
         <v>3</v>
       </c>
-      <c r="AH204" s="6">
+      <c r="AH204" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI204" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="205" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A205" s="18">
         <v>20</v>
       </c>
@@ -23010,11 +23626,14 @@
       <c r="AG205" s="32">
         <v>0</v>
       </c>
-      <c r="AH205" s="6">
+      <c r="AH205" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI205" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="206" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A206" s="18">
         <v>20</v>
       </c>
@@ -23117,11 +23736,14 @@
       <c r="AG206" s="32">
         <v>0</v>
       </c>
-      <c r="AH206" s="6">
+      <c r="AH206" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI206" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="207" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A207" s="18">
         <v>20</v>
       </c>
@@ -23224,11 +23846,14 @@
       <c r="AG207" s="32">
         <v>0</v>
       </c>
-      <c r="AH207" s="6">
+      <c r="AH207" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI207" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="208" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A208" s="18">
         <v>20</v>
       </c>
@@ -23331,11 +23956,14 @@
       <c r="AG208" s="32">
         <v>0</v>
       </c>
-      <c r="AH208" s="6">
+      <c r="AH208" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI208" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="209" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A209" s="18">
         <v>20</v>
       </c>
@@ -23438,11 +24066,14 @@
       <c r="AG209" s="32">
         <v>0</v>
       </c>
-      <c r="AH209" s="6">
+      <c r="AH209" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI209" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="210" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A210" s="18">
         <v>20</v>
       </c>
@@ -23545,11 +24176,14 @@
       <c r="AG210" s="32">
         <v>0</v>
       </c>
-      <c r="AH210" s="6">
+      <c r="AH210" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI210" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="211" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A211" s="18">
         <v>20</v>
       </c>
@@ -23652,11 +24286,14 @@
       <c r="AG211" s="32">
         <v>3</v>
       </c>
-      <c r="AH211" s="6">
+      <c r="AH211" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI211" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="212" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A212" s="18">
         <v>20</v>
       </c>
@@ -23759,11 +24396,14 @@
       <c r="AG212" s="32">
         <v>3</v>
       </c>
-      <c r="AH212" s="6">
+      <c r="AH212" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI212" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="213" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A213" s="18">
         <v>20</v>
       </c>
@@ -23866,11 +24506,14 @@
       <c r="AG213" s="32">
         <v>3</v>
       </c>
-      <c r="AH213" s="6">
+      <c r="AH213" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI213" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="214" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A214" s="18">
         <v>20</v>
       </c>
@@ -23973,11 +24616,14 @@
       <c r="AG214" s="32">
         <v>3</v>
       </c>
-      <c r="AH214" s="6">
+      <c r="AH214" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI214" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="215" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A215" s="18">
         <v>20</v>
       </c>
@@ -24080,11 +24726,14 @@
       <c r="AG215" s="32">
         <v>3</v>
       </c>
-      <c r="AH215" s="6">
+      <c r="AH215" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI215" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="216" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A216" s="18">
         <v>20</v>
       </c>
@@ -24187,11 +24836,14 @@
       <c r="AG216" s="32">
         <v>3</v>
       </c>
-      <c r="AH216" s="6">
+      <c r="AH216" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI216" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="217" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A217" s="18">
         <v>21</v>
       </c>
@@ -24294,11 +24946,14 @@
       <c r="AG217" s="32">
         <v>3</v>
       </c>
-      <c r="AH217" s="6">
+      <c r="AH217" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI217" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="218" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A218" s="18">
         <v>21</v>
       </c>
@@ -24401,11 +25056,14 @@
       <c r="AG218" s="32">
         <v>3</v>
       </c>
-      <c r="AH218" s="6">
+      <c r="AH218" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI218" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="219" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A219" s="18">
         <v>21</v>
       </c>
@@ -24508,11 +25166,14 @@
       <c r="AG219" s="32">
         <v>3</v>
       </c>
-      <c r="AH219" s="6">
+      <c r="AH219" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI219" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="220" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A220" s="18">
         <v>21</v>
       </c>
@@ -24615,11 +25276,14 @@
       <c r="AG220" s="32">
         <v>3</v>
       </c>
-      <c r="AH220" s="6">
+      <c r="AH220" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI220" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="221" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A221" s="18">
         <v>21</v>
       </c>
@@ -24722,11 +25386,14 @@
       <c r="AG221" s="32">
         <v>3</v>
       </c>
-      <c r="AH221" s="6">
+      <c r="AH221" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI221" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="222" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A222" s="18">
         <v>21</v>
       </c>
@@ -24829,11 +25496,14 @@
       <c r="AG222" s="32">
         <v>3</v>
       </c>
-      <c r="AH222" s="6">
+      <c r="AH222" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI222" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="223" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A223" s="18">
         <v>21</v>
       </c>
@@ -24936,11 +25606,14 @@
       <c r="AG223" s="32">
         <v>0</v>
       </c>
-      <c r="AH223" s="6">
+      <c r="AH223" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI223" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="224" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A224" s="18">
         <v>21</v>
       </c>
@@ -25043,11 +25716,14 @@
       <c r="AG224" s="32">
         <v>0</v>
       </c>
-      <c r="AH224" s="6">
+      <c r="AH224" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI224" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="225" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A225" s="18">
         <v>21</v>
       </c>
@@ -25150,11 +25826,14 @@
       <c r="AG225" s="32">
         <v>0</v>
       </c>
-      <c r="AH225" s="6">
+      <c r="AH225" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI225" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="226" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A226" s="18">
         <v>21</v>
       </c>
@@ -25257,11 +25936,14 @@
       <c r="AG226" s="32">
         <v>0</v>
       </c>
-      <c r="AH226" s="6">
+      <c r="AH226" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI226" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="227" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A227" s="18">
         <v>21</v>
       </c>
@@ -25364,11 +26046,14 @@
       <c r="AG227" s="32">
         <v>0</v>
       </c>
-      <c r="AH227" s="6">
+      <c r="AH227" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI227" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="228" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A228" s="18">
         <v>21</v>
       </c>
@@ -25471,11 +26156,14 @@
       <c r="AG228" s="32">
         <v>0</v>
       </c>
-      <c r="AH228" s="6">
+      <c r="AH228" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI228" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="229" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A229" s="18">
         <v>22</v>
       </c>
@@ -25578,11 +26266,14 @@
       <c r="AG229" s="32">
         <v>3</v>
       </c>
-      <c r="AH229" s="6">
+      <c r="AH229" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI229" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="230" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A230" s="18">
         <v>22</v>
       </c>
@@ -25685,11 +26376,14 @@
       <c r="AG230" s="32">
         <v>3</v>
       </c>
-      <c r="AH230" s="6">
+      <c r="AH230" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI230" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="231" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A231" s="18">
         <v>22</v>
       </c>
@@ -25792,11 +26486,14 @@
       <c r="AG231" s="32">
         <v>3</v>
       </c>
-      <c r="AH231" s="6">
+      <c r="AH231" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI231" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="232" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A232" s="18">
         <v>22</v>
       </c>
@@ -25899,11 +26596,14 @@
       <c r="AG232" s="32">
         <v>3</v>
       </c>
-      <c r="AH232" s="6">
+      <c r="AH232" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI232" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="233" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A233" s="18">
         <v>22</v>
       </c>
@@ -26006,11 +26706,14 @@
       <c r="AG233" s="32">
         <v>3</v>
       </c>
-      <c r="AH233" s="6">
+      <c r="AH233" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI233" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="234" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A234" s="18">
         <v>22</v>
       </c>
@@ -26113,11 +26816,14 @@
       <c r="AG234" s="32">
         <v>3</v>
       </c>
-      <c r="AH234" s="6">
+      <c r="AH234" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI234" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="235" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A235" s="18">
         <v>22</v>
       </c>
@@ -26220,11 +26926,14 @@
       <c r="AG235" s="32">
         <v>3</v>
       </c>
-      <c r="AH235" s="6">
+      <c r="AH235" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI235" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A236" s="18">
         <v>22</v>
       </c>
@@ -26327,11 +27036,14 @@
       <c r="AG236" s="32">
         <v>0</v>
       </c>
-      <c r="AH236" s="6">
+      <c r="AH236" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI236" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="237" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A237" s="18">
         <v>22</v>
       </c>
@@ -26434,11 +27146,14 @@
       <c r="AG237" s="32">
         <v>0</v>
       </c>
-      <c r="AH237" s="6">
+      <c r="AH237" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI237" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="238" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A238" s="18">
         <v>22</v>
       </c>
@@ -26541,11 +27256,14 @@
       <c r="AG238" s="32">
         <v>0</v>
       </c>
-      <c r="AH238" s="6">
+      <c r="AH238" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI238" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="239" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A239" s="18">
         <v>22</v>
       </c>
@@ -26648,11 +27366,14 @@
       <c r="AG239" s="32">
         <v>0</v>
       </c>
-      <c r="AH239" s="6">
+      <c r="AH239" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI239" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="240" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A240" s="18">
         <v>22</v>
       </c>
@@ -26755,11 +27476,14 @@
       <c r="AG240" s="32">
         <v>0</v>
       </c>
-      <c r="AH240" s="6">
+      <c r="AH240" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI240" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="241" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A241" s="18">
         <v>22</v>
       </c>
@@ -26862,11 +27586,14 @@
       <c r="AG241" s="32">
         <v>0</v>
       </c>
-      <c r="AH241" s="6">
+      <c r="AH241" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI241" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="242" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A242" s="18">
         <v>23</v>
       </c>
@@ -26969,11 +27696,14 @@
       <c r="AG242" s="32">
         <v>0</v>
       </c>
-      <c r="AH242" s="6">
+      <c r="AH242" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI242" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="243" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A243" s="18">
         <v>23</v>
       </c>
@@ -27076,11 +27806,14 @@
       <c r="AG243" s="32">
         <v>0</v>
       </c>
-      <c r="AH243" s="6">
+      <c r="AH243" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI243" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="244" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A244" s="18">
         <v>23</v>
       </c>
@@ -27183,11 +27916,14 @@
       <c r="AG244" s="32">
         <v>0</v>
       </c>
-      <c r="AH244" s="6">
+      <c r="AH244" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI244" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="245" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A245" s="18">
         <v>23</v>
       </c>
@@ -27290,11 +28026,14 @@
       <c r="AG245" s="32">
         <v>0</v>
       </c>
-      <c r="AH245" s="6">
+      <c r="AH245" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI245" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="246" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A246" s="18">
         <v>23</v>
       </c>
@@ -27397,11 +28136,14 @@
       <c r="AG246" s="32">
         <v>0</v>
       </c>
-      <c r="AH246" s="6">
+      <c r="AH246" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI246" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="247" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A247" s="18">
         <v>23</v>
       </c>
@@ -27504,11 +28246,14 @@
       <c r="AG247" s="32">
         <v>3</v>
       </c>
-      <c r="AH247" s="6">
+      <c r="AH247" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI247" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="248" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A248" s="18">
         <v>23</v>
       </c>
@@ -27611,11 +28356,14 @@
       <c r="AG248" s="32">
         <v>3</v>
       </c>
-      <c r="AH248" s="6">
+      <c r="AH248" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI248" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="249" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A249" s="18">
         <v>23</v>
       </c>
@@ -27718,11 +28466,14 @@
       <c r="AG249" s="32">
         <v>3</v>
       </c>
-      <c r="AH249" s="6">
+      <c r="AH249" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI249" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="250" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A250" s="18">
         <v>23</v>
       </c>
@@ -27825,11 +28576,14 @@
       <c r="AG250" s="32">
         <v>3</v>
       </c>
-      <c r="AH250" s="6">
+      <c r="AH250" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI250" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="251" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A251" s="18">
         <v>23</v>
       </c>
@@ -27932,11 +28686,14 @@
       <c r="AG251" s="32">
         <v>3</v>
       </c>
-      <c r="AH251" s="6">
+      <c r="AH251" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI251" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="252" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A252" s="18">
         <v>24</v>
       </c>
@@ -28039,11 +28796,14 @@
       <c r="AG252" s="32">
         <v>1</v>
       </c>
-      <c r="AH252" s="6">
+      <c r="AH252" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI252" s="6">
         <v>52</v>
       </c>
     </row>
-    <row r="253" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A253" s="18">
         <v>24</v>
       </c>
@@ -28146,11 +28906,14 @@
       <c r="AG253" s="32">
         <v>1</v>
       </c>
-      <c r="AH253" s="6">
+      <c r="AH253" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI253" s="6">
         <v>52</v>
       </c>
     </row>
-    <row r="254" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A254" s="18">
         <v>24</v>
       </c>
@@ -28253,11 +29016,14 @@
       <c r="AG254" s="32">
         <v>1</v>
       </c>
-      <c r="AH254" s="6">
+      <c r="AH254" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI254" s="6">
         <v>52</v>
       </c>
     </row>
-    <row r="255" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A255" s="18">
         <v>24</v>
       </c>
@@ -28360,11 +29126,14 @@
       <c r="AG255" s="32">
         <v>1</v>
       </c>
-      <c r="AH255" s="6">
+      <c r="AH255" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI255" s="6">
         <v>52</v>
       </c>
     </row>
-    <row r="256" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A256" s="18">
         <v>24</v>
       </c>
@@ -28467,11 +29236,14 @@
       <c r="AG256" s="32">
         <v>1</v>
       </c>
-      <c r="AH256" s="6">
+      <c r="AH256" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI256" s="6">
         <v>52</v>
       </c>
     </row>
-    <row r="257" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A257" s="18">
         <v>24</v>
       </c>
@@ -28574,11 +29346,14 @@
       <c r="AG257" s="32">
         <v>1</v>
       </c>
-      <c r="AH257" s="6">
+      <c r="AH257" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI257" s="6">
         <v>52</v>
       </c>
     </row>
-    <row r="258" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A258" s="18">
         <v>24</v>
       </c>
@@ -28681,11 +29456,14 @@
       <c r="AG258" s="32">
         <v>1</v>
       </c>
-      <c r="AH258" s="6">
+      <c r="AH258" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI258" s="6">
         <v>52</v>
       </c>
     </row>
-    <row r="259" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A259" s="18">
         <v>24</v>
       </c>
@@ -28788,11 +29566,14 @@
       <c r="AG259" s="32">
         <v>1</v>
       </c>
-      <c r="AH259" s="6">
+      <c r="AH259" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI259" s="6">
         <v>52</v>
       </c>
     </row>
-    <row r="260" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A260" s="18">
         <v>24</v>
       </c>
@@ -28895,11 +29676,14 @@
       <c r="AG260" s="32">
         <v>1</v>
       </c>
-      <c r="AH260" s="6">
+      <c r="AH260" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI260" s="6">
         <v>52</v>
       </c>
     </row>
-    <row r="261" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A261" s="18">
         <v>24</v>
       </c>
@@ -29002,11 +29786,14 @@
       <c r="AG261" s="32">
         <v>1</v>
       </c>
-      <c r="AH261" s="6">
+      <c r="AH261" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI261" s="6">
         <v>52</v>
       </c>
     </row>
-    <row r="262" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A262" s="18">
         <v>24</v>
       </c>
@@ -29109,11 +29896,14 @@
       <c r="AG262" s="32">
         <v>1</v>
       </c>
-      <c r="AH262" s="6">
+      <c r="AH262" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI262" s="6">
         <v>52</v>
       </c>
     </row>
-    <row r="263" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A263" s="18">
         <v>24</v>
       </c>
@@ -29216,11 +30006,14 @@
       <c r="AG263" s="32">
         <v>1</v>
       </c>
-      <c r="AH263" s="6">
+      <c r="AH263" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI263" s="6">
         <v>52</v>
       </c>
     </row>
-    <row r="264" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A264" s="18">
         <v>25</v>
       </c>
@@ -29323,11 +30116,14 @@
       <c r="AG264" s="32">
         <v>0</v>
       </c>
-      <c r="AH264" s="6">
+      <c r="AH264" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI264" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="265" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A265" s="18">
         <v>25</v>
       </c>
@@ -29430,11 +30226,14 @@
       <c r="AG265" s="32">
         <v>0</v>
       </c>
-      <c r="AH265" s="6">
+      <c r="AH265" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI265" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="266" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A266" s="18">
         <v>25</v>
       </c>
@@ -29537,11 +30336,14 @@
       <c r="AG266" s="32">
         <v>0</v>
       </c>
-      <c r="AH266" s="6">
+      <c r="AH266" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI266" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="267" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A267" s="18">
         <v>25</v>
       </c>
@@ -29644,11 +30446,14 @@
       <c r="AG267" s="32">
         <v>0</v>
       </c>
-      <c r="AH267" s="6">
+      <c r="AH267" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI267" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="268" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A268" s="18">
         <v>25</v>
       </c>
@@ -29751,11 +30556,14 @@
       <c r="AG268" s="32">
         <v>0</v>
       </c>
-      <c r="AH268" s="6">
+      <c r="AH268" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI268" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="269" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A269" s="18">
         <v>25</v>
       </c>
@@ -29858,11 +30666,14 @@
       <c r="AG269" s="32">
         <v>0</v>
       </c>
-      <c r="AH269" s="6">
+      <c r="AH269" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI269" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="270" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A270" s="18">
         <v>25</v>
       </c>
@@ -29965,11 +30776,14 @@
       <c r="AG270" s="32">
         <v>3</v>
       </c>
-      <c r="AH270" s="6">
+      <c r="AH270" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI270" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="271" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A271" s="18">
         <v>25</v>
       </c>
@@ -30072,11 +30886,14 @@
       <c r="AG271" s="32">
         <v>3</v>
       </c>
-      <c r="AH271" s="6">
+      <c r="AH271" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI271" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="272" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A272" s="18">
         <v>25</v>
       </c>
@@ -30179,11 +30996,14 @@
       <c r="AG272" s="32">
         <v>3</v>
       </c>
-      <c r="AH272" s="6">
+      <c r="AH272" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI272" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="273" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A273" s="18">
         <v>25</v>
       </c>
@@ -30286,11 +31106,14 @@
       <c r="AG273" s="32">
         <v>3</v>
       </c>
-      <c r="AH273" s="6">
+      <c r="AH273" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI273" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="274" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A274" s="18">
         <v>25</v>
       </c>
@@ -30393,11 +31216,14 @@
       <c r="AG274" s="32">
         <v>3</v>
       </c>
-      <c r="AH274" s="6">
+      <c r="AH274" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI274" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="275" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A275" s="18">
         <v>25</v>
       </c>
@@ -30500,11 +31326,14 @@
       <c r="AG275" s="32">
         <v>3</v>
       </c>
-      <c r="AH275" s="6">
+      <c r="AH275" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI275" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="276" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A276" s="18">
         <v>26</v>
       </c>
@@ -30567,11 +31396,14 @@
         <v>0</v>
       </c>
       <c r="AG276" s="32"/>
-      <c r="AH276" s="6">
+      <c r="AH276" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI276" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="277" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A277" s="18">
         <v>26</v>
       </c>
@@ -30634,11 +31466,14 @@
         <v>0</v>
       </c>
       <c r="AG277" s="32"/>
-      <c r="AH277" s="6">
+      <c r="AH277" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI277" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="278" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A278" s="18">
         <v>26</v>
       </c>
@@ -30701,11 +31536,14 @@
         <v>0</v>
       </c>
       <c r="AG278" s="32"/>
-      <c r="AH278" s="6">
+      <c r="AH278" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI278" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="279" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A279" s="18">
         <v>26</v>
       </c>
@@ -30768,11 +31606,14 @@
         <v>0</v>
       </c>
       <c r="AG279" s="32"/>
-      <c r="AH279" s="6">
+      <c r="AH279" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI279" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="280" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A280" s="18">
         <v>26</v>
       </c>
@@ -30835,11 +31676,14 @@
         <v>0</v>
       </c>
       <c r="AG280" s="32"/>
-      <c r="AH280" s="6">
+      <c r="AH280" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI280" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="281" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A281" s="18">
         <v>26</v>
       </c>
@@ -30902,11 +31746,14 @@
         <v>0</v>
       </c>
       <c r="AG281" s="32"/>
-      <c r="AH281" s="6">
+      <c r="AH281" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI281" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="282" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A282" s="18">
         <v>26</v>
       </c>
@@ -30968,11 +31815,14 @@
         <v>0</v>
       </c>
       <c r="AG282" s="32"/>
-      <c r="AH282" s="6">
+      <c r="AH282" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI282" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="283" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A283" s="18">
         <v>26</v>
       </c>
@@ -31035,11 +31885,14 @@
         <v>0</v>
       </c>
       <c r="AG283" s="32"/>
-      <c r="AH283" s="6">
+      <c r="AH283" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI283" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="284" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A284" s="18">
         <v>26</v>
       </c>
@@ -31102,11 +31955,14 @@
         <v>0</v>
       </c>
       <c r="AG284" s="32"/>
-      <c r="AH284" s="6">
+      <c r="AH284" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI284" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="285" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A285" s="18">
         <v>26</v>
       </c>
@@ -31169,11 +32025,14 @@
         <v>0</v>
       </c>
       <c r="AG285" s="32"/>
-      <c r="AH285" s="6">
+      <c r="AH285" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI285" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="286" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A286" s="18">
         <v>26</v>
       </c>
@@ -31236,11 +32095,14 @@
         <v>0</v>
       </c>
       <c r="AG286" s="32"/>
-      <c r="AH286" s="6">
+      <c r="AH286" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI286" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="287" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A287" s="18">
         <v>26</v>
       </c>
@@ -31303,11 +32165,14 @@
         <v>0</v>
       </c>
       <c r="AG287" s="32"/>
-      <c r="AH287" s="6">
+      <c r="AH287" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI287" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="288" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A288" s="18">
         <v>27</v>
       </c>
@@ -31370,11 +32235,14 @@
         <v>0</v>
       </c>
       <c r="AG288" s="32"/>
-      <c r="AH288" s="6">
+      <c r="AH288" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI288" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="289" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A289" s="18">
         <v>27</v>
       </c>
@@ -31437,11 +32305,14 @@
         <v>0</v>
       </c>
       <c r="AG289" s="32"/>
-      <c r="AH289" s="6">
+      <c r="AH289" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI289" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="290" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A290" s="18">
         <v>27</v>
       </c>
@@ -31504,11 +32375,14 @@
         <v>0</v>
       </c>
       <c r="AG290" s="32"/>
-      <c r="AH290" s="6">
+      <c r="AH290" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI290" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="291" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A291" s="18">
         <v>27</v>
       </c>
@@ -31571,11 +32445,14 @@
         <v>0</v>
       </c>
       <c r="AG291" s="32"/>
-      <c r="AH291" s="6">
+      <c r="AH291" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI291" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="292" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A292" s="18">
         <v>27</v>
       </c>
@@ -31638,11 +32515,14 @@
         <v>0</v>
       </c>
       <c r="AG292" s="32"/>
-      <c r="AH292" s="6">
+      <c r="AH292" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI292" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="293" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A293" s="18">
         <v>27</v>
       </c>
@@ -31705,11 +32585,14 @@
         <v>0</v>
       </c>
       <c r="AG293" s="32"/>
-      <c r="AH293" s="6">
+      <c r="AH293" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI293" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="294" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A294" s="18">
         <v>27</v>
       </c>
@@ -31772,11 +32655,14 @@
         <v>0</v>
       </c>
       <c r="AG294" s="32"/>
-      <c r="AH294" s="6">
+      <c r="AH294" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI294" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="295" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A295" s="18">
         <v>27</v>
       </c>
@@ -31839,11 +32725,14 @@
         <v>0</v>
       </c>
       <c r="AG295" s="32"/>
-      <c r="AH295" s="6">
+      <c r="AH295" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI295" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="296" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A296" s="18">
         <v>27</v>
       </c>
@@ -31906,11 +32795,14 @@
         <v>0</v>
       </c>
       <c r="AG296" s="32"/>
-      <c r="AH296" s="6">
+      <c r="AH296" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI296" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="297" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A297" s="18">
         <v>27</v>
       </c>
@@ -31973,11 +32865,14 @@
         <v>0</v>
       </c>
       <c r="AG297" s="32"/>
-      <c r="AH297" s="6">
+      <c r="AH297" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI297" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="298" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A298" s="18">
         <v>27</v>
       </c>
@@ -32040,11 +32935,14 @@
         <v>0</v>
       </c>
       <c r="AG298" s="32"/>
-      <c r="AH298" s="6">
+      <c r="AH298" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI298" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="299" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A299" s="18">
         <v>27</v>
       </c>
@@ -32107,11 +33005,14 @@
         <v>0</v>
       </c>
       <c r="AG299" s="32"/>
-      <c r="AH299" s="6">
+      <c r="AH299" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI299" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="300" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A300" s="18">
         <v>28</v>
       </c>
@@ -32174,11 +33075,14 @@
         <v>0</v>
       </c>
       <c r="AG300" s="32"/>
-      <c r="AH300" s="6">
+      <c r="AH300" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI300" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="301" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A301" s="18">
         <v>28</v>
       </c>
@@ -32241,11 +33145,14 @@
         <v>0</v>
       </c>
       <c r="AG301" s="32"/>
-      <c r="AH301" s="6">
+      <c r="AH301" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI301" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="302" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A302" s="18">
         <v>28</v>
       </c>
@@ -32308,11 +33215,14 @@
         <v>0</v>
       </c>
       <c r="AG302" s="32"/>
-      <c r="AH302" s="6">
+      <c r="AH302" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI302" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="303" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A303" s="18">
         <v>28</v>
       </c>
@@ -32375,11 +33285,14 @@
         <v>0</v>
       </c>
       <c r="AG303" s="32"/>
-      <c r="AH303" s="6">
+      <c r="AH303" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI303" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="304" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A304" s="18">
         <v>28</v>
       </c>
@@ -32442,11 +33355,14 @@
         <v>0</v>
       </c>
       <c r="AG304" s="32"/>
-      <c r="AH304" s="6">
+      <c r="AH304" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI304" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="305" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A305" s="18">
         <v>28</v>
       </c>
@@ -32509,11 +33425,14 @@
         <v>0</v>
       </c>
       <c r="AG305" s="32"/>
-      <c r="AH305" s="6">
+      <c r="AH305" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI305" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="306" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A306" s="18">
         <v>28</v>
       </c>
@@ -32576,11 +33495,14 @@
         <v>0</v>
       </c>
       <c r="AG306" s="32"/>
-      <c r="AH306" s="6">
+      <c r="AH306" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI306" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="307" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A307" s="18">
         <v>28</v>
       </c>
@@ -32643,11 +33565,14 @@
         <v>0</v>
       </c>
       <c r="AG307" s="32"/>
-      <c r="AH307" s="6">
+      <c r="AH307" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI307" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="308" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A308" s="18">
         <v>28</v>
       </c>
@@ -32710,11 +33635,14 @@
         <v>0</v>
       </c>
       <c r="AG308" s="32"/>
-      <c r="AH308" s="6">
+      <c r="AH308" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI308" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="309" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A309" s="18">
         <v>28</v>
       </c>
@@ -32777,11 +33705,14 @@
         <v>0</v>
       </c>
       <c r="AG309" s="32"/>
-      <c r="AH309" s="6">
+      <c r="AH309" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI309" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="310" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A310" s="18">
         <v>28</v>
       </c>
@@ -32844,11 +33775,14 @@
         <v>0</v>
       </c>
       <c r="AG310" s="32"/>
-      <c r="AH310" s="6">
+      <c r="AH310" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI310" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="311" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A311" s="18">
         <v>28</v>
       </c>
@@ -32911,11 +33845,14 @@
         <v>0</v>
       </c>
       <c r="AG311" s="32"/>
-      <c r="AH311" s="6">
+      <c r="AH311" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI311" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="312" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A312" s="18">
         <v>29</v>
       </c>
@@ -32978,11 +33915,14 @@
         <v>0</v>
       </c>
       <c r="AG312" s="32"/>
-      <c r="AH312" s="6">
+      <c r="AH312" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI312" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="313" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A313" s="18">
         <v>29</v>
       </c>
@@ -33045,11 +33985,14 @@
         <v>0</v>
       </c>
       <c r="AG313" s="32"/>
-      <c r="AH313" s="6">
+      <c r="AH313" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI313" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="314" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A314" s="18">
         <v>29</v>
       </c>
@@ -33112,11 +34055,14 @@
         <v>0</v>
       </c>
       <c r="AG314" s="32"/>
-      <c r="AH314" s="6">
+      <c r="AH314" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI314" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="315" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A315" s="18">
         <v>29</v>
       </c>
@@ -33179,11 +34125,14 @@
         <v>0</v>
       </c>
       <c r="AG315" s="32"/>
-      <c r="AH315" s="6">
+      <c r="AH315" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI315" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="316" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A316" s="18">
         <v>29</v>
       </c>
@@ -33246,11 +34195,14 @@
         <v>0</v>
       </c>
       <c r="AG316" s="32"/>
-      <c r="AH316" s="6">
+      <c r="AH316" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI316" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="317" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A317" s="18">
         <v>29</v>
       </c>
@@ -33313,11 +34265,14 @@
         <v>0</v>
       </c>
       <c r="AG317" s="32"/>
-      <c r="AH317" s="6">
+      <c r="AH317" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI317" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="318" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A318" s="18">
         <v>29</v>
       </c>
@@ -33380,11 +34335,14 @@
         <v>0</v>
       </c>
       <c r="AG318" s="32"/>
-      <c r="AH318" s="6">
+      <c r="AH318" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI318" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="319" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A319" s="18">
         <v>29</v>
       </c>
@@ -33447,11 +34405,14 @@
         <v>0</v>
       </c>
       <c r="AG319" s="32"/>
-      <c r="AH319" s="6">
+      <c r="AH319" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI319" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="320" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A320" s="18">
         <v>29</v>
       </c>
@@ -33514,11 +34475,14 @@
         <v>0</v>
       </c>
       <c r="AG320" s="32"/>
-      <c r="AH320" s="6">
+      <c r="AH320" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI320" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="321" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A321" s="18">
         <v>29</v>
       </c>
@@ -33581,11 +34545,14 @@
         <v>0</v>
       </c>
       <c r="AG321" s="32"/>
-      <c r="AH321" s="6">
+      <c r="AH321" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI321" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="322" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A322" s="18">
         <v>29</v>
       </c>
@@ -33648,11 +34615,14 @@
         <v>0</v>
       </c>
       <c r="AG322" s="32"/>
-      <c r="AH322" s="6">
+      <c r="AH322" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI322" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="323" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A323" s="18">
         <v>29</v>
       </c>
@@ -33715,11 +34685,14 @@
         <v>0</v>
       </c>
       <c r="AG323" s="32"/>
-      <c r="AH323" s="6">
+      <c r="AH323" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI323" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="324" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A324" s="18">
         <v>30</v>
       </c>
@@ -33782,11 +34755,14 @@
         <v>0</v>
       </c>
       <c r="AG324" s="32"/>
-      <c r="AH324" s="6">
+      <c r="AH324" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI324" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="325" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A325" s="18">
         <v>30</v>
       </c>
@@ -33849,11 +34825,14 @@
         <v>0</v>
       </c>
       <c r="AG325" s="32"/>
-      <c r="AH325" s="6">
+      <c r="AH325" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI325" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="326" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A326" s="18">
         <v>30</v>
       </c>
@@ -33916,11 +34895,14 @@
         <v>0</v>
       </c>
       <c r="AG326" s="32"/>
-      <c r="AH326" s="6">
+      <c r="AH326" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI326" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="327" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A327" s="18">
         <v>30</v>
       </c>
@@ -33983,11 +34965,14 @@
         <v>0</v>
       </c>
       <c r="AG327" s="32"/>
-      <c r="AH327" s="6">
+      <c r="AH327" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI327" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="328" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A328" s="18">
         <v>30</v>
       </c>
@@ -34050,11 +35035,14 @@
         <v>0</v>
       </c>
       <c r="AG328" s="32"/>
-      <c r="AH328" s="6">
+      <c r="AH328" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI328" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="329" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A329" s="18">
         <v>30</v>
       </c>
@@ -34117,11 +35105,14 @@
         <v>0</v>
       </c>
       <c r="AG329" s="32"/>
-      <c r="AH329" s="6">
+      <c r="AH329" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI329" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="330" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A330" s="18">
         <v>30</v>
       </c>
@@ -34184,11 +35175,14 @@
         <v>0</v>
       </c>
       <c r="AG330" s="32"/>
-      <c r="AH330" s="6">
+      <c r="AH330" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI330" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="331" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A331" s="18">
         <v>30</v>
       </c>
@@ -34251,11 +35245,14 @@
         <v>0</v>
       </c>
       <c r="AG331" s="32"/>
-      <c r="AH331" s="6">
+      <c r="AH331" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI331" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="332" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A332" s="18">
         <v>30</v>
       </c>
@@ -34318,11 +35315,14 @@
         <v>0</v>
       </c>
       <c r="AG332" s="32"/>
-      <c r="AH332" s="6">
+      <c r="AH332" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI332" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="333" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A333" s="18">
         <v>30</v>
       </c>
@@ -34385,11 +35385,14 @@
         <v>0</v>
       </c>
       <c r="AG333" s="32"/>
-      <c r="AH333" s="6">
+      <c r="AH333" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI333" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="334" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A334" s="18">
         <v>30</v>
       </c>
@@ -34452,11 +35455,14 @@
         <v>0</v>
       </c>
       <c r="AG334" s="32"/>
-      <c r="AH334" s="6">
+      <c r="AH334" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI334" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="335" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A335" s="18">
         <v>30</v>
       </c>
@@ -34519,11 +35525,14 @@
         <v>0</v>
       </c>
       <c r="AG335" s="32"/>
-      <c r="AH335" s="6">
+      <c r="AH335" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI335" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="336" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A336" s="39">
         <v>31</v>
       </c>
@@ -34586,11 +35595,14 @@
         <v>0</v>
       </c>
       <c r="AG336" s="32"/>
-      <c r="AH336" s="6">
+      <c r="AH336" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI336" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="337" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A337" s="39">
         <v>31</v>
       </c>
@@ -34653,11 +35665,14 @@
         <v>0</v>
       </c>
       <c r="AG337" s="32"/>
-      <c r="AH337" s="6">
+      <c r="AH337" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI337" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="338" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A338" s="39">
         <v>31</v>
       </c>
@@ -34720,11 +35735,14 @@
         <v>0</v>
       </c>
       <c r="AG338" s="32"/>
-      <c r="AH338" s="6">
+      <c r="AH338" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI338" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="339" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A339" s="39">
         <v>31</v>
       </c>
@@ -34789,11 +35807,14 @@
         <v>0</v>
       </c>
       <c r="AG339" s="32"/>
-      <c r="AH339" s="6">
+      <c r="AH339" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI339" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="340" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A340" s="39">
         <v>31</v>
       </c>
@@ -34858,11 +35879,14 @@
         <v>0</v>
       </c>
       <c r="AG340" s="32"/>
-      <c r="AH340" s="6">
+      <c r="AH340" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI340" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="341" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A341" s="39">
         <v>31</v>
       </c>
@@ -34927,11 +35951,14 @@
         <v>0</v>
       </c>
       <c r="AG341" s="32"/>
-      <c r="AH341" s="6">
+      <c r="AH341" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI341" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="342" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A342" s="39">
         <v>31</v>
       </c>
@@ -34994,11 +36021,14 @@
         <v>0</v>
       </c>
       <c r="AG342" s="32"/>
-      <c r="AH342" s="6">
+      <c r="AH342" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI342" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="343" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A343" s="39">
         <v>31</v>
       </c>
@@ -35061,11 +36091,14 @@
         <v>0</v>
       </c>
       <c r="AG343" s="32"/>
-      <c r="AH343" s="6">
+      <c r="AH343" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI343" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="344" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A344" s="39">
         <v>31</v>
       </c>
@@ -35128,11 +36161,14 @@
         <v>0</v>
       </c>
       <c r="AG344" s="32"/>
-      <c r="AH344" s="6">
+      <c r="AH344" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI344" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="345" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A345" s="39">
         <v>31</v>
       </c>
@@ -35195,11 +36231,14 @@
         <v>0</v>
       </c>
       <c r="AG345" s="32"/>
-      <c r="AH345" s="6">
+      <c r="AH345" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI345" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="346" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A346" s="39">
         <v>31</v>
       </c>
@@ -35262,11 +36301,14 @@
         <v>0</v>
       </c>
       <c r="AG346" s="32"/>
-      <c r="AH346" s="6">
+      <c r="AH346" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI346" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="347" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A347" s="39">
         <v>31</v>
       </c>
@@ -35329,11 +36371,14 @@
         <v>0</v>
       </c>
       <c r="AG347" s="32"/>
-      <c r="AH347" s="6">
+      <c r="AH347" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI347" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="348" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A348" s="18">
         <v>32</v>
       </c>
@@ -35396,11 +36441,14 @@
         <v>0</v>
       </c>
       <c r="AG348" s="32"/>
-      <c r="AH348" s="6">
+      <c r="AH348" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI348" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="349" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A349" s="18">
         <v>32</v>
       </c>
@@ -35463,11 +36511,14 @@
         <v>0</v>
       </c>
       <c r="AG349" s="32"/>
-      <c r="AH349" s="6">
+      <c r="AH349" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI349" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="350" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A350" s="18">
         <v>32</v>
       </c>
@@ -35530,11 +36581,14 @@
         <v>0</v>
       </c>
       <c r="AG350" s="32"/>
-      <c r="AH350" s="6">
+      <c r="AH350" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI350" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="351" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A351" s="18">
         <v>32</v>
       </c>
@@ -35597,11 +36651,14 @@
         <v>0</v>
       </c>
       <c r="AG351" s="32"/>
-      <c r="AH351" s="6">
+      <c r="AH351" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI351" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="352" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A352" s="18">
         <v>32</v>
       </c>
@@ -35664,11 +36721,14 @@
         <v>0</v>
       </c>
       <c r="AG352" s="32"/>
-      <c r="AH352" s="6">
+      <c r="AH352" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI352" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="353" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A353" s="18">
         <v>32</v>
       </c>
@@ -35731,11 +36791,14 @@
         <v>0</v>
       </c>
       <c r="AG353" s="32"/>
-      <c r="AH353" s="6">
+      <c r="AH353" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI353" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="354" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A354" s="18">
         <v>32</v>
       </c>
@@ -35798,11 +36861,14 @@
         <v>0</v>
       </c>
       <c r="AG354" s="32"/>
-      <c r="AH354" s="6">
+      <c r="AH354" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI354" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="355" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A355" s="18">
         <v>32</v>
       </c>
@@ -35865,11 +36931,14 @@
         <v>0</v>
       </c>
       <c r="AG355" s="32"/>
-      <c r="AH355" s="6">
+      <c r="AH355" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI355" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="356" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A356" s="18">
         <v>32</v>
       </c>
@@ -35932,11 +37001,14 @@
         <v>0</v>
       </c>
       <c r="AG356" s="32"/>
-      <c r="AH356" s="6">
+      <c r="AH356" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI356" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="357" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A357" s="18">
         <v>32</v>
       </c>
@@ -35999,11 +37071,14 @@
         <v>0</v>
       </c>
       <c r="AG357" s="32"/>
-      <c r="AH357" s="6">
+      <c r="AH357" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI357" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="358" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A358" s="18">
         <v>33</v>
       </c>
@@ -36066,11 +37141,14 @@
         <v>0</v>
       </c>
       <c r="AG358" s="32"/>
-      <c r="AH358" s="6">
+      <c r="AH358" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI358" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="359" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A359" s="18">
         <v>33</v>
       </c>
@@ -36133,11 +37211,14 @@
         <v>0</v>
       </c>
       <c r="AG359" s="32"/>
-      <c r="AH359" s="6">
+      <c r="AH359" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI359" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="360" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A360" s="18">
         <v>33</v>
       </c>
@@ -36200,11 +37281,14 @@
         <v>0</v>
       </c>
       <c r="AG360" s="32"/>
-      <c r="AH360" s="6">
+      <c r="AH360" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI360" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="361" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A361" s="18">
         <v>33</v>
       </c>
@@ -36267,11 +37351,14 @@
         <v>0</v>
       </c>
       <c r="AG361" s="32"/>
-      <c r="AH361" s="6">
+      <c r="AH361" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI361" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="362" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A362" s="18">
         <v>33</v>
       </c>
@@ -36334,11 +37421,14 @@
         <v>0</v>
       </c>
       <c r="AG362" s="32"/>
-      <c r="AH362" s="6">
+      <c r="AH362" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI362" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="363" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A363" s="18">
         <v>33</v>
       </c>
@@ -36401,11 +37491,14 @@
         <v>0</v>
       </c>
       <c r="AG363" s="32"/>
-      <c r="AH363" s="6">
+      <c r="AH363" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI363" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="364" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A364" s="18">
         <v>33</v>
       </c>
@@ -36468,11 +37561,14 @@
         <v>0</v>
       </c>
       <c r="AG364" s="32"/>
-      <c r="AH364" s="6">
+      <c r="AH364" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI364" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="365" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A365" s="18">
         <v>33</v>
       </c>
@@ -36535,11 +37631,14 @@
         <v>0</v>
       </c>
       <c r="AG365" s="32"/>
-      <c r="AH365" s="6">
+      <c r="AH365" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI365" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="366" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A366" s="18">
         <v>33</v>
       </c>
@@ -36602,11 +37701,14 @@
         <v>0</v>
       </c>
       <c r="AG366" s="32"/>
-      <c r="AH366" s="6">
+      <c r="AH366" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI366" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="367" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A367" s="18">
         <v>33</v>
       </c>
@@ -36669,11 +37771,14 @@
         <v>0</v>
       </c>
       <c r="AG367" s="32"/>
-      <c r="AH367" s="6">
+      <c r="AH367" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI367" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="368" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A368" s="18">
         <v>33</v>
       </c>
@@ -36736,11 +37841,14 @@
         <v>0</v>
       </c>
       <c r="AG368" s="32"/>
-      <c r="AH368" s="6">
+      <c r="AH368" s="32">
+        <v>12</v>
+      </c>
+      <c r="AI368" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="369" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A369" s="19">
         <v>33</v>
       </c>
@@ -36803,11 +37911,14 @@
         <v>0</v>
       </c>
       <c r="AG369" s="33"/>
-      <c r="AH369" s="24">
+      <c r="AH369" s="33">
+        <v>12</v>
+      </c>
+      <c r="AI369" s="24">
         <v>57</v>
       </c>
     </row>
-    <row r="370" spans="1:34" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="370" spans="1:35" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
